--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <t>序列ID</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>中奖概率(万分比)</t>
-  </si>
-  <si>
-    <t>平均中奖金额</t>
   </si>
   <si>
     <t>int</t>
@@ -887,7 +884,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -912,19 +909,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1266,20 +1257,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="18.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="16.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9" style="3"/>
     <col min="7" max="7" width="9.25" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1295,40 +1286,37 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1338,7 +1326,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" spans="1:5">
       <c r="A5" s="7">
         <v>101</v>
       </c>
@@ -1349,24 +1337,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="7">
         <v>1600</v>
       </c>
-      <c r="F5" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G5" s="1">
-        <f>E5/SUMIF(B:B,B5,E:E)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H5" s="1">
-        <f>G5*F5</f>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:5">
       <c r="A6" s="7">
         <v>102</v>
       </c>
@@ -1377,24 +1354,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="7">
         <v>1000</v>
       </c>
-      <c r="F6" s="8">
-        <v>30000</v>
-      </c>
-      <c r="G6" s="1">
-        <f t="shared" ref="G6:G16" si="0">E6/SUMIF(B:B,B6,E:E)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="1">
-        <f t="shared" ref="H6:H40" si="1">G6*F6</f>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:5">
       <c r="A7" s="7">
         <v>103</v>
       </c>
@@ -1405,24 +1371,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="7">
         <v>1300</v>
       </c>
-      <c r="F7" s="8">
-        <v>20000</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>0.13</v>
-      </c>
-      <c r="H7" s="1">
-        <f t="shared" si="1"/>
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:8">
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:7">
       <c r="A8" s="7">
         <v>104</v>
       </c>
@@ -1433,24 +1388,14 @@
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="7">
         <v>1000</v>
       </c>
-      <c r="F8" s="9">
-        <v>50000</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:8">
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:7">
       <c r="A9" s="7">
         <v>105</v>
       </c>
@@ -1461,24 +1406,14 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="7">
         <v>900</v>
       </c>
-      <c r="F9" s="9">
-        <v>80000</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>0.09</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="1"/>
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:8">
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:7">
       <c r="A10" s="7">
         <v>106</v>
       </c>
@@ -1489,24 +1424,14 @@
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="7">
         <v>1000</v>
       </c>
-      <c r="F10" s="9">
-        <v>40000</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:8">
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:7">
       <c r="A11" s="7">
         <v>107</v>
       </c>
@@ -1517,24 +1442,14 @@
         <v>1</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="7">
         <v>1200</v>
       </c>
-      <c r="F11" s="9">
-        <v>100000</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.12</v>
-      </c>
-      <c r="H11" s="1">
-        <f t="shared" si="1"/>
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:7">
       <c r="A12" s="7">
         <v>108</v>
       </c>
@@ -1545,24 +1460,14 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="7">
         <v>300</v>
       </c>
-      <c r="F12" s="9">
-        <v>200000</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.03</v>
-      </c>
-      <c r="H12" s="1">
-        <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:8">
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:7">
       <c r="A13" s="7">
         <v>109</v>
       </c>
@@ -1573,24 +1478,14 @@
         <v>1</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="7">
         <v>600</v>
       </c>
-      <c r="F13" s="9">
-        <v>120000</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>0.06</v>
-      </c>
-      <c r="H13" s="1">
-        <f t="shared" si="1"/>
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:8">
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:7">
       <c r="A14" s="7">
         <v>110</v>
       </c>
@@ -1601,24 +1496,14 @@
         <v>1</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="7">
         <v>800</v>
       </c>
-      <c r="F14" s="9">
-        <v>90000</v>
-      </c>
-      <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>0.08</v>
-      </c>
-      <c r="H14" s="1">
-        <f t="shared" si="1"/>
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:8">
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:7">
       <c r="A15" s="7">
         <v>111</v>
       </c>
@@ -1629,24 +1514,14 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="7">
         <v>200</v>
       </c>
-      <c r="F15" s="9">
-        <v>400000</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-      <c r="H15" s="1">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:8">
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:7">
       <c r="A16" s="7">
         <v>112</v>
       </c>
@@ -1657,693 +1532,428 @@
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="7">
         <v>100</v>
       </c>
-      <c r="F16" s="9">
-        <v>800000</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="H16" s="1">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
-      <c r="A17" s="10">
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:5">
+      <c r="A17" s="9">
         <v>201</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>2</v>
       </c>
-      <c r="C17" s="10">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="9">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:5">
+      <c r="A18" s="9">
+        <v>202</v>
+      </c>
+      <c r="B18" s="9">
+        <v>2</v>
+      </c>
+      <c r="C18" s="9">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="9">
+        <v>203</v>
+      </c>
+      <c r="B19" s="9">
+        <v>2</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E19" s="9">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:7">
+      <c r="A20" s="9">
+        <v>204</v>
+      </c>
+      <c r="B20" s="9">
+        <v>2</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:7">
+      <c r="A21" s="9">
+        <v>205</v>
+      </c>
+      <c r="B21" s="9">
+        <v>2</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="9">
+        <v>900</v>
+      </c>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:7">
+      <c r="A22" s="9">
+        <v>206</v>
+      </c>
+      <c r="B22" s="9">
+        <v>2</v>
+      </c>
+      <c r="C22" s="9">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:7">
+      <c r="A23" s="9">
+        <v>207</v>
+      </c>
+      <c r="B23" s="9">
+        <v>2</v>
+      </c>
+      <c r="C23" s="9">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1200</v>
+      </c>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="1:7">
+      <c r="A24" s="9">
+        <v>208</v>
+      </c>
+      <c r="B24" s="9">
+        <v>2</v>
+      </c>
+      <c r="C24" s="9">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="9">
+        <v>300</v>
+      </c>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:7">
+      <c r="A25" s="9">
+        <v>209</v>
+      </c>
+      <c r="B25" s="9">
+        <v>2</v>
+      </c>
+      <c r="C25" s="9">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="9">
+        <v>600</v>
+      </c>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:7">
+      <c r="A26" s="9">
+        <v>210</v>
+      </c>
+      <c r="B26" s="9">
+        <v>2</v>
+      </c>
+      <c r="C26" s="9">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="9">
+        <v>800</v>
+      </c>
+      <c r="G26" s="8"/>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:7">
+      <c r="A27" s="9">
+        <v>211</v>
+      </c>
+      <c r="B27" s="9">
+        <v>2</v>
+      </c>
+      <c r="C27" s="9">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="9">
+        <v>200</v>
+      </c>
+      <c r="G27" s="8"/>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:7">
+      <c r="A28" s="9">
+        <v>212</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2</v>
+      </c>
+      <c r="C28" s="9">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="9">
+        <v>100</v>
+      </c>
+      <c r="G28" s="8"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="10">
+        <v>301</v>
+      </c>
+      <c r="B29" s="10">
+        <v>3</v>
+      </c>
+      <c r="C29" s="10">
+        <v>1</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="10">
         <v>1600</v>
       </c>
-      <c r="F17" s="8">
-        <v>50000</v>
-      </c>
-      <c r="G17" s="1">
-        <f t="shared" ref="G17:G40" si="2">E17/SUMIF(B:B,B17,E:E)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H17" s="1">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
-      <c r="A18" s="10">
-        <v>202</v>
-      </c>
-      <c r="B18" s="10">
-        <v>2</v>
-      </c>
-      <c r="C18" s="10">
-        <v>1</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="10">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="10">
+        <v>302</v>
+      </c>
+      <c r="B30" s="10">
+        <v>3</v>
+      </c>
+      <c r="C30" s="10">
+        <v>1</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="10">
         <v>1000</v>
       </c>
-      <c r="F18" s="8">
-        <v>60000</v>
-      </c>
-      <c r="G18" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="1">
-        <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
-      <c r="A19" s="10">
-        <v>203</v>
-      </c>
-      <c r="B19" s="10">
-        <v>2</v>
-      </c>
-      <c r="C19" s="10">
-        <v>1</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="10">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="10">
+        <v>303</v>
+      </c>
+      <c r="B31" s="10">
+        <v>3</v>
+      </c>
+      <c r="C31" s="10">
+        <v>1</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="10">
         <v>1300</v>
       </c>
-      <c r="F19" s="8">
-        <v>80000</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="H19" s="1">
-        <f t="shared" si="1"/>
-        <v>10400</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:8">
-      <c r="A20" s="10">
-        <v>204</v>
-      </c>
-      <c r="B20" s="10">
-        <v>2</v>
-      </c>
-      <c r="C20" s="10">
-        <v>1</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="10">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="10">
+        <v>304</v>
+      </c>
+      <c r="B32" s="10">
+        <v>3</v>
+      </c>
+      <c r="C32" s="10">
+        <v>1</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="10">
         <v>1000</v>
       </c>
-      <c r="F20" s="9">
-        <v>100000</v>
-      </c>
-      <c r="G20" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H20" s="1">
-        <f t="shared" si="1"/>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:8">
-      <c r="A21" s="10">
-        <v>205</v>
-      </c>
-      <c r="B21" s="10">
-        <v>2</v>
-      </c>
-      <c r="C21" s="10">
-        <v>1</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="10">
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="10">
+        <v>305</v>
+      </c>
+      <c r="B33" s="10">
+        <v>3</v>
+      </c>
+      <c r="C33" s="10">
+        <v>1</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="10">
         <v>900</v>
       </c>
-      <c r="F21" s="9">
-        <v>160000</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="2"/>
-        <v>0.09</v>
-      </c>
-      <c r="H21" s="1">
-        <f t="shared" si="1"/>
-        <v>14400</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:8">
-      <c r="A22" s="10">
-        <v>206</v>
-      </c>
-      <c r="B22" s="10">
-        <v>2</v>
-      </c>
-      <c r="C22" s="10">
-        <v>1</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="10">
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="10">
+        <v>306</v>
+      </c>
+      <c r="B34" s="10">
+        <v>3</v>
+      </c>
+      <c r="C34" s="10">
+        <v>1</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="10">
         <v>1000</v>
       </c>
-      <c r="F22" s="9">
-        <v>80000</v>
-      </c>
-      <c r="G22" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="1">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:8">
-      <c r="A23" s="10">
-        <v>207</v>
-      </c>
-      <c r="B23" s="10">
-        <v>2</v>
-      </c>
-      <c r="C23" s="10">
-        <v>1</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="10">
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="10">
+        <v>307</v>
+      </c>
+      <c r="B35" s="10">
+        <v>3</v>
+      </c>
+      <c r="C35" s="10">
+        <v>1</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="10">
         <v>1200</v>
       </c>
-      <c r="F23" s="9">
-        <v>200000</v>
-      </c>
-      <c r="G23" s="1">
-        <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="H23" s="1">
-        <f t="shared" si="1"/>
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:8">
-      <c r="A24" s="10">
-        <v>208</v>
-      </c>
-      <c r="B24" s="10">
-        <v>2</v>
-      </c>
-      <c r="C24" s="10">
-        <v>1</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="10">
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="10">
+        <v>308</v>
+      </c>
+      <c r="B36" s="10">
+        <v>3</v>
+      </c>
+      <c r="C36" s="10">
+        <v>1</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="10">
         <v>300</v>
       </c>
-      <c r="F24" s="9">
-        <v>400000</v>
-      </c>
-      <c r="G24" s="1">
-        <f t="shared" si="2"/>
-        <v>0.03</v>
-      </c>
-      <c r="H24" s="1">
-        <f t="shared" si="1"/>
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:8">
-      <c r="A25" s="10">
-        <v>209</v>
-      </c>
-      <c r="B25" s="10">
-        <v>2</v>
-      </c>
-      <c r="C25" s="10">
-        <v>1</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="10">
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="10">
+        <v>309</v>
+      </c>
+      <c r="B37" s="10">
+        <v>3</v>
+      </c>
+      <c r="C37" s="10">
+        <v>1</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="10">
         <v>600</v>
       </c>
-      <c r="F25" s="9">
-        <v>240000</v>
-      </c>
-      <c r="G25" s="1">
-        <f t="shared" si="2"/>
-        <v>0.06</v>
-      </c>
-      <c r="H25" s="1">
-        <f t="shared" si="1"/>
-        <v>14400</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:8">
-      <c r="A26" s="10">
-        <v>210</v>
-      </c>
-      <c r="B26" s="10">
-        <v>2</v>
-      </c>
-      <c r="C26" s="10">
-        <v>1</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="10">
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="10">
+        <v>310</v>
+      </c>
+      <c r="B38" s="10">
+        <v>3</v>
+      </c>
+      <c r="C38" s="10">
+        <v>1</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="10">
         <v>800</v>
       </c>
-      <c r="F26" s="9">
-        <v>180000</v>
-      </c>
-      <c r="G26" s="1">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="H26" s="1">
-        <f t="shared" si="1"/>
-        <v>14400</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:8">
-      <c r="A27" s="10">
-        <v>211</v>
-      </c>
-      <c r="B27" s="10">
-        <v>2</v>
-      </c>
-      <c r="C27" s="10">
-        <v>1</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="10">
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="10">
+        <v>311</v>
+      </c>
+      <c r="B39" s="10">
+        <v>3</v>
+      </c>
+      <c r="C39" s="10">
+        <v>1</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="10">
         <v>200</v>
       </c>
-      <c r="F27" s="9">
-        <v>800000</v>
-      </c>
-      <c r="G27" s="1">
-        <f t="shared" si="2"/>
-        <v>0.02</v>
-      </c>
-      <c r="H27" s="1">
-        <f t="shared" si="1"/>
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:8">
-      <c r="A28" s="10">
-        <v>212</v>
-      </c>
-      <c r="B28" s="10">
-        <v>2</v>
-      </c>
-      <c r="C28" s="10">
-        <v>1</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="10">
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="10">
+        <v>312</v>
+      </c>
+      <c r="B40" s="10">
+        <v>3</v>
+      </c>
+      <c r="C40" s="10">
+        <v>1</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="10">
         <v>100</v>
-      </c>
-      <c r="F28" s="9">
-        <v>1600000</v>
-      </c>
-      <c r="G28" s="1">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="H28" s="1">
-        <f t="shared" si="1"/>
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="11">
-        <v>301</v>
-      </c>
-      <c r="B29" s="11">
-        <v>3</v>
-      </c>
-      <c r="C29" s="11">
-        <v>1</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="11">
-        <v>1600</v>
-      </c>
-      <c r="F29" s="12">
-        <v>100000</v>
-      </c>
-      <c r="G29" s="1">
-        <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-      <c r="H29" s="1">
-        <f t="shared" si="1"/>
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="11">
-        <v>302</v>
-      </c>
-      <c r="B30" s="11">
-        <v>3</v>
-      </c>
-      <c r="C30" s="11">
-        <v>1</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="11">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="12">
-        <v>300000</v>
-      </c>
-      <c r="G30" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H30" s="1">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="11">
-        <v>303</v>
-      </c>
-      <c r="B31" s="11">
-        <v>3</v>
-      </c>
-      <c r="C31" s="11">
-        <v>1</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="11">
-        <v>1300</v>
-      </c>
-      <c r="F31" s="12">
-        <v>200000</v>
-      </c>
-      <c r="G31" s="1">
-        <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="H31" s="1">
-        <f t="shared" si="1"/>
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="11">
-        <v>304</v>
-      </c>
-      <c r="B32" s="11">
-        <v>3</v>
-      </c>
-      <c r="C32" s="11">
-        <v>1</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="11">
-        <v>1000</v>
-      </c>
-      <c r="F32" s="12">
-        <v>500000</v>
-      </c>
-      <c r="G32" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H32" s="1">
-        <f t="shared" si="1"/>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="11">
-        <v>305</v>
-      </c>
-      <c r="B33" s="11">
-        <v>3</v>
-      </c>
-      <c r="C33" s="11">
-        <v>1</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="11">
-        <v>900</v>
-      </c>
-      <c r="F33" s="12">
-        <v>800000</v>
-      </c>
-      <c r="G33" s="1">
-        <f t="shared" si="2"/>
-        <v>0.09</v>
-      </c>
-      <c r="H33" s="1">
-        <f t="shared" si="1"/>
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="11">
-        <v>306</v>
-      </c>
-      <c r="B34" s="11">
-        <v>3</v>
-      </c>
-      <c r="C34" s="11">
-        <v>1</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="11">
-        <v>1000</v>
-      </c>
-      <c r="F34" s="12">
-        <v>400000</v>
-      </c>
-      <c r="G34" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H34" s="1">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="11">
-        <v>307</v>
-      </c>
-      <c r="B35" s="11">
-        <v>3</v>
-      </c>
-      <c r="C35" s="11">
-        <v>1</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="11">
-        <v>1200</v>
-      </c>
-      <c r="F35" s="12">
-        <v>1000000</v>
-      </c>
-      <c r="G35" s="1">
-        <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="H35" s="1">
-        <f t="shared" si="1"/>
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="11">
-        <v>308</v>
-      </c>
-      <c r="B36" s="11">
-        <v>3</v>
-      </c>
-      <c r="C36" s="11">
-        <v>1</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="11">
-        <v>300</v>
-      </c>
-      <c r="F36" s="12">
-        <v>2000000</v>
-      </c>
-      <c r="G36" s="1">
-        <f t="shared" si="2"/>
-        <v>0.03</v>
-      </c>
-      <c r="H36" s="1">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="11">
-        <v>309</v>
-      </c>
-      <c r="B37" s="11">
-        <v>3</v>
-      </c>
-      <c r="C37" s="11">
-        <v>1</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="11">
-        <v>600</v>
-      </c>
-      <c r="F37" s="12">
-        <v>1200000</v>
-      </c>
-      <c r="G37" s="1">
-        <f t="shared" si="2"/>
-        <v>0.06</v>
-      </c>
-      <c r="H37" s="1">
-        <f t="shared" si="1"/>
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="11">
-        <v>310</v>
-      </c>
-      <c r="B38" s="11">
-        <v>3</v>
-      </c>
-      <c r="C38" s="11">
-        <v>1</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="11">
-        <v>800</v>
-      </c>
-      <c r="F38" s="12">
-        <v>900000</v>
-      </c>
-      <c r="G38" s="1">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="H38" s="1">
-        <f t="shared" si="1"/>
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="11">
-        <v>311</v>
-      </c>
-      <c r="B39" s="11">
-        <v>3</v>
-      </c>
-      <c r="C39" s="11">
-        <v>1</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="11">
-        <v>200</v>
-      </c>
-      <c r="F39" s="12">
-        <v>4000000</v>
-      </c>
-      <c r="G39" s="1">
-        <f t="shared" si="2"/>
-        <v>0.02</v>
-      </c>
-      <c r="H39" s="1">
-        <f t="shared" si="1"/>
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="11">
-        <v>312</v>
-      </c>
-      <c r="B40" s="11">
-        <v>3</v>
-      </c>
-      <c r="C40" s="11">
-        <v>1</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="11">
-        <v>100</v>
-      </c>
-      <c r="F40" s="12">
-        <v>8000000</v>
-      </c>
-      <c r="G40" s="1">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="H40" s="1">
-        <f t="shared" si="1"/>
-        <v>80000</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>序列ID</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>中奖概率(万分比)</t>
+  </si>
+  <si>
+    <t>平均中奖金额</t>
   </si>
   <si>
     <t>int</t>
@@ -884,7 +887,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -909,13 +912,19 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1257,20 +1266,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="18.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="16.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9" style="3"/>
+    <col min="6" max="6" width="23.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="9.25" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1286,37 +1295,40 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1326,7 +1338,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:5">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="7">
         <v>101</v>
       </c>
@@ -1337,13 +1349,24 @@
         <v>1</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7">
         <v>1600</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:5">
+      <c r="F5" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="1">
+        <f>E5/SUMIF(B:B,B5,E:E)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H5" s="1">
+        <f>G5*F5</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="7">
         <v>102</v>
       </c>
@@ -1354,13 +1377,24 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="7">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:5">
+      <c r="F6" s="8">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" ref="G6:G16" si="0">E6/SUMIF(B:B,B6,E:E)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" ref="H6:H40" si="1">G6*F6</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="7">
         <v>103</v>
       </c>
@@ -1371,13 +1405,24 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="7">
         <v>1300</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:7">
+      <c r="F7" s="8">
+        <v>20000</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.13</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:8">
       <c r="A8" s="7">
         <v>104</v>
       </c>
@@ -1388,14 +1433,24 @@
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="7">
         <v>1000</v>
       </c>
-      <c r="G8" s="8"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:7">
+      <c r="F8" s="9">
+        <v>50000</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:8">
       <c r="A9" s="7">
         <v>105</v>
       </c>
@@ -1406,14 +1461,24 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="7">
         <v>900</v>
       </c>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:7">
+      <c r="F9" s="9">
+        <v>80000</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:8">
       <c r="A10" s="7">
         <v>106</v>
       </c>
@@ -1424,14 +1489,24 @@
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="7">
         <v>1000</v>
       </c>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:7">
+      <c r="F10" s="9">
+        <v>40000</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:8">
       <c r="A11" s="7">
         <v>107</v>
       </c>
@@ -1442,14 +1517,24 @@
         <v>1</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" s="7">
         <v>1200</v>
       </c>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:7">
+      <c r="F11" s="9">
+        <v>100000</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:8">
       <c r="A12" s="7">
         <v>108</v>
       </c>
@@ -1460,14 +1545,24 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="7">
         <v>300</v>
       </c>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:7">
+      <c r="F12" s="9">
+        <v>200000</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.03</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:8">
       <c r="A13" s="7">
         <v>109</v>
       </c>
@@ -1478,14 +1573,24 @@
         <v>1</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="7">
         <v>600</v>
       </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:7">
+      <c r="F13" s="9">
+        <v>120000</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.06</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:8">
       <c r="A14" s="7">
         <v>110</v>
       </c>
@@ -1496,14 +1601,24 @@
         <v>1</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="7">
         <v>800</v>
       </c>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:7">
+      <c r="F14" s="9">
+        <v>90000</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:8">
       <c r="A15" s="7">
         <v>111</v>
       </c>
@@ -1514,14 +1629,24 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7">
         <v>200</v>
       </c>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:7">
+      <c r="F15" s="9">
+        <v>400000</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:8">
       <c r="A16" s="7">
         <v>112</v>
       </c>
@@ -1532,428 +1657,693 @@
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16" s="7">
         <v>100</v>
       </c>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:5">
-      <c r="A17" s="9">
+      <c r="F16" s="9">
+        <v>800000</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:8">
+      <c r="A17" s="10">
         <v>201</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="10">
         <v>2</v>
       </c>
-      <c r="C17" s="9">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="9">
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="10">
         <v>1600</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:5">
-      <c r="A18" s="9">
+      <c r="F17" s="8">
+        <v>50000</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" ref="G17:G40" si="2">E17/SUMIF(B:B,B17,E:E)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:8">
+      <c r="A18" s="10">
         <v>202</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="10">
         <v>2</v>
       </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="10">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F18" s="8">
+        <v>60000</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:8">
+      <c r="A19" s="10">
+        <v>203</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2</v>
+      </c>
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1300</v>
+      </c>
+      <c r="F19" s="8">
+        <v>80000</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="2"/>
+        <v>0.13</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="1"/>
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:8">
+      <c r="A20" s="10">
+        <v>204</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="9">
+        <v>100000</v>
+      </c>
+      <c r="G20" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:8">
+      <c r="A21" s="10">
+        <v>205</v>
+      </c>
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="10">
+        <v>900</v>
+      </c>
+      <c r="F21" s="9">
+        <v>160000</v>
+      </c>
+      <c r="G21" s="1">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="1"/>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:8">
+      <c r="A22" s="10">
+        <v>206</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10">
+        <v>1</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="9">
+        <v>80000</v>
+      </c>
+      <c r="G22" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:8">
+      <c r="A23" s="10">
+        <v>207</v>
+      </c>
+      <c r="B23" s="10">
+        <v>2</v>
+      </c>
+      <c r="C23" s="10">
+        <v>1</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1200</v>
+      </c>
+      <c r="F23" s="9">
+        <v>200000</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="1:8">
+      <c r="A24" s="10">
+        <v>208</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="10">
+        <v>300</v>
+      </c>
+      <c r="F24" s="9">
+        <v>400000</v>
+      </c>
+      <c r="G24" s="1">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:8">
+      <c r="A25" s="10">
+        <v>209</v>
+      </c>
+      <c r="B25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="10">
+        <v>1</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="10">
+        <v>600</v>
+      </c>
+      <c r="F25" s="9">
+        <v>240000</v>
+      </c>
+      <c r="G25" s="1">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="1"/>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:8">
+      <c r="A26" s="10">
+        <v>210</v>
+      </c>
+      <c r="B26" s="10">
+        <v>2</v>
+      </c>
+      <c r="C26" s="10">
+        <v>1</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="10">
+        <v>800</v>
+      </c>
+      <c r="F26" s="9">
+        <v>180000</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:8">
+      <c r="A27" s="10">
+        <v>211</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2</v>
+      </c>
+      <c r="C27" s="10">
+        <v>1</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E27" s="10">
+        <v>200</v>
+      </c>
+      <c r="F27" s="9">
+        <v>800000</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="2"/>
+        <v>0.02</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="1"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:8">
+      <c r="A28" s="10">
+        <v>212</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2</v>
+      </c>
+      <c r="C28" s="10">
+        <v>1</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="10">
+        <v>100</v>
+      </c>
+      <c r="F28" s="9">
+        <v>1600000</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="2"/>
+        <v>0.01</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="1"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="11">
+        <v>301</v>
+      </c>
+      <c r="B29" s="11">
+        <v>3</v>
+      </c>
+      <c r="C29" s="11">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="11">
+        <v>1600</v>
+      </c>
+      <c r="F29" s="12">
+        <v>100000</v>
+      </c>
+      <c r="G29" s="1">
+        <f t="shared" si="2"/>
+        <v>0.16</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="1"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="11">
+        <v>302</v>
+      </c>
+      <c r="B30" s="11">
+        <v>3</v>
+      </c>
+      <c r="C30" s="11">
+        <v>1</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="11">
         <v>1000</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:5">
-      <c r="A19" s="9">
-        <v>203</v>
-      </c>
-      <c r="B19" s="9">
-        <v>2</v>
-      </c>
-      <c r="C19" s="9">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="F30" s="12">
+        <v>300000</v>
+      </c>
+      <c r="G30" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="1"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="11">
+        <v>303</v>
+      </c>
+      <c r="B31" s="11">
+        <v>3</v>
+      </c>
+      <c r="C31" s="11">
+        <v>1</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="11">
         <v>1300</v>
       </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:7">
-      <c r="A20" s="9">
-        <v>204</v>
-      </c>
-      <c r="B20" s="9">
-        <v>2</v>
-      </c>
-      <c r="C20" s="9">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="F31" s="12">
+        <v>200000</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="2"/>
+        <v>0.13</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="1"/>
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="11">
+        <v>304</v>
+      </c>
+      <c r="B32" s="11">
+        <v>3</v>
+      </c>
+      <c r="C32" s="11">
+        <v>1</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="11">
         <v>1000</v>
       </c>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:7">
-      <c r="A21" s="9">
-        <v>205</v>
-      </c>
-      <c r="B21" s="9">
-        <v>2</v>
-      </c>
-      <c r="C21" s="9">
-        <v>1</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="F32" s="12">
+        <v>500000</v>
+      </c>
+      <c r="G32" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H32" s="1">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="11">
+        <v>305</v>
+      </c>
+      <c r="B33" s="11">
+        <v>3</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="11">
         <v>900</v>
       </c>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:7">
-      <c r="A22" s="9">
-        <v>206</v>
-      </c>
-      <c r="B22" s="9">
-        <v>2</v>
-      </c>
-      <c r="C22" s="9">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="9">
+      <c r="F33" s="12">
+        <v>800000</v>
+      </c>
+      <c r="G33" s="1">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
+      </c>
+      <c r="H33" s="1">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="11">
+        <v>306</v>
+      </c>
+      <c r="B34" s="11">
+        <v>3</v>
+      </c>
+      <c r="C34" s="11">
+        <v>1</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="11">
         <v>1000</v>
       </c>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:7">
-      <c r="A23" s="9">
-        <v>207</v>
-      </c>
-      <c r="B23" s="9">
-        <v>2</v>
-      </c>
-      <c r="C23" s="9">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="9">
+      <c r="F34" s="12">
+        <v>400000</v>
+      </c>
+      <c r="G34" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H34" s="1">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="11">
+        <v>307</v>
+      </c>
+      <c r="B35" s="11">
+        <v>3</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="11">
         <v>1200</v>
       </c>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:7">
-      <c r="A24" s="9">
-        <v>208</v>
-      </c>
-      <c r="B24" s="9">
-        <v>2</v>
-      </c>
-      <c r="C24" s="9">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="9">
+      <c r="F35" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="G35" s="1">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="H35" s="1">
+        <f t="shared" si="1"/>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="11">
+        <v>308</v>
+      </c>
+      <c r="B36" s="11">
+        <v>3</v>
+      </c>
+      <c r="C36" s="11">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="11">
         <v>300</v>
       </c>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:7">
-      <c r="A25" s="9">
-        <v>209</v>
-      </c>
-      <c r="B25" s="9">
-        <v>2</v>
-      </c>
-      <c r="C25" s="9">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="9">
+      <c r="F36" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="G36" s="1">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="11">
+        <v>309</v>
+      </c>
+      <c r="B37" s="11">
+        <v>3</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="11">
         <v>600</v>
       </c>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:7">
-      <c r="A26" s="9">
-        <v>210</v>
-      </c>
-      <c r="B26" s="9">
-        <v>2</v>
-      </c>
-      <c r="C26" s="9">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="9">
+      <c r="F37" s="12">
+        <v>1200000</v>
+      </c>
+      <c r="G37" s="1">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="11">
+        <v>310</v>
+      </c>
+      <c r="B38" s="11">
+        <v>3</v>
+      </c>
+      <c r="C38" s="11">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="11">
         <v>800</v>
       </c>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:7">
-      <c r="A27" s="9">
-        <v>211</v>
-      </c>
-      <c r="B27" s="9">
-        <v>2</v>
-      </c>
-      <c r="C27" s="9">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="9">
+      <c r="F38" s="12">
+        <v>900000</v>
+      </c>
+      <c r="G38" s="1">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+      <c r="H38" s="1">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="11">
+        <v>311</v>
+      </c>
+      <c r="B39" s="11">
+        <v>3</v>
+      </c>
+      <c r="C39" s="11">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="11">
         <v>200</v>
       </c>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:7">
-      <c r="A28" s="9">
-        <v>212</v>
-      </c>
-      <c r="B28" s="9">
-        <v>2</v>
-      </c>
-      <c r="C28" s="9">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="9">
+      <c r="F39" s="12">
+        <v>4000000</v>
+      </c>
+      <c r="G39" s="1">
+        <f t="shared" si="2"/>
+        <v>0.02</v>
+      </c>
+      <c r="H39" s="1">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="11">
+        <v>312</v>
+      </c>
+      <c r="B40" s="11">
+        <v>3</v>
+      </c>
+      <c r="C40" s="11">
+        <v>1</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="11">
         <v>100</v>
       </c>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="10">
-        <v>301</v>
-      </c>
-      <c r="B29" s="10">
-        <v>3</v>
-      </c>
-      <c r="C29" s="10">
-        <v>1</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="10">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="10">
-        <v>302</v>
-      </c>
-      <c r="B30" s="10">
-        <v>3</v>
-      </c>
-      <c r="C30" s="10">
-        <v>1</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="10">
-        <v>303</v>
-      </c>
-      <c r="B31" s="10">
-        <v>3</v>
-      </c>
-      <c r="C31" s="10">
-        <v>1</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="10">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="10">
-        <v>304</v>
-      </c>
-      <c r="B32" s="10">
-        <v>3</v>
-      </c>
-      <c r="C32" s="10">
-        <v>1</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="10">
-        <v>305</v>
-      </c>
-      <c r="B33" s="10">
-        <v>3</v>
-      </c>
-      <c r="C33" s="10">
-        <v>1</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="10">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="10">
-        <v>306</v>
-      </c>
-      <c r="B34" s="10">
-        <v>3</v>
-      </c>
-      <c r="C34" s="10">
-        <v>1</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="10">
-        <v>307</v>
-      </c>
-      <c r="B35" s="10">
-        <v>3</v>
-      </c>
-      <c r="C35" s="10">
-        <v>1</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="10">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="10">
-        <v>308</v>
-      </c>
-      <c r="B36" s="10">
-        <v>3</v>
-      </c>
-      <c r="C36" s="10">
-        <v>1</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="10">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="10">
-        <v>309</v>
-      </c>
-      <c r="B37" s="10">
-        <v>3</v>
-      </c>
-      <c r="C37" s="10">
-        <v>1</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="10">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="10">
-        <v>310</v>
-      </c>
-      <c r="B38" s="10">
-        <v>3</v>
-      </c>
-      <c r="C38" s="10">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="10">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="10">
-        <v>311</v>
-      </c>
-      <c r="B39" s="10">
-        <v>3</v>
-      </c>
-      <c r="C39" s="10">
-        <v>1</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="10">
-        <v>312</v>
-      </c>
-      <c r="B40" s="10">
-        <v>3</v>
-      </c>
-      <c r="C40" s="10">
-        <v>1</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="10">
-        <v>100</v>
+      <c r="F40" s="12">
+        <v>8000000</v>
+      </c>
+      <c r="G40" s="1">
+        <f t="shared" si="2"/>
+        <v>0.01</v>
+      </c>
+      <c r="H40" s="1">
+        <f t="shared" si="1"/>
+        <v>80000</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>序列ID</t>
   </si>
@@ -123,6 +123,9 @@
     <t>中奖概率(万分比)</t>
   </si>
   <si>
+    <t>平均中奖金额</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -135,13 +138,13 @@
     <t>turntableType</t>
   </si>
   <si>
-    <t>CalculationType</t>
+    <t>calculationType</t>
   </si>
   <si>
     <t>getitem</t>
   </si>
   <si>
-    <t>Probability</t>
+    <t>probability</t>
   </si>
   <si>
     <t>1990000_10000</t>
@@ -884,7 +887,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -909,13 +912,19 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1257,20 +1266,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="18.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="16.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9" style="3"/>
+    <col min="6" max="6" width="23.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="9.25" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1286,37 +1295,40 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1326,7 +1338,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:5">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="7">
         <v>101</v>
       </c>
@@ -1337,13 +1349,24 @@
         <v>1</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7">
         <v>1600</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:5">
+      <c r="F5" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="1">
+        <f>E5/SUMIF(B:B,B5,E:E)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H5" s="1">
+        <f>G5*F5</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="7">
         <v>102</v>
       </c>
@@ -1354,13 +1377,24 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="7">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:5">
+      <c r="F6" s="8">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" ref="G6:G16" si="0">E6/SUMIF(B:B,B6,E:E)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" ref="H6:H40" si="1">G6*F6</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="7">
         <v>103</v>
       </c>
@@ -1371,13 +1405,24 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="7">
         <v>1300</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:7">
+      <c r="F7" s="8">
+        <v>20000</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.13</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:8">
       <c r="A8" s="7">
         <v>104</v>
       </c>
@@ -1388,14 +1433,24 @@
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="7">
         <v>1000</v>
       </c>
-      <c r="G8" s="8"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:7">
+      <c r="F8" s="9">
+        <v>50000</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:8">
       <c r="A9" s="7">
         <v>105</v>
       </c>
@@ -1406,14 +1461,24 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="7">
         <v>900</v>
       </c>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:7">
+      <c r="F9" s="9">
+        <v>80000</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:8">
       <c r="A10" s="7">
         <v>106</v>
       </c>
@@ -1424,14 +1489,24 @@
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="7">
         <v>1000</v>
       </c>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:7">
+      <c r="F10" s="9">
+        <v>40000</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:8">
       <c r="A11" s="7">
         <v>107</v>
       </c>
@@ -1442,14 +1517,24 @@
         <v>1</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" s="7">
         <v>1200</v>
       </c>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:7">
+      <c r="F11" s="9">
+        <v>100000</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:8">
       <c r="A12" s="7">
         <v>108</v>
       </c>
@@ -1460,14 +1545,24 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="7">
         <v>300</v>
       </c>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:7">
+      <c r="F12" s="9">
+        <v>200000</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.03</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:8">
       <c r="A13" s="7">
         <v>109</v>
       </c>
@@ -1478,14 +1573,24 @@
         <v>1</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="7">
         <v>600</v>
       </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:7">
+      <c r="F13" s="9">
+        <v>120000</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.06</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:8">
       <c r="A14" s="7">
         <v>110</v>
       </c>
@@ -1496,14 +1601,24 @@
         <v>1</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="7">
         <v>800</v>
       </c>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:7">
+      <c r="F14" s="9">
+        <v>90000</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:8">
       <c r="A15" s="7">
         <v>111</v>
       </c>
@@ -1514,14 +1629,24 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7">
         <v>200</v>
       </c>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:7">
+      <c r="F15" s="9">
+        <v>400000</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:8">
       <c r="A16" s="7">
         <v>112</v>
       </c>
@@ -1532,428 +1657,693 @@
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16" s="7">
         <v>100</v>
       </c>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:5">
-      <c r="A17" s="9">
+      <c r="F16" s="9">
+        <v>800000</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:8">
+      <c r="A17" s="10">
         <v>201</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="10">
         <v>2</v>
       </c>
-      <c r="C17" s="9">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="9">
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="10">
         <v>1600</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:5">
-      <c r="A18" s="9">
+      <c r="F17" s="8">
+        <v>50000</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" ref="G17:G40" si="2">E17/SUMIF(B:B,B17,E:E)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:8">
+      <c r="A18" s="10">
         <v>202</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="10">
         <v>2</v>
       </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="10">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F18" s="8">
+        <v>60000</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:8">
+      <c r="A19" s="10">
+        <v>203</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2</v>
+      </c>
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1300</v>
+      </c>
+      <c r="F19" s="8">
+        <v>80000</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="2"/>
+        <v>0.13</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="1"/>
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:8">
+      <c r="A20" s="10">
+        <v>204</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="9">
+        <v>100000</v>
+      </c>
+      <c r="G20" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:8">
+      <c r="A21" s="10">
+        <v>205</v>
+      </c>
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="10">
+        <v>900</v>
+      </c>
+      <c r="F21" s="9">
+        <v>160000</v>
+      </c>
+      <c r="G21" s="1">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="1"/>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:8">
+      <c r="A22" s="10">
+        <v>206</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10">
+        <v>1</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="9">
+        <v>80000</v>
+      </c>
+      <c r="G22" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:8">
+      <c r="A23" s="10">
+        <v>207</v>
+      </c>
+      <c r="B23" s="10">
+        <v>2</v>
+      </c>
+      <c r="C23" s="10">
+        <v>1</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1200</v>
+      </c>
+      <c r="F23" s="9">
+        <v>200000</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="1:8">
+      <c r="A24" s="10">
+        <v>208</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="10">
+        <v>300</v>
+      </c>
+      <c r="F24" s="9">
+        <v>400000</v>
+      </c>
+      <c r="G24" s="1">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:8">
+      <c r="A25" s="10">
+        <v>209</v>
+      </c>
+      <c r="B25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="10">
+        <v>1</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="10">
+        <v>600</v>
+      </c>
+      <c r="F25" s="9">
+        <v>240000</v>
+      </c>
+      <c r="G25" s="1">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="1"/>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:8">
+      <c r="A26" s="10">
+        <v>210</v>
+      </c>
+      <c r="B26" s="10">
+        <v>2</v>
+      </c>
+      <c r="C26" s="10">
+        <v>1</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="10">
+        <v>800</v>
+      </c>
+      <c r="F26" s="9">
+        <v>180000</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:8">
+      <c r="A27" s="10">
+        <v>211</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2</v>
+      </c>
+      <c r="C27" s="10">
+        <v>1</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E27" s="10">
+        <v>200</v>
+      </c>
+      <c r="F27" s="9">
+        <v>800000</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="2"/>
+        <v>0.02</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="1"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:8">
+      <c r="A28" s="10">
+        <v>212</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2</v>
+      </c>
+      <c r="C28" s="10">
+        <v>1</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="10">
+        <v>100</v>
+      </c>
+      <c r="F28" s="9">
+        <v>1600000</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="2"/>
+        <v>0.01</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="1"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="11">
+        <v>301</v>
+      </c>
+      <c r="B29" s="11">
+        <v>3</v>
+      </c>
+      <c r="C29" s="11">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="11">
+        <v>1600</v>
+      </c>
+      <c r="F29" s="12">
+        <v>100000</v>
+      </c>
+      <c r="G29" s="1">
+        <f t="shared" si="2"/>
+        <v>0.16</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="1"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="11">
+        <v>302</v>
+      </c>
+      <c r="B30" s="11">
+        <v>3</v>
+      </c>
+      <c r="C30" s="11">
+        <v>1</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="11">
         <v>1000</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:5">
-      <c r="A19" s="9">
-        <v>203</v>
-      </c>
-      <c r="B19" s="9">
-        <v>2</v>
-      </c>
-      <c r="C19" s="9">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="F30" s="12">
+        <v>300000</v>
+      </c>
+      <c r="G30" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="1"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="11">
+        <v>303</v>
+      </c>
+      <c r="B31" s="11">
+        <v>3</v>
+      </c>
+      <c r="C31" s="11">
+        <v>1</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="11">
         <v>1300</v>
       </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:7">
-      <c r="A20" s="9">
-        <v>204</v>
-      </c>
-      <c r="B20" s="9">
-        <v>2</v>
-      </c>
-      <c r="C20" s="9">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="F31" s="12">
+        <v>200000</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="2"/>
+        <v>0.13</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="1"/>
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="11">
+        <v>304</v>
+      </c>
+      <c r="B32" s="11">
+        <v>3</v>
+      </c>
+      <c r="C32" s="11">
+        <v>1</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="11">
         <v>1000</v>
       </c>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:7">
-      <c r="A21" s="9">
-        <v>205</v>
-      </c>
-      <c r="B21" s="9">
-        <v>2</v>
-      </c>
-      <c r="C21" s="9">
-        <v>1</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="F32" s="12">
+        <v>500000</v>
+      </c>
+      <c r="G32" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H32" s="1">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="11">
+        <v>305</v>
+      </c>
+      <c r="B33" s="11">
+        <v>3</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="11">
         <v>900</v>
       </c>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:7">
-      <c r="A22" s="9">
-        <v>206</v>
-      </c>
-      <c r="B22" s="9">
-        <v>2</v>
-      </c>
-      <c r="C22" s="9">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="9">
+      <c r="F33" s="12">
+        <v>800000</v>
+      </c>
+      <c r="G33" s="1">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
+      </c>
+      <c r="H33" s="1">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="11">
+        <v>306</v>
+      </c>
+      <c r="B34" s="11">
+        <v>3</v>
+      </c>
+      <c r="C34" s="11">
+        <v>1</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="11">
         <v>1000</v>
       </c>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:7">
-      <c r="A23" s="9">
-        <v>207</v>
-      </c>
-      <c r="B23" s="9">
-        <v>2</v>
-      </c>
-      <c r="C23" s="9">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="9">
+      <c r="F34" s="12">
+        <v>400000</v>
+      </c>
+      <c r="G34" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="H34" s="1">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="11">
+        <v>307</v>
+      </c>
+      <c r="B35" s="11">
+        <v>3</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="11">
         <v>1200</v>
       </c>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:7">
-      <c r="A24" s="9">
-        <v>208</v>
-      </c>
-      <c r="B24" s="9">
-        <v>2</v>
-      </c>
-      <c r="C24" s="9">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="9">
+      <c r="F35" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="G35" s="1">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="H35" s="1">
+        <f t="shared" si="1"/>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="11">
+        <v>308</v>
+      </c>
+      <c r="B36" s="11">
+        <v>3</v>
+      </c>
+      <c r="C36" s="11">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="11">
         <v>300</v>
       </c>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:7">
-      <c r="A25" s="9">
-        <v>209</v>
-      </c>
-      <c r="B25" s="9">
-        <v>2</v>
-      </c>
-      <c r="C25" s="9">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="9">
+      <c r="F36" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="G36" s="1">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="11">
+        <v>309</v>
+      </c>
+      <c r="B37" s="11">
+        <v>3</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="11">
         <v>600</v>
       </c>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:7">
-      <c r="A26" s="9">
-        <v>210</v>
-      </c>
-      <c r="B26" s="9">
-        <v>2</v>
-      </c>
-      <c r="C26" s="9">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="9">
+      <c r="F37" s="12">
+        <v>1200000</v>
+      </c>
+      <c r="G37" s="1">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="11">
+        <v>310</v>
+      </c>
+      <c r="B38" s="11">
+        <v>3</v>
+      </c>
+      <c r="C38" s="11">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="11">
         <v>800</v>
       </c>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:7">
-      <c r="A27" s="9">
-        <v>211</v>
-      </c>
-      <c r="B27" s="9">
-        <v>2</v>
-      </c>
-      <c r="C27" s="9">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="9">
+      <c r="F38" s="12">
+        <v>900000</v>
+      </c>
+      <c r="G38" s="1">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+      <c r="H38" s="1">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="11">
+        <v>311</v>
+      </c>
+      <c r="B39" s="11">
+        <v>3</v>
+      </c>
+      <c r="C39" s="11">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="11">
         <v>200</v>
       </c>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:7">
-      <c r="A28" s="9">
-        <v>212</v>
-      </c>
-      <c r="B28" s="9">
-        <v>2</v>
-      </c>
-      <c r="C28" s="9">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="9">
+      <c r="F39" s="12">
+        <v>4000000</v>
+      </c>
+      <c r="G39" s="1">
+        <f t="shared" si="2"/>
+        <v>0.02</v>
+      </c>
+      <c r="H39" s="1">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="11">
+        <v>312</v>
+      </c>
+      <c r="B40" s="11">
+        <v>3</v>
+      </c>
+      <c r="C40" s="11">
+        <v>1</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="11">
         <v>100</v>
       </c>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="10">
-        <v>301</v>
-      </c>
-      <c r="B29" s="10">
-        <v>3</v>
-      </c>
-      <c r="C29" s="10">
-        <v>1</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="10">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="10">
-        <v>302</v>
-      </c>
-      <c r="B30" s="10">
-        <v>3</v>
-      </c>
-      <c r="C30" s="10">
-        <v>1</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="10">
-        <v>303</v>
-      </c>
-      <c r="B31" s="10">
-        <v>3</v>
-      </c>
-      <c r="C31" s="10">
-        <v>1</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="10">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="10">
-        <v>304</v>
-      </c>
-      <c r="B32" s="10">
-        <v>3</v>
-      </c>
-      <c r="C32" s="10">
-        <v>1</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="10">
-        <v>305</v>
-      </c>
-      <c r="B33" s="10">
-        <v>3</v>
-      </c>
-      <c r="C33" s="10">
-        <v>1</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="10">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="10">
-        <v>306</v>
-      </c>
-      <c r="B34" s="10">
-        <v>3</v>
-      </c>
-      <c r="C34" s="10">
-        <v>1</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="10">
-        <v>307</v>
-      </c>
-      <c r="B35" s="10">
-        <v>3</v>
-      </c>
-      <c r="C35" s="10">
-        <v>1</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="10">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="10">
-        <v>308</v>
-      </c>
-      <c r="B36" s="10">
-        <v>3</v>
-      </c>
-      <c r="C36" s="10">
-        <v>1</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="10">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="10">
-        <v>309</v>
-      </c>
-      <c r="B37" s="10">
-        <v>3</v>
-      </c>
-      <c r="C37" s="10">
-        <v>1</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="10">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="10">
-        <v>310</v>
-      </c>
-      <c r="B38" s="10">
-        <v>3</v>
-      </c>
-      <c r="C38" s="10">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="10">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="10">
-        <v>311</v>
-      </c>
-      <c r="B39" s="10">
-        <v>3</v>
-      </c>
-      <c r="C39" s="10">
-        <v>1</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="10">
-        <v>312</v>
-      </c>
-      <c r="B40" s="10">
-        <v>3</v>
-      </c>
-      <c r="C40" s="10">
-        <v>1</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="10">
-        <v>100</v>
+      <c r="F40" s="12">
+        <v>8000000</v>
+      </c>
+      <c r="G40" s="1">
+        <f t="shared" si="2"/>
+        <v>0.01</v>
+      </c>
+      <c r="H40" s="1">
+        <f t="shared" si="1"/>
+        <v>80000</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08275E8C-2627-4CAC-9C1A-93CD409E1612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OfficialAwards" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -106,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>序列ID</t>
   </si>
@@ -220,19 +226,17 @@
   </si>
   <si>
     <t>1990000_8000000</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,150 +262,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -412,8 +272,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,216 +295,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.9"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -639,262 +332,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -906,16 +354,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -924,65 +366,21 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1260,98 +658,100 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="7" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="7">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
         <v>101</v>
       </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>1600</v>
       </c>
       <c r="F5" s="1">
@@ -1366,23 +766,23 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="7">
+    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
         <v>102</v>
       </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>1000</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="1">
         <v>30000</v>
       </c>
       <c r="G6" s="1">
@@ -1394,23 +794,23 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="7">
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
         <v>103</v>
       </c>
-      <c r="B7" s="7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>1300</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="1">
         <v>20000</v>
       </c>
       <c r="G7" s="1">
@@ -1422,23 +822,23 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:8">
-      <c r="A8" s="7">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>104</v>
       </c>
-      <c r="B8" s="7">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>1000</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="2">
         <v>50000</v>
       </c>
       <c r="G8" s="1">
@@ -1450,23 +850,23 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:8">
-      <c r="A9" s="7">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
         <v>105</v>
       </c>
-      <c r="B9" s="7">
-        <v>1</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>900</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="2">
         <v>80000</v>
       </c>
       <c r="G9" s="1">
@@ -1478,23 +878,23 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:8">
-      <c r="A10" s="7">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
         <v>106</v>
       </c>
-      <c r="B10" s="7">
-        <v>1</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>1000</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="2">
         <v>40000</v>
       </c>
       <c r="G10" s="1">
@@ -1506,23 +906,23 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:8">
-      <c r="A11" s="7">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <v>107</v>
       </c>
-      <c r="B11" s="7">
-        <v>1</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>1200</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="2">
         <v>100000</v>
       </c>
       <c r="G11" s="1">
@@ -1534,23 +934,23 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
-      <c r="A12" s="7">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
         <v>108</v>
       </c>
-      <c r="B12" s="7">
-        <v>1</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>300</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="2">
         <v>200000</v>
       </c>
       <c r="G12" s="1">
@@ -1562,23 +962,23 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:8">
-      <c r="A13" s="7">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>109</v>
       </c>
-      <c r="B13" s="7">
-        <v>1</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>600</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="2">
         <v>120000</v>
       </c>
       <c r="G13" s="1">
@@ -1590,23 +990,23 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:8">
-      <c r="A14" s="7">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>110</v>
       </c>
-      <c r="B14" s="7">
-        <v>1</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>800</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="2">
         <v>90000</v>
       </c>
       <c r="G14" s="1">
@@ -1618,23 +1018,23 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:8">
-      <c r="A15" s="7">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>111</v>
       </c>
-      <c r="B15" s="7">
-        <v>1</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="B15" s="6">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>200</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="2">
         <v>400000</v>
       </c>
       <c r="G15" s="1">
@@ -1646,23 +1046,23 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:8">
-      <c r="A16" s="7">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>112</v>
       </c>
-      <c r="B16" s="7">
-        <v>1</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <v>100</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="2">
         <v>800000</v>
       </c>
       <c r="G16" s="1">
@@ -1674,23 +1074,23 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
-      <c r="A17" s="10">
+    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
         <v>201</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>2</v>
       </c>
-      <c r="C17" s="10">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="7">
         <v>1600</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="1">
         <v>50000</v>
       </c>
       <c r="G17" s="1">
@@ -1702,23 +1102,23 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
-      <c r="A18" s="10">
+    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
         <v>202</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>2</v>
       </c>
-      <c r="C18" s="10">
-        <v>1</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="7">
         <v>1000</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="1">
         <v>60000</v>
       </c>
       <c r="G18" s="1">
@@ -1730,23 +1130,23 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
-      <c r="A19" s="10">
+    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
         <v>203</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>2</v>
       </c>
-      <c r="C19" s="10">
-        <v>1</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="7">
         <v>1300</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="1">
         <v>80000</v>
       </c>
       <c r="G19" s="1">
@@ -1758,23 +1158,23 @@
         <v>10400</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:8">
-      <c r="A20" s="10">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <v>204</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>2</v>
       </c>
-      <c r="C20" s="10">
-        <v>1</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="7">
         <v>1000</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="2">
         <v>100000</v>
       </c>
       <c r="G20" s="1">
@@ -1786,23 +1186,23 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:8">
-      <c r="A21" s="10">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
         <v>205</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>2</v>
       </c>
-      <c r="C21" s="10">
-        <v>1</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="7">
         <v>900</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="2">
         <v>160000</v>
       </c>
       <c r="G21" s="1">
@@ -1814,23 +1214,23 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:8">
-      <c r="A22" s="10">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
         <v>206</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>2</v>
       </c>
-      <c r="C22" s="10">
-        <v>1</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="7">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="7">
         <v>1000</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="2">
         <v>80000</v>
       </c>
       <c r="G22" s="1">
@@ -1842,23 +1242,23 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:8">
-      <c r="A23" s="10">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
         <v>207</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>2</v>
       </c>
-      <c r="C23" s="10">
-        <v>1</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="7">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="7">
         <v>1200</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="2">
         <v>200000</v>
       </c>
       <c r="G23" s="1">
@@ -1870,23 +1270,23 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:8">
-      <c r="A24" s="10">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
         <v>208</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>2</v>
       </c>
-      <c r="C24" s="10">
-        <v>1</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="7">
         <v>300</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="2">
         <v>400000</v>
       </c>
       <c r="G24" s="1">
@@ -1898,23 +1298,23 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:8">
-      <c r="A25" s="10">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
         <v>209</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>2</v>
       </c>
-      <c r="C25" s="10">
-        <v>1</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="7">
         <v>600</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="2">
         <v>240000</v>
       </c>
       <c r="G25" s="1">
@@ -1926,23 +1326,23 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:8">
-      <c r="A26" s="10">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
         <v>210</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="7">
         <v>2</v>
       </c>
-      <c r="C26" s="10">
-        <v>1</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="7">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="7">
         <v>800</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="2">
         <v>180000</v>
       </c>
       <c r="G26" s="1">
@@ -1954,23 +1354,23 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:8">
-      <c r="A27" s="10">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="7">
         <v>211</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="7">
         <v>2</v>
       </c>
-      <c r="C27" s="10">
-        <v>1</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="C27" s="7">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="7">
         <v>200</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="2">
         <v>800000</v>
       </c>
       <c r="G27" s="1">
@@ -1982,23 +1382,23 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:8">
-      <c r="A28" s="10">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="7">
         <v>212</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="7">
         <v>2</v>
       </c>
-      <c r="C28" s="10">
-        <v>1</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="C28" s="7">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="7">
         <v>100</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="2">
         <v>1600000</v>
       </c>
       <c r="G28" s="1">
@@ -2010,23 +1410,23 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="11">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
         <v>301</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="8">
         <v>3</v>
       </c>
-      <c r="C29" s="11">
-        <v>1</v>
-      </c>
-      <c r="D29" s="11" t="s">
+      <c r="C29" s="8">
+        <v>1</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <v>1600</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="2">
         <v>100000</v>
       </c>
       <c r="G29" s="1">
@@ -2038,23 +1438,23 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="11">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
         <v>302</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="8">
         <v>3</v>
       </c>
-      <c r="C30" s="11">
-        <v>1</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="C30" s="8">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="8">
         <v>1000</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="2">
         <v>300000</v>
       </c>
       <c r="G30" s="1">
@@ -2066,23 +1466,23 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="11">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
         <v>303</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="8">
         <v>3</v>
       </c>
-      <c r="C31" s="11">
-        <v>1</v>
-      </c>
-      <c r="D31" s="11" t="s">
+      <c r="C31" s="8">
+        <v>1</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="8">
         <v>1300</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="2">
         <v>200000</v>
       </c>
       <c r="G31" s="1">
@@ -2094,23 +1494,23 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="11">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
         <v>304</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="8">
         <v>3</v>
       </c>
-      <c r="C32" s="11">
-        <v>1</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="8">
         <v>1000</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="2">
         <v>500000</v>
       </c>
       <c r="G32" s="1">
@@ -2122,23 +1522,23 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="11">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>305</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="8">
         <v>3</v>
       </c>
-      <c r="C33" s="11">
-        <v>1</v>
-      </c>
-      <c r="D33" s="11" t="s">
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="8">
         <v>900</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="2">
         <v>800000</v>
       </c>
       <c r="G33" s="1">
@@ -2150,23 +1550,23 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="11">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
         <v>306</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="8">
         <v>3</v>
       </c>
-      <c r="C34" s="11">
-        <v>1</v>
-      </c>
-      <c r="D34" s="11" t="s">
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="8">
         <v>1000</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="2">
         <v>400000</v>
       </c>
       <c r="G34" s="1">
@@ -2178,23 +1578,23 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="11">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
         <v>307</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="8">
         <v>3</v>
       </c>
-      <c r="C35" s="11">
-        <v>1</v>
-      </c>
-      <c r="D35" s="11" t="s">
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="8">
         <v>1200</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="2">
         <v>1000000</v>
       </c>
       <c r="G35" s="1">
@@ -2206,23 +1606,23 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="11">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
         <v>308</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="8">
         <v>3</v>
       </c>
-      <c r="C36" s="11">
-        <v>1</v>
-      </c>
-      <c r="D36" s="11" t="s">
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="8">
         <v>300</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="2">
         <v>2000000</v>
       </c>
       <c r="G36" s="1">
@@ -2234,23 +1634,23 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="11">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
         <v>309</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="8">
         <v>3</v>
       </c>
-      <c r="C37" s="11">
-        <v>1</v>
-      </c>
-      <c r="D37" s="11" t="s">
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="8">
         <v>600</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="2">
         <v>1200000</v>
       </c>
       <c r="G37" s="1">
@@ -2262,23 +1662,23 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="11">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
         <v>310</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="8">
         <v>3</v>
       </c>
-      <c r="C38" s="11">
-        <v>1</v>
-      </c>
-      <c r="D38" s="11" t="s">
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="8">
         <v>800</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="2">
         <v>900000</v>
       </c>
       <c r="G38" s="1">
@@ -2290,23 +1690,23 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="11">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
         <v>311</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="8">
         <v>3</v>
       </c>
-      <c r="C39" s="11">
-        <v>1</v>
-      </c>
-      <c r="D39" s="11" t="s">
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="8">
         <v>200</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="2">
         <v>4000000</v>
       </c>
       <c r="G39" s="1">
@@ -2318,23 +1718,23 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="11">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
         <v>312</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="8">
         <v>3</v>
       </c>
-      <c r="C40" s="11">
-        <v>1</v>
-      </c>
-      <c r="D40" s="11" t="s">
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="8">
         <v>100</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="2">
         <v>8000000</v>
       </c>
       <c r="G40" s="1">
@@ -2347,8 +1747,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08275E8C-2627-4CAC-9C1A-93CD409E1612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="OfficialAwards" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="48">
   <si>
     <t>序列ID</t>
   </si>
@@ -126,6 +120,9 @@
     <t>奖励</t>
   </si>
   <si>
+    <t>奖励显示图标</t>
+  </si>
+  <si>
     <t>中奖概率(万分比)</t>
   </si>
   <si>
@@ -138,6 +135,9 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -150,15 +150,24 @@
     <t>getitem</t>
   </si>
   <si>
+    <t>showicon</t>
+  </si>
+  <si>
     <t>probability</t>
   </si>
   <si>
     <t>1990000_10000</t>
   </si>
   <si>
+    <t>gfpj_props_1.png</t>
+  </si>
+  <si>
     <t>1990000_30000</t>
   </si>
   <si>
+    <t>gfpj_props_3.png</t>
+  </si>
+  <si>
     <t>1990000_20000</t>
   </si>
   <si>
@@ -168,24 +177,39 @@
     <t>1990000_80000</t>
   </si>
   <si>
+    <t>gfpj_props_5.png</t>
+  </si>
+  <si>
     <t>1990000_40000</t>
   </si>
   <si>
     <t>1990000_100000</t>
   </si>
   <si>
+    <t>gfpj_props_2.png</t>
+  </si>
+  <si>
     <t>1990000_200000</t>
   </si>
   <si>
+    <t>gfpj_props_4.png</t>
+  </si>
+  <si>
     <t>1990000_120000</t>
   </si>
   <si>
+    <t>gfpj_props_6.png</t>
+  </si>
+  <si>
     <t>1990000_90000</t>
   </si>
   <si>
     <t>1990000_400000</t>
   </si>
   <si>
+    <t>gfpj_props_7.png</t>
+  </si>
+  <si>
     <t>1990000_800000</t>
   </si>
   <si>
@@ -226,17 +250,19 @@
   </si>
   <si>
     <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +288,150 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -272,21 +442,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -295,36 +452,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -332,17 +669,262 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -354,33 +936,86 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -658,1097 +1293,1216 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="7" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F2" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:9">
+      <c r="A5" s="8">
         <v>101</v>
       </c>
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="8">
         <v>1600</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>10000</v>
       </c>
-      <c r="G5" s="1">
-        <f>E5/SUMIF(B:B,B5,E:E)</f>
+      <c r="H5" s="1">
+        <f>F5/SUMIF(B:B,B5,F:F)</f>
         <v>0.16</v>
       </c>
-      <c r="H5" s="1">
-        <f>G5*F5</f>
+      <c r="I5" s="1">
+        <f>H5*G5</f>
         <v>1600</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" s="1" customFormat="1" spans="1:9">
+      <c r="A6" s="8">
         <v>102</v>
       </c>
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="8">
         <v>1000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="9">
         <v>30000</v>
       </c>
-      <c r="G6" s="1">
-        <f t="shared" ref="G6:G16" si="0">E6/SUMIF(B:B,B6,E:E)</f>
+      <c r="H6" s="1">
+        <f t="shared" ref="H6:H16" si="0">F6/SUMIF(B:B,B6,F:F)</f>
         <v>0.1</v>
       </c>
-      <c r="H6" s="1">
-        <f t="shared" ref="H6:H40" si="1">G6*F6</f>
+      <c r="I6" s="1">
+        <f t="shared" ref="I6:I40" si="1">H6*G6</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" s="1" customFormat="1" spans="1:9">
+      <c r="A7" s="8">
         <v>103</v>
       </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="8">
         <v>1300</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="9">
         <v>20000</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <f t="shared" si="1"/>
         <v>2600</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" s="2" customFormat="1" spans="1:9">
+      <c r="A8" s="8">
         <v>104</v>
       </c>
-      <c r="B8" s="6">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="8">
         <v>1000</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="10">
         <v>50000</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" s="2" customFormat="1" spans="1:9">
+      <c r="A9" s="8">
         <v>105</v>
       </c>
-      <c r="B9" s="6">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="8">
         <v>900</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="10">
         <v>80000</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" s="2" customFormat="1" spans="1:9">
+      <c r="A10" s="8">
         <v>106</v>
       </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="8">
         <v>1000</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="10">
         <v>40000</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" s="2" customFormat="1" spans="1:9">
+      <c r="A11" s="8">
         <v>107</v>
       </c>
-      <c r="B11" s="6">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="B11" s="8">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="8">
         <v>1200</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="10">
         <v>100000</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
+    <row r="12" s="2" customFormat="1" spans="1:9">
+      <c r="A12" s="8">
         <v>108</v>
       </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="B12" s="8">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="8">
         <v>300</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="10">
         <v>200000</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
+    <row r="13" s="2" customFormat="1" spans="1:9">
+      <c r="A13" s="8">
         <v>109</v>
       </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="8">
         <v>600</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="10">
         <v>120000</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
+    <row r="14" s="2" customFormat="1" spans="1:9">
+      <c r="A14" s="8">
         <v>110</v>
       </c>
-      <c r="B14" s="6">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="8">
         <v>800</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="10">
         <v>90000</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
+    <row r="15" s="2" customFormat="1" spans="1:9">
+      <c r="A15" s="8">
         <v>111</v>
       </c>
-      <c r="B15" s="6">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="8">
         <v>200</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="10">
         <v>400000</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
+    <row r="16" s="2" customFormat="1" spans="1:9">
+      <c r="A16" s="8">
         <v>112</v>
       </c>
-      <c r="B16" s="6">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="8">
         <v>100</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="10">
         <v>800000</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7">
+    <row r="17" s="1" customFormat="1" spans="1:9">
+      <c r="A17" s="11">
         <v>201</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="11">
         <v>2</v>
       </c>
-      <c r="C17" s="7">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="7">
+      <c r="C17" s="11">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="11">
         <v>1600</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="9">
         <v>50000</v>
       </c>
-      <c r="G17" s="1">
-        <f t="shared" ref="G17:G40" si="2">E17/SUMIF(B:B,B17,E:E)</f>
+      <c r="H17" s="1">
+        <f t="shared" ref="H17:H40" si="2">F17/SUMIF(B:B,B17,F:F)</f>
         <v>0.16</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7">
+    <row r="18" s="1" customFormat="1" spans="1:9">
+      <c r="A18" s="11">
         <v>202</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="11">
         <v>2</v>
       </c>
-      <c r="C18" s="7">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="7">
+      <c r="C18" s="11">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="11">
         <v>1000</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="9">
         <v>60000</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7">
+    <row r="19" s="1" customFormat="1" spans="1:9">
+      <c r="A19" s="11">
         <v>203</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="11">
         <v>2</v>
       </c>
-      <c r="C19" s="7">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="7">
+      <c r="F19" s="11">
         <v>1300</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="9">
         <v>80000</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <f t="shared" si="1"/>
         <v>10400</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="7">
+    <row r="20" s="2" customFormat="1" spans="1:9">
+      <c r="A20" s="11">
         <v>204</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="11">
         <v>2</v>
       </c>
-      <c r="C20" s="7">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="7">
+      <c r="F20" s="11">
         <v>1000</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="10">
         <v>100000</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="7">
+    <row r="21" s="2" customFormat="1" spans="1:9">
+      <c r="A21" s="11">
         <v>205</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="11">
         <v>2</v>
       </c>
-      <c r="C21" s="7">
-        <v>1</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="7">
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="11">
         <v>900</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="10">
         <v>160000</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <f t="shared" si="2"/>
         <v>0.09</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="7">
+    <row r="22" s="2" customFormat="1" spans="1:9">
+      <c r="A22" s="11">
         <v>206</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="11">
         <v>2</v>
       </c>
-      <c r="C22" s="7">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="7">
+      <c r="C22" s="11">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="11">
         <v>1000</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="10">
         <v>80000</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
+    <row r="23" s="2" customFormat="1" spans="1:9">
+      <c r="A23" s="11">
         <v>207</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="11">
         <v>2</v>
       </c>
-      <c r="C23" s="7">
-        <v>1</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="7">
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="11">
         <v>1200</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="10">
         <v>200000</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <f t="shared" si="1"/>
         <v>24000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="7">
+    <row r="24" s="2" customFormat="1" spans="1:9">
+      <c r="A24" s="11">
         <v>208</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="11">
         <v>2</v>
       </c>
-      <c r="C24" s="7">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="7">
+      <c r="C24" s="11">
+        <v>1</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="11">
         <v>300</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="10">
         <v>400000</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="7">
+    <row r="25" s="2" customFormat="1" spans="1:9">
+      <c r="A25" s="11">
         <v>209</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="11">
         <v>2</v>
       </c>
-      <c r="C25" s="7">
-        <v>1</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="7">
+      <c r="C25" s="11">
+        <v>1</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="11">
         <v>600</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="10">
         <v>240000</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="7">
+    <row r="26" s="2" customFormat="1" spans="1:9">
+      <c r="A26" s="11">
         <v>210</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="11">
         <v>2</v>
       </c>
-      <c r="C26" s="7">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="7">
+      <c r="C26" s="11">
+        <v>1</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="11">
         <v>800</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="10">
         <v>180000</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="7">
+    <row r="27" s="2" customFormat="1" spans="1:9">
+      <c r="A27" s="11">
         <v>211</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="11">
         <v>2</v>
       </c>
-      <c r="C27" s="7">
-        <v>1</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="7">
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="11">
         <v>200</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="10">
         <v>800000</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="7">
+    <row r="28" s="2" customFormat="1" spans="1:9">
+      <c r="A28" s="11">
         <v>212</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="11">
         <v>2</v>
       </c>
-      <c r="C28" s="7">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="7">
+      <c r="C28" s="11">
+        <v>1</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="11">
         <v>100</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="10">
         <v>1600000</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
+    <row r="29" spans="1:9">
+      <c r="A29" s="12">
         <v>301</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="12">
         <v>3</v>
       </c>
-      <c r="C29" s="8">
-        <v>1</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="8">
+      <c r="C29" s="12">
+        <v>1</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="12">
         <v>1600</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="13">
         <v>100000</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
+    <row r="30" spans="1:9">
+      <c r="A30" s="12">
         <v>302</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="12">
         <v>3</v>
       </c>
-      <c r="C30" s="8">
-        <v>1</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="8">
+      <c r="C30" s="12">
+        <v>1</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="12">
         <v>1000</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="13">
         <v>300000</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
+    <row r="31" spans="1:9">
+      <c r="A31" s="12">
         <v>303</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="12">
         <v>3</v>
       </c>
-      <c r="C31" s="8">
-        <v>1</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="C31" s="12">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="12">
         <v>1300</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="13">
         <v>200000</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <f t="shared" si="1"/>
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
+    <row r="32" spans="1:9">
+      <c r="A32" s="12">
         <v>304</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="12">
         <v>3</v>
       </c>
-      <c r="C32" s="8">
-        <v>1</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="8">
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="12">
         <v>1000</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="13">
         <v>500000</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
+    <row r="33" spans="1:9">
+      <c r="A33" s="12">
         <v>305</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="12">
         <v>3</v>
       </c>
-      <c r="C33" s="8">
-        <v>1</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8">
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="12">
         <v>900</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="13">
         <v>800000</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <f t="shared" si="2"/>
         <v>0.09</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="8">
+    <row r="34" spans="1:9">
+      <c r="A34" s="12">
         <v>306</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="12">
         <v>3</v>
       </c>
-      <c r="C34" s="8">
-        <v>1</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="8">
+      <c r="C34" s="12">
+        <v>1</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="13">
         <v>400000</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
+    <row r="35" spans="1:9">
+      <c r="A35" s="12">
         <v>307</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="12">
         <v>3</v>
       </c>
-      <c r="C35" s="8">
-        <v>1</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="8">
+      <c r="C35" s="12">
+        <v>1</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="12">
         <v>1200</v>
       </c>
-      <c r="F35" s="2">
+      <c r="G35" s="13">
         <v>1000000</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
+    <row r="36" spans="1:9">
+      <c r="A36" s="12">
         <v>308</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="12">
         <v>3</v>
       </c>
-      <c r="C36" s="8">
-        <v>1</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="8">
+      <c r="C36" s="12">
+        <v>1</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="12">
         <v>300</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G36" s="13">
         <v>2000000</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
+    <row r="37" spans="1:9">
+      <c r="A37" s="12">
         <v>309</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="12">
         <v>3</v>
       </c>
-      <c r="C37" s="8">
-        <v>1</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="8">
+      <c r="C37" s="12">
+        <v>1</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="12">
         <v>600</v>
       </c>
-      <c r="F37" s="2">
+      <c r="G37" s="13">
         <v>1200000</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
+    <row r="38" spans="1:9">
+      <c r="A38" s="12">
         <v>310</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="12">
         <v>3</v>
       </c>
-      <c r="C38" s="8">
-        <v>1</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="8">
+      <c r="C38" s="12">
+        <v>1</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="12">
         <v>800</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="13">
         <v>900000</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
+    <row r="39" spans="1:9">
+      <c r="A39" s="12">
         <v>311</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="12">
         <v>3</v>
       </c>
-      <c r="C39" s="8">
-        <v>1</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="8">
+      <c r="C39" s="12">
+        <v>1</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="12">
         <v>200</v>
       </c>
-      <c r="F39" s="2">
+      <c r="G39" s="13">
         <v>4000000</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="8">
+    <row r="40" spans="1:9">
+      <c r="A40" s="12">
         <v>312</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="12">
         <v>3</v>
       </c>
-      <c r="C40" s="8">
-        <v>1</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="8">
+      <c r="C40" s="12">
+        <v>1</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="12">
         <v>100</v>
       </c>
-      <c r="F40" s="2">
+      <c r="G40" s="13">
         <v>8000000</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -74,29 +74,6 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1. 有效下注
-2. 充值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
 仅配置一个道具</t>
         </r>
       </text>
@@ -106,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>序列ID</t>
   </si>
@@ -114,9 +91,6 @@
     <t>转盘类型</t>
   </si>
   <si>
-    <t>统计类型</t>
-  </si>
-  <si>
     <t>奖励</t>
   </si>
   <si>
@@ -142,9 +116,6 @@
   </si>
   <si>
     <t>turntableType</t>
-  </si>
-  <si>
-    <t>calculationType</t>
   </si>
   <si>
     <t>getitem</t>
@@ -1299,21 +1270,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="18.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1326,1176 +1296,1058 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:9">
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="8">
         <v>101</v>
       </c>
       <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="8">
-        <v>1</v>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="8">
+        <v>15</v>
+      </c>
+      <c r="E5" s="8">
         <v>1600</v>
       </c>
+      <c r="F5" s="1">
+        <v>10000</v>
+      </c>
       <c r="G5" s="1">
-        <v>10000</v>
+        <f>E5/SUMIF(B:B,B5,E:E)</f>
+        <v>0.16</v>
       </c>
       <c r="H5" s="1">
-        <f>F5/SUMIF(B:B,B5,F:F)</f>
-        <v>0.16</v>
-      </c>
-      <c r="I5" s="1">
-        <f>H5*G5</f>
+        <f>G5*F5</f>
         <v>1600</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:9">
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="8">
         <v>102</v>
       </c>
       <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="8">
-        <v>1</v>
+      <c r="C6" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="8">
+        <v>17</v>
+      </c>
+      <c r="E6" s="8">
         <v>1000</v>
       </c>
-      <c r="G6" s="9">
+      <c r="F6" s="9">
         <v>30000</v>
       </c>
+      <c r="G6" s="1">
+        <f t="shared" ref="G6:G16" si="0">E6/SUMIF(B:B,B6,E:E)</f>
+        <v>0.1</v>
+      </c>
       <c r="H6" s="1">
-        <f t="shared" ref="H6:H16" si="0">F6/SUMIF(B:B,B6,F:F)</f>
-        <v>0.1</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" ref="I6:I40" si="1">H6*G6</f>
+        <f t="shared" ref="H6:H40" si="1">G6*F6</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:9">
+    <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="8">
         <v>103</v>
       </c>
       <c r="B7" s="8">
         <v>1</v>
       </c>
-      <c r="C7" s="8">
-        <v>1</v>
+      <c r="C7" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="8">
+        <v>15</v>
+      </c>
+      <c r="E7" s="8">
         <v>1300</v>
       </c>
-      <c r="G7" s="9">
+      <c r="F7" s="9">
         <v>20000</v>
       </c>
-      <c r="H7" s="1">
+      <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
-      <c r="I7" s="1">
+      <c r="H7" s="1">
         <f t="shared" si="1"/>
         <v>2600</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:9">
+    <row r="8" s="2" customFormat="1" spans="1:8">
       <c r="A8" s="8">
         <v>104</v>
       </c>
       <c r="B8" s="8">
         <v>1</v>
       </c>
-      <c r="C8" s="8">
-        <v>1</v>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="8">
+        <v>17</v>
+      </c>
+      <c r="E8" s="8">
         <v>1000</v>
       </c>
-      <c r="G8" s="10">
+      <c r="F8" s="10">
         <v>50000</v>
       </c>
-      <c r="H8" s="1">
+      <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="I8" s="1">
+      <c r="H8" s="1">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:9">
+    <row r="9" s="2" customFormat="1" spans="1:8">
       <c r="A9" s="8">
         <v>105</v>
       </c>
       <c r="B9" s="8">
         <v>1</v>
       </c>
-      <c r="C9" s="8">
-        <v>1</v>
+      <c r="C9" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="8">
+        <v>21</v>
+      </c>
+      <c r="E9" s="8">
         <v>900</v>
       </c>
-      <c r="G9" s="10">
+      <c r="F9" s="10">
         <v>80000</v>
       </c>
-      <c r="H9" s="1">
+      <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
-      <c r="I9" s="1">
+      <c r="H9" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:9">
+    <row r="10" s="2" customFormat="1" spans="1:8">
       <c r="A10" s="8">
         <v>106</v>
       </c>
       <c r="B10" s="8">
         <v>1</v>
       </c>
-      <c r="C10" s="8">
-        <v>1</v>
+      <c r="C10" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="8">
+        <v>17</v>
+      </c>
+      <c r="E10" s="8">
         <v>1000</v>
       </c>
-      <c r="G10" s="10">
+      <c r="F10" s="10">
         <v>40000</v>
       </c>
-      <c r="H10" s="1">
+      <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="I10" s="1">
+      <c r="H10" s="1">
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:9">
+    <row r="11" s="2" customFormat="1" spans="1:8">
       <c r="A11" s="8">
         <v>107</v>
       </c>
       <c r="B11" s="8">
         <v>1</v>
       </c>
-      <c r="C11" s="8">
-        <v>1</v>
+      <c r="C11" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="8">
+        <v>24</v>
+      </c>
+      <c r="E11" s="8">
         <v>1200</v>
       </c>
-      <c r="G11" s="10">
+      <c r="F11" s="10">
         <v>100000</v>
       </c>
-      <c r="H11" s="1">
+      <c r="G11" s="1">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="I11" s="1">
+      <c r="H11" s="1">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:9">
+    <row r="12" s="2" customFormat="1" spans="1:8">
       <c r="A12" s="8">
         <v>108</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
       </c>
-      <c r="C12" s="8">
-        <v>1</v>
+      <c r="C12" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="8">
+        <v>26</v>
+      </c>
+      <c r="E12" s="8">
         <v>300</v>
       </c>
-      <c r="G12" s="10">
+      <c r="F12" s="10">
         <v>200000</v>
       </c>
-      <c r="H12" s="1">
+      <c r="G12" s="1">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="I12" s="1">
+      <c r="H12" s="1">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:9">
+    <row r="13" s="2" customFormat="1" spans="1:8">
       <c r="A13" s="8">
         <v>109</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
       </c>
-      <c r="C13" s="8">
-        <v>1</v>
+      <c r="C13" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="8">
+        <v>28</v>
+      </c>
+      <c r="E13" s="8">
         <v>600</v>
       </c>
-      <c r="G13" s="10">
+      <c r="F13" s="10">
         <v>120000</v>
       </c>
-      <c r="H13" s="1">
+      <c r="G13" s="1">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
-      <c r="I13" s="1">
+      <c r="H13" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:9">
+    <row r="14" s="2" customFormat="1" spans="1:8">
       <c r="A14" s="8">
         <v>110</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
       </c>
-      <c r="C14" s="8">
-        <v>1</v>
+      <c r="C14" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="8">
+        <v>21</v>
+      </c>
+      <c r="E14" s="8">
         <v>800</v>
       </c>
-      <c r="G14" s="10">
+      <c r="F14" s="10">
         <v>90000</v>
       </c>
-      <c r="H14" s="1">
+      <c r="G14" s="1">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="I14" s="1">
+      <c r="H14" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:9">
+    <row r="15" s="2" customFormat="1" spans="1:8">
       <c r="A15" s="8">
         <v>111</v>
       </c>
       <c r="B15" s="8">
         <v>1</v>
       </c>
-      <c r="C15" s="8">
-        <v>1</v>
+      <c r="C15" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="8">
+        <v>31</v>
+      </c>
+      <c r="E15" s="8">
         <v>200</v>
       </c>
-      <c r="G15" s="10">
+      <c r="F15" s="10">
         <v>400000</v>
       </c>
-      <c r="H15" s="1">
+      <c r="G15" s="1">
         <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
-      <c r="I15" s="1">
+      <c r="H15" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:9">
+    <row r="16" s="2" customFormat="1" spans="1:8">
       <c r="A16" s="8">
         <v>112</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
       </c>
-      <c r="C16" s="8">
-        <v>1</v>
+      <c r="C16" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="8">
+        <v>31</v>
+      </c>
+      <c r="E16" s="8">
         <v>100</v>
       </c>
-      <c r="G16" s="10">
+      <c r="F16" s="10">
         <v>800000</v>
       </c>
-      <c r="H16" s="1">
+      <c r="G16" s="1">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="I16" s="1">
+      <c r="H16" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:9">
+    <row r="17" s="1" customFormat="1" spans="1:8">
       <c r="A17" s="11">
         <v>201</v>
       </c>
       <c r="B17" s="11">
         <v>2</v>
       </c>
-      <c r="C17" s="11">
-        <v>1</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="11">
+      <c r="C17" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="11">
         <v>1600</v>
       </c>
-      <c r="G17" s="9">
+      <c r="F17" s="9">
         <v>50000</v>
       </c>
+      <c r="G17" s="1">
+        <f t="shared" ref="G17:G40" si="2">E17/SUMIF(B:B,B17,E:E)</f>
+        <v>0.16</v>
+      </c>
       <c r="H17" s="1">
-        <f t="shared" ref="H17:H40" si="2">F17/SUMIF(B:B,B17,F:F)</f>
-        <v>0.16</v>
-      </c>
-      <c r="I17" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:9">
+    <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="11">
         <v>202</v>
       </c>
       <c r="B18" s="11">
         <v>2</v>
       </c>
-      <c r="C18" s="11">
-        <v>1</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="11">
+      <c r="C18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="11">
         <v>1000</v>
       </c>
-      <c r="G18" s="9">
+      <c r="F18" s="9">
         <v>60000</v>
       </c>
-      <c r="H18" s="1">
+      <c r="G18" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I18" s="1">
+      <c r="H18" s="1">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:9">
+    <row r="19" s="1" customFormat="1" spans="1:8">
       <c r="A19" s="11">
         <v>203</v>
       </c>
       <c r="B19" s="11">
         <v>2</v>
       </c>
-      <c r="C19" s="11">
-        <v>1</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="11">
+      <c r="C19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="11">
         <v>1300</v>
       </c>
-      <c r="G19" s="9">
+      <c r="F19" s="9">
         <v>80000</v>
       </c>
-      <c r="H19" s="1">
+      <c r="G19" s="1">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="I19" s="1">
+      <c r="H19" s="1">
         <f t="shared" si="1"/>
         <v>10400</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:9">
+    <row r="20" s="2" customFormat="1" spans="1:8">
       <c r="A20" s="11">
         <v>204</v>
       </c>
       <c r="B20" s="11">
         <v>2</v>
       </c>
-      <c r="C20" s="11">
-        <v>1</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="11">
+      <c r="C20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="11">
         <v>1000</v>
       </c>
-      <c r="G20" s="10">
+      <c r="F20" s="10">
         <v>100000</v>
       </c>
-      <c r="H20" s="1">
+      <c r="G20" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I20" s="1">
+      <c r="H20" s="1">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:9">
+    <row r="21" s="2" customFormat="1" spans="1:8">
       <c r="A21" s="11">
         <v>205</v>
       </c>
       <c r="B21" s="11">
         <v>2</v>
       </c>
-      <c r="C21" s="11">
-        <v>1</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="11">
+      <c r="C21" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="11">
         <v>900</v>
       </c>
-      <c r="G21" s="10">
+      <c r="F21" s="10">
         <v>160000</v>
       </c>
-      <c r="H21" s="1">
+      <c r="G21" s="1">
         <f t="shared" si="2"/>
         <v>0.09</v>
       </c>
-      <c r="I21" s="1">
+      <c r="H21" s="1">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:9">
+    <row r="22" s="2" customFormat="1" spans="1:8">
       <c r="A22" s="11">
         <v>206</v>
       </c>
       <c r="B22" s="11">
         <v>2</v>
       </c>
-      <c r="C22" s="11">
-        <v>1</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="11">
+      <c r="C22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="11">
         <v>1000</v>
       </c>
-      <c r="G22" s="10">
+      <c r="F22" s="10">
         <v>80000</v>
       </c>
-      <c r="H22" s="1">
+      <c r="G22" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I22" s="1">
+      <c r="H22" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:9">
+    <row r="23" s="2" customFormat="1" spans="1:8">
       <c r="A23" s="11">
         <v>207</v>
       </c>
       <c r="B23" s="11">
         <v>2</v>
       </c>
-      <c r="C23" s="11">
-        <v>1</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="11">
+      <c r="C23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="11">
         <v>1200</v>
       </c>
-      <c r="G23" s="10">
+      <c r="F23" s="10">
         <v>200000</v>
       </c>
-      <c r="H23" s="1">
+      <c r="G23" s="1">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="I23" s="1">
+      <c r="H23" s="1">
         <f t="shared" si="1"/>
         <v>24000</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:9">
+    <row r="24" s="2" customFormat="1" spans="1:8">
       <c r="A24" s="11">
         <v>208</v>
       </c>
       <c r="B24" s="11">
         <v>2</v>
       </c>
-      <c r="C24" s="11">
-        <v>1</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="11">
+      <c r="C24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="11">
         <v>300</v>
       </c>
-      <c r="G24" s="10">
+      <c r="F24" s="10">
         <v>400000</v>
       </c>
-      <c r="H24" s="1">
+      <c r="G24" s="1">
         <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
-      <c r="I24" s="1">
+      <c r="H24" s="1">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:9">
+    <row r="25" s="2" customFormat="1" spans="1:8">
       <c r="A25" s="11">
         <v>209</v>
       </c>
       <c r="B25" s="11">
         <v>2</v>
       </c>
-      <c r="C25" s="11">
-        <v>1</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="11">
+      <c r="C25" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="11">
         <v>600</v>
       </c>
-      <c r="G25" s="10">
+      <c r="F25" s="10">
         <v>240000</v>
       </c>
-      <c r="H25" s="1">
+      <c r="G25" s="1">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="I25" s="1">
+      <c r="H25" s="1">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:9">
+    <row r="26" s="2" customFormat="1" spans="1:8">
       <c r="A26" s="11">
         <v>210</v>
       </c>
       <c r="B26" s="11">
         <v>2</v>
       </c>
-      <c r="C26" s="11">
-        <v>1</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="11">
+      <c r="C26" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="11">
         <v>800</v>
       </c>
-      <c r="G26" s="10">
+      <c r="F26" s="10">
         <v>180000</v>
       </c>
-      <c r="H26" s="1">
+      <c r="G26" s="1">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
-      <c r="I26" s="1">
+      <c r="H26" s="1">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:9">
+    <row r="27" s="2" customFormat="1" spans="1:8">
       <c r="A27" s="11">
         <v>211</v>
       </c>
       <c r="B27" s="11">
         <v>2</v>
       </c>
-      <c r="C27" s="11">
-        <v>1</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" s="11">
+      <c r="C27" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="11">
         <v>200</v>
       </c>
-      <c r="G27" s="10">
+      <c r="F27" s="10">
         <v>800000</v>
       </c>
-      <c r="H27" s="1">
+      <c r="G27" s="1">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
-      <c r="I27" s="1">
+      <c r="H27" s="1">
         <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:9">
+    <row r="28" s="2" customFormat="1" spans="1:8">
       <c r="A28" s="11">
         <v>212</v>
       </c>
       <c r="B28" s="11">
         <v>2</v>
       </c>
-      <c r="C28" s="11">
-        <v>1</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="11">
+      <c r="C28" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="11">
         <v>100</v>
       </c>
-      <c r="G28" s="10">
+      <c r="F28" s="10">
         <v>1600000</v>
       </c>
-      <c r="H28" s="1">
+      <c r="G28" s="1">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="I28" s="1">
+      <c r="H28" s="1">
         <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:8">
       <c r="A29" s="12">
         <v>301</v>
       </c>
       <c r="B29" s="12">
         <v>3</v>
       </c>
-      <c r="C29" s="12">
-        <v>1</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="12">
+      <c r="C29" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="12">
         <v>1600</v>
       </c>
-      <c r="G29" s="13">
+      <c r="F29" s="13">
         <v>100000</v>
       </c>
-      <c r="H29" s="1">
+      <c r="G29" s="1">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="I29" s="1">
+      <c r="H29" s="1">
         <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:8">
       <c r="A30" s="12">
         <v>302</v>
       </c>
       <c r="B30" s="12">
         <v>3</v>
       </c>
-      <c r="C30" s="12">
-        <v>1</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="12">
+      <c r="C30" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="12">
         <v>1000</v>
       </c>
-      <c r="G30" s="13">
+      <c r="F30" s="13">
         <v>300000</v>
       </c>
-      <c r="H30" s="1">
+      <c r="G30" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I30" s="1">
+      <c r="H30" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:8">
       <c r="A31" s="12">
         <v>303</v>
       </c>
       <c r="B31" s="12">
         <v>3</v>
       </c>
-      <c r="C31" s="12">
-        <v>1</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="12">
+      <c r="C31" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="12">
         <v>1300</v>
       </c>
-      <c r="G31" s="13">
+      <c r="F31" s="13">
         <v>200000</v>
       </c>
-      <c r="H31" s="1">
+      <c r="G31" s="1">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="I31" s="1">
+      <c r="H31" s="1">
         <f t="shared" si="1"/>
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:8">
       <c r="A32" s="12">
         <v>304</v>
       </c>
       <c r="B32" s="12">
         <v>3</v>
       </c>
-      <c r="C32" s="12">
-        <v>1</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" s="12">
+      <c r="C32" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="12">
         <v>1000</v>
       </c>
-      <c r="G32" s="13">
+      <c r="F32" s="13">
         <v>500000</v>
       </c>
-      <c r="H32" s="1">
+      <c r="G32" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I32" s="1">
+      <c r="H32" s="1">
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:8">
       <c r="A33" s="12">
         <v>305</v>
       </c>
       <c r="B33" s="12">
         <v>3</v>
       </c>
-      <c r="C33" s="12">
-        <v>1</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="12">
+      <c r="C33" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="12">
         <v>900</v>
       </c>
-      <c r="G33" s="13">
+      <c r="F33" s="13">
         <v>800000</v>
       </c>
-      <c r="H33" s="1">
+      <c r="G33" s="1">
         <f t="shared" si="2"/>
         <v>0.09</v>
       </c>
-      <c r="I33" s="1">
+      <c r="H33" s="1">
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:8">
       <c r="A34" s="12">
         <v>306</v>
       </c>
       <c r="B34" s="12">
         <v>3</v>
       </c>
-      <c r="C34" s="12">
-        <v>1</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" s="12">
+      <c r="C34" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="13">
+      <c r="F34" s="13">
         <v>400000</v>
       </c>
-      <c r="H34" s="1">
+      <c r="G34" s="1">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="I34" s="1">
+      <c r="H34" s="1">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:8">
       <c r="A35" s="12">
         <v>307</v>
       </c>
       <c r="B35" s="12">
         <v>3</v>
       </c>
-      <c r="C35" s="12">
-        <v>1</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="12">
+      <c r="C35" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="12">
         <v>1200</v>
       </c>
-      <c r="G35" s="13">
+      <c r="F35" s="13">
         <v>1000000</v>
       </c>
-      <c r="H35" s="1">
+      <c r="G35" s="1">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="I35" s="1">
+      <c r="H35" s="1">
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:8">
       <c r="A36" s="12">
         <v>308</v>
       </c>
       <c r="B36" s="12">
         <v>3</v>
       </c>
-      <c r="C36" s="12">
-        <v>1</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="12">
+      <c r="C36" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="12">
         <v>300</v>
       </c>
-      <c r="G36" s="13">
+      <c r="F36" s="13">
         <v>2000000</v>
       </c>
-      <c r="H36" s="1">
+      <c r="G36" s="1">
         <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
-      <c r="I36" s="1">
+      <c r="H36" s="1">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:8">
       <c r="A37" s="12">
         <v>309</v>
       </c>
       <c r="B37" s="12">
         <v>3</v>
       </c>
-      <c r="C37" s="12">
-        <v>1</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="12">
+      <c r="C37" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="12">
         <v>600</v>
       </c>
-      <c r="G37" s="13">
+      <c r="F37" s="13">
         <v>1200000</v>
       </c>
-      <c r="H37" s="1">
+      <c r="G37" s="1">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="I37" s="1">
+      <c r="H37" s="1">
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:8">
       <c r="A38" s="12">
         <v>310</v>
       </c>
       <c r="B38" s="12">
         <v>3</v>
       </c>
-      <c r="C38" s="12">
-        <v>1</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38" s="12">
+      <c r="C38" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="12">
         <v>800</v>
       </c>
-      <c r="G38" s="13">
+      <c r="F38" s="13">
         <v>900000</v>
       </c>
-      <c r="H38" s="1">
+      <c r="G38" s="1">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
-      <c r="I38" s="1">
+      <c r="H38" s="1">
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:8">
       <c r="A39" s="12">
         <v>311</v>
       </c>
       <c r="B39" s="12">
         <v>3</v>
       </c>
-      <c r="C39" s="12">
-        <v>1</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" s="12">
+      <c r="C39" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="12">
         <v>200</v>
       </c>
-      <c r="G39" s="13">
+      <c r="F39" s="13">
         <v>4000000</v>
       </c>
-      <c r="H39" s="1">
+      <c r="G39" s="1">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
-      <c r="I39" s="1">
+      <c r="H39" s="1">
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:8">
       <c r="A40" s="12">
         <v>312</v>
       </c>
       <c r="B40" s="12">
         <v>3</v>
       </c>
-      <c r="C40" s="12">
-        <v>1</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F40" s="12">
+      <c r="C40" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="12">
         <v>100</v>
       </c>
-      <c r="G40" s="13">
+      <c r="F40" s="13">
         <v>8000000</v>
       </c>
-      <c r="H40" s="1">
+      <c r="G40" s="1">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="I40" s="1">
+      <c r="H40" s="1">
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -50,9 +50,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1. 初级转盘
-2. 中级转盘
-3. 高级转盘</t>
+三个转盘分别配置开始日期，
+读取 ActivityConfig.xlsx 表中的 “time_start” 字段开始日期值</t>
         </r>
       </text>
     </comment>
@@ -88,7 +87,7 @@
     <t>序列ID</t>
   </si>
   <si>
-    <t>转盘类型</t>
+    <t>开始日期</t>
   </si>
   <si>
     <t>奖励</t>
@@ -115,7 +114,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>turntableType</t>
+    <t>starDate</t>
   </si>
   <si>
     <t>getitem</t>
@@ -1685,7 +1684,7 @@
         <v>201</v>
       </c>
       <c r="B17" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>19</v>
@@ -1713,7 +1712,7 @@
         <v>202</v>
       </c>
       <c r="B18" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>33</v>
@@ -1741,7 +1740,7 @@
         <v>203</v>
       </c>
       <c r="B19" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>20</v>
@@ -1769,7 +1768,7 @@
         <v>204</v>
       </c>
       <c r="B20" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>23</v>
@@ -1797,7 +1796,7 @@
         <v>205</v>
       </c>
       <c r="B21" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>34</v>
@@ -1825,7 +1824,7 @@
         <v>206</v>
       </c>
       <c r="B22" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>20</v>
@@ -1853,7 +1852,7 @@
         <v>207</v>
       </c>
       <c r="B23" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>25</v>
@@ -1881,7 +1880,7 @@
         <v>208</v>
       </c>
       <c r="B24" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>30</v>
@@ -1909,7 +1908,7 @@
         <v>209</v>
       </c>
       <c r="B25" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>35</v>
@@ -1937,7 +1936,7 @@
         <v>210</v>
       </c>
       <c r="B26" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>36</v>
@@ -1965,7 +1964,7 @@
         <v>211</v>
       </c>
       <c r="B27" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>32</v>
@@ -1993,7 +1992,7 @@
         <v>212</v>
       </c>
       <c r="B28" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>37</v>
@@ -2021,7 +2020,7 @@
         <v>301</v>
       </c>
       <c r="B29" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>23</v>
@@ -2049,7 +2048,7 @@
         <v>302</v>
       </c>
       <c r="B30" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>38</v>
@@ -2077,7 +2076,7 @@
         <v>303</v>
       </c>
       <c r="B31" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>25</v>
@@ -2105,7 +2104,7 @@
         <v>304</v>
       </c>
       <c r="B32" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>39</v>
@@ -2133,7 +2132,7 @@
         <v>305</v>
       </c>
       <c r="B33" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>32</v>
@@ -2161,7 +2160,7 @@
         <v>306</v>
       </c>
       <c r="B34" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>30</v>
@@ -2189,7 +2188,7 @@
         <v>307</v>
       </c>
       <c r="B35" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>40</v>
@@ -2217,7 +2216,7 @@
         <v>308</v>
       </c>
       <c r="B36" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>41</v>
@@ -2245,7 +2244,7 @@
         <v>309</v>
       </c>
       <c r="B37" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>42</v>
@@ -2273,7 +2272,7 @@
         <v>310</v>
       </c>
       <c r="B38" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>43</v>
@@ -2301,7 +2300,7 @@
         <v>311</v>
       </c>
       <c r="B39" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>44</v>
@@ -2329,7 +2328,7 @@
         <v>312</v>
       </c>
       <c r="B40" s="12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>45</v>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -50,29 +50,6 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-三个转盘分别配置开始日期，
-读取 ActivityConfig.xlsx 表中的 “time_start” 字段开始日期值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
 仅配置一个道具</t>
         </r>
       </text>
@@ -82,14 +59,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
   <si>
     <t>序列ID</t>
   </si>
   <si>
-    <t>开始日期</t>
-  </si>
-  <si>
     <t>奖励</t>
   </si>
   <si>
@@ -112,9 +86,6 @@
   </si>
   <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>starDate</t>
   </si>
   <si>
     <t>getitem</t>
@@ -1269,20 +1240,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="18.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1292,1062 +1262,872 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="8">
         <v>101</v>
       </c>
-      <c r="B5" s="8">
-        <v>1</v>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="8">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8">
         <v>1600</v>
       </c>
+      <c r="E5" s="1">
+        <v>10000</v>
+      </c>
       <c r="F5" s="1">
-        <v>10000</v>
+        <v>0.16</v>
       </c>
       <c r="G5" s="1">
-        <f>E5/SUMIF(B:B,B5,E:E)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H5" s="1">
-        <f>G5*F5</f>
         <v>1600</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="8">
         <v>102</v>
       </c>
-      <c r="B6" s="8">
-        <v>1</v>
+      <c r="B6" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="8">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8">
         <v>1000</v>
       </c>
-      <c r="F6" s="9">
+      <c r="E6" s="9">
         <v>30000</v>
       </c>
+      <c r="F6" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G6" s="1">
-        <f t="shared" ref="G6:G16" si="0">E6/SUMIF(B:B,B6,E:E)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="1">
-        <f t="shared" ref="H6:H40" si="1">G6*F6</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+    <row r="7" s="1" customFormat="1" spans="1:7">
       <c r="A7" s="8">
         <v>103</v>
       </c>
-      <c r="B7" s="8">
-        <v>1</v>
+      <c r="B7" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="8">
+        <v>13</v>
+      </c>
+      <c r="D7" s="8">
         <v>1300</v>
       </c>
-      <c r="F7" s="9">
+      <c r="E7" s="9">
         <v>20000</v>
       </c>
+      <c r="F7" s="1">
+        <v>0.13</v>
+      </c>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>0.13</v>
-      </c>
-      <c r="H7" s="1">
-        <f t="shared" si="1"/>
         <v>2600</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:8">
+    <row r="8" s="2" customFormat="1" spans="1:7">
       <c r="A8" s="8">
         <v>104</v>
       </c>
-      <c r="B8" s="8">
-        <v>1</v>
+      <c r="B8" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="8">
+        <v>15</v>
+      </c>
+      <c r="D8" s="8">
         <v>1000</v>
       </c>
-      <c r="F8" s="10">
+      <c r="E8" s="10">
         <v>50000</v>
       </c>
+      <c r="F8" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" si="1"/>
         <v>5000</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:8">
+    <row r="9" s="2" customFormat="1" spans="1:7">
       <c r="A9" s="8">
         <v>105</v>
       </c>
-      <c r="B9" s="8">
-        <v>1</v>
+      <c r="B9" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="8">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8">
         <v>900</v>
       </c>
-      <c r="F9" s="10">
+      <c r="E9" s="10">
         <v>80000</v>
       </c>
+      <c r="F9" s="1">
+        <v>0.09</v>
+      </c>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>0.09</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:8">
+    <row r="10" s="2" customFormat="1" spans="1:7">
       <c r="A10" s="8">
         <v>106</v>
       </c>
-      <c r="B10" s="8">
-        <v>1</v>
+      <c r="B10" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="8">
+        <v>15</v>
+      </c>
+      <c r="D10" s="8">
         <v>1000</v>
       </c>
-      <c r="F10" s="10">
+      <c r="E10" s="10">
         <v>40000</v>
       </c>
+      <c r="F10" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="H10" s="1">
-        <f t="shared" si="1"/>
         <v>4000</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:8">
+    <row r="11" s="2" customFormat="1" spans="1:7">
       <c r="A11" s="8">
         <v>107</v>
       </c>
-      <c r="B11" s="8">
-        <v>1</v>
+      <c r="B11" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="8">
+        <v>22</v>
+      </c>
+      <c r="D11" s="8">
         <v>1200</v>
       </c>
-      <c r="F11" s="10">
+      <c r="E11" s="10">
         <v>100000</v>
       </c>
+      <c r="F11" s="1">
+        <v>0.12</v>
+      </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.12</v>
-      </c>
-      <c r="H11" s="1">
-        <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
+    <row r="12" s="2" customFormat="1" spans="1:7">
       <c r="A12" s="8">
         <v>108</v>
       </c>
-      <c r="B12" s="8">
-        <v>1</v>
+      <c r="B12" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="8">
+        <v>24</v>
+      </c>
+      <c r="D12" s="8">
         <v>300</v>
       </c>
-      <c r="F12" s="10">
+      <c r="E12" s="10">
         <v>200000</v>
       </c>
+      <c r="F12" s="1">
+        <v>0.03</v>
+      </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.03</v>
-      </c>
-      <c r="H12" s="1">
-        <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:8">
+    <row r="13" s="2" customFormat="1" spans="1:7">
       <c r="A13" s="8">
         <v>109</v>
       </c>
-      <c r="B13" s="8">
-        <v>1</v>
+      <c r="B13" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="8">
+        <v>26</v>
+      </c>
+      <c r="D13" s="8">
         <v>600</v>
       </c>
-      <c r="F13" s="10">
+      <c r="E13" s="10">
         <v>120000</v>
       </c>
+      <c r="F13" s="1">
+        <v>0.06</v>
+      </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>0.06</v>
-      </c>
-      <c r="H13" s="1">
-        <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:8">
+    <row r="14" s="2" customFormat="1" spans="1:7">
       <c r="A14" s="8">
         <v>110</v>
       </c>
-      <c r="B14" s="8">
-        <v>1</v>
+      <c r="B14" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="8">
+        <v>19</v>
+      </c>
+      <c r="D14" s="8">
         <v>800</v>
       </c>
-      <c r="F14" s="10">
+      <c r="E14" s="10">
         <v>90000</v>
       </c>
+      <c r="F14" s="1">
+        <v>0.08</v>
+      </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>0.08</v>
-      </c>
-      <c r="H14" s="1">
-        <f t="shared" si="1"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:8">
+    <row r="15" s="2" customFormat="1" spans="1:7">
       <c r="A15" s="8">
         <v>111</v>
       </c>
-      <c r="B15" s="8">
-        <v>1</v>
+      <c r="B15" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="8">
+        <v>29</v>
+      </c>
+      <c r="D15" s="8">
         <v>200</v>
       </c>
-      <c r="F15" s="10">
+      <c r="E15" s="10">
         <v>400000</v>
       </c>
+      <c r="F15" s="1">
+        <v>0.02</v>
+      </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-      <c r="H15" s="1">
-        <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:8">
+    <row r="16" s="2" customFormat="1" spans="1:7">
       <c r="A16" s="8">
         <v>112</v>
       </c>
-      <c r="B16" s="8">
-        <v>1</v>
+      <c r="B16" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="8">
+        <v>29</v>
+      </c>
+      <c r="D16" s="8">
         <v>100</v>
       </c>
-      <c r="F16" s="10">
+      <c r="E16" s="10">
         <v>800000</v>
       </c>
+      <c r="F16" s="1">
+        <v>0.01</v>
+      </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="H16" s="1">
-        <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
+    <row r="17" s="1" customFormat="1" spans="1:7">
       <c r="A17" s="11">
         <v>201</v>
       </c>
-      <c r="B17" s="11">
-        <v>10</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="11">
+      <c r="B17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="11">
         <v>1600</v>
       </c>
-      <c r="F17" s="9">
+      <c r="E17" s="9">
         <v>50000</v>
       </c>
+      <c r="F17" s="1">
+        <v>0.16</v>
+      </c>
       <c r="G17" s="1">
-        <f t="shared" ref="G17:G40" si="2">E17/SUMIF(B:B,B17,E:E)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H17" s="1">
-        <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
+    <row r="18" s="1" customFormat="1" spans="1:7">
       <c r="A18" s="11">
         <v>202</v>
       </c>
-      <c r="B18" s="11">
-        <v>10</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="11">
+      <c r="B18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="11">
         <v>1000</v>
       </c>
-      <c r="F18" s="9">
+      <c r="E18" s="9">
         <v>60000</v>
       </c>
+      <c r="F18" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G18" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="1">
-        <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
+    <row r="19" s="1" customFormat="1" spans="1:7">
       <c r="A19" s="11">
         <v>203</v>
       </c>
-      <c r="B19" s="11">
-        <v>10</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="11">
+      <c r="B19" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="11">
         <v>1300</v>
       </c>
-      <c r="F19" s="9">
+      <c r="E19" s="9">
         <v>80000</v>
       </c>
+      <c r="F19" s="1">
+        <v>0.13</v>
+      </c>
       <c r="G19" s="1">
-        <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="H19" s="1">
-        <f t="shared" si="1"/>
         <v>10400</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:8">
+    <row r="20" s="2" customFormat="1" spans="1:7">
       <c r="A20" s="11">
         <v>204</v>
       </c>
-      <c r="B20" s="11">
-        <v>10</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="11">
+      <c r="B20" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="11">
         <v>1000</v>
       </c>
-      <c r="F20" s="10">
+      <c r="E20" s="10">
         <v>100000</v>
       </c>
+      <c r="F20" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G20" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H20" s="1">
-        <f t="shared" si="1"/>
         <v>10000</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:8">
+    <row r="21" s="2" customFormat="1" spans="1:7">
       <c r="A21" s="11">
         <v>205</v>
       </c>
-      <c r="B21" s="11">
-        <v>10</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="11">
+      <c r="B21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="11">
         <v>900</v>
       </c>
-      <c r="F21" s="10">
+      <c r="E21" s="10">
         <v>160000</v>
       </c>
+      <c r="F21" s="1">
+        <v>0.09</v>
+      </c>
       <c r="G21" s="1">
-        <f t="shared" si="2"/>
-        <v>0.09</v>
-      </c>
-      <c r="H21" s="1">
-        <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:8">
+    <row r="22" s="2" customFormat="1" spans="1:7">
       <c r="A22" s="11">
         <v>206</v>
       </c>
-      <c r="B22" s="11">
-        <v>10</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="11">
+      <c r="B22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="11">
         <v>1000</v>
       </c>
-      <c r="F22" s="10">
+      <c r="E22" s="10">
         <v>80000</v>
       </c>
+      <c r="F22" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G22" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="1">
-        <f t="shared" si="1"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:8">
+    <row r="23" s="2" customFormat="1" spans="1:7">
       <c r="A23" s="11">
         <v>207</v>
       </c>
-      <c r="B23" s="11">
-        <v>10</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="11">
+      <c r="B23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="11">
         <v>1200</v>
       </c>
-      <c r="F23" s="10">
+      <c r="E23" s="10">
         <v>200000</v>
       </c>
+      <c r="F23" s="1">
+        <v>0.12</v>
+      </c>
       <c r="G23" s="1">
-        <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="H23" s="1">
-        <f t="shared" si="1"/>
         <v>24000</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:8">
+    <row r="24" s="2" customFormat="1" spans="1:7">
       <c r="A24" s="11">
         <v>208</v>
       </c>
-      <c r="B24" s="11">
-        <v>10</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="11">
+      <c r="B24" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="11">
         <v>300</v>
       </c>
-      <c r="F24" s="10">
+      <c r="E24" s="10">
         <v>400000</v>
       </c>
+      <c r="F24" s="1">
+        <v>0.03</v>
+      </c>
       <c r="G24" s="1">
-        <f t="shared" si="2"/>
-        <v>0.03</v>
-      </c>
-      <c r="H24" s="1">
-        <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:8">
+    <row r="25" s="2" customFormat="1" spans="1:7">
       <c r="A25" s="11">
         <v>209</v>
       </c>
-      <c r="B25" s="11">
-        <v>10</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="11">
+      <c r="B25" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="11">
         <v>600</v>
       </c>
-      <c r="F25" s="10">
+      <c r="E25" s="10">
         <v>240000</v>
       </c>
+      <c r="F25" s="1">
+        <v>0.06</v>
+      </c>
       <c r="G25" s="1">
-        <f t="shared" si="2"/>
-        <v>0.06</v>
-      </c>
-      <c r="H25" s="1">
-        <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:8">
+    <row r="26" s="2" customFormat="1" spans="1:7">
       <c r="A26" s="11">
         <v>210</v>
       </c>
-      <c r="B26" s="11">
-        <v>10</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="11">
+      <c r="B26" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="11">
         <v>800</v>
       </c>
-      <c r="F26" s="10">
+      <c r="E26" s="10">
         <v>180000</v>
       </c>
+      <c r="F26" s="1">
+        <v>0.08</v>
+      </c>
       <c r="G26" s="1">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="H26" s="1">
-        <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:8">
+    <row r="27" s="2" customFormat="1" spans="1:7">
       <c r="A27" s="11">
         <v>211</v>
       </c>
-      <c r="B27" s="11">
-        <v>10</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="11">
+      <c r="B27" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="11">
         <v>200</v>
       </c>
-      <c r="F27" s="10">
+      <c r="E27" s="10">
         <v>800000</v>
       </c>
+      <c r="F27" s="1">
+        <v>0.02</v>
+      </c>
       <c r="G27" s="1">
-        <f t="shared" si="2"/>
-        <v>0.02</v>
-      </c>
-      <c r="H27" s="1">
-        <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:8">
+    <row r="28" s="2" customFormat="1" spans="1:7">
       <c r="A28" s="11">
         <v>212</v>
       </c>
-      <c r="B28" s="11">
-        <v>10</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="11">
+      <c r="B28" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="11">
         <v>100</v>
       </c>
-      <c r="F28" s="10">
+      <c r="E28" s="10">
         <v>1600000</v>
       </c>
+      <c r="F28" s="1">
+        <v>0.01</v>
+      </c>
       <c r="G28" s="1">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="H28" s="1">
-        <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:7">
       <c r="A29" s="12">
         <v>301</v>
       </c>
-      <c r="B29" s="12">
-        <v>16</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="12">
+      <c r="B29" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="12">
         <v>1600</v>
       </c>
-      <c r="F29" s="13">
+      <c r="E29" s="13">
         <v>100000</v>
       </c>
+      <c r="F29" s="1">
+        <v>0.16</v>
+      </c>
       <c r="G29" s="1">
-        <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-      <c r="H29" s="1">
-        <f t="shared" si="1"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:7">
       <c r="A30" s="12">
         <v>302</v>
       </c>
-      <c r="B30" s="12">
-        <v>16</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="12">
+      <c r="B30" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="12">
         <v>1000</v>
       </c>
-      <c r="F30" s="13">
+      <c r="E30" s="13">
         <v>300000</v>
       </c>
+      <c r="F30" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G30" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H30" s="1">
-        <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:7">
       <c r="A31" s="12">
         <v>303</v>
       </c>
-      <c r="B31" s="12">
-        <v>16</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="12">
+      <c r="B31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="12">
         <v>1300</v>
       </c>
-      <c r="F31" s="13">
+      <c r="E31" s="13">
         <v>200000</v>
       </c>
+      <c r="F31" s="1">
+        <v>0.13</v>
+      </c>
       <c r="G31" s="1">
-        <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="H31" s="1">
-        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:7">
       <c r="A32" s="12">
         <v>304</v>
       </c>
-      <c r="B32" s="12">
-        <v>16</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="12">
+      <c r="B32" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="12">
         <v>1000</v>
       </c>
-      <c r="F32" s="13">
+      <c r="E32" s="13">
         <v>500000</v>
       </c>
+      <c r="F32" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G32" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H32" s="1">
-        <f t="shared" si="1"/>
         <v>50000</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:7">
       <c r="A33" s="12">
         <v>305</v>
       </c>
-      <c r="B33" s="12">
-        <v>16</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="12">
+      <c r="B33" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="12">
         <v>900</v>
       </c>
-      <c r="F33" s="13">
+      <c r="E33" s="13">
         <v>800000</v>
       </c>
+      <c r="F33" s="1">
+        <v>0.09</v>
+      </c>
       <c r="G33" s="1">
-        <f t="shared" si="2"/>
-        <v>0.09</v>
-      </c>
-      <c r="H33" s="1">
-        <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:7">
       <c r="A34" s="12">
         <v>306</v>
       </c>
-      <c r="B34" s="12">
-        <v>16</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="12">
+      <c r="B34" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="12">
         <v>1000</v>
       </c>
-      <c r="F34" s="13">
+      <c r="E34" s="13">
         <v>400000</v>
       </c>
+      <c r="F34" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G34" s="1">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="H34" s="1">
-        <f t="shared" si="1"/>
         <v>40000</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:7">
       <c r="A35" s="12">
         <v>307</v>
       </c>
-      <c r="B35" s="12">
-        <v>16</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="12">
+      <c r="B35" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="12">
         <v>1200</v>
       </c>
-      <c r="F35" s="13">
+      <c r="E35" s="13">
         <v>1000000</v>
       </c>
+      <c r="F35" s="1">
+        <v>0.12</v>
+      </c>
       <c r="G35" s="1">
-        <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="H35" s="1">
-        <f t="shared" si="1"/>
         <v>120000</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:7">
       <c r="A36" s="12">
         <v>308</v>
       </c>
-      <c r="B36" s="12">
-        <v>16</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="12">
+      <c r="B36" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="12">
         <v>300</v>
       </c>
-      <c r="F36" s="13">
+      <c r="E36" s="13">
         <v>2000000</v>
       </c>
+      <c r="F36" s="1">
+        <v>0.03</v>
+      </c>
       <c r="G36" s="1">
-        <f t="shared" si="2"/>
-        <v>0.03</v>
-      </c>
-      <c r="H36" s="1">
-        <f t="shared" si="1"/>
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:7">
       <c r="A37" s="12">
         <v>309</v>
       </c>
-      <c r="B37" s="12">
-        <v>16</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="12">
+      <c r="B37" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="12">
         <v>600</v>
       </c>
-      <c r="F37" s="13">
+      <c r="E37" s="13">
         <v>1200000</v>
       </c>
+      <c r="F37" s="1">
+        <v>0.06</v>
+      </c>
       <c r="G37" s="1">
-        <f t="shared" si="2"/>
-        <v>0.06</v>
-      </c>
-      <c r="H37" s="1">
-        <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:7">
       <c r="A38" s="12">
         <v>310</v>
       </c>
-      <c r="B38" s="12">
-        <v>16</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="12">
+      <c r="B38" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="12">
         <v>800</v>
       </c>
-      <c r="F38" s="13">
+      <c r="E38" s="13">
         <v>900000</v>
       </c>
+      <c r="F38" s="1">
+        <v>0.08</v>
+      </c>
       <c r="G38" s="1">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="H38" s="1">
-        <f t="shared" si="1"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:7">
       <c r="A39" s="12">
         <v>311</v>
       </c>
-      <c r="B39" s="12">
-        <v>16</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" s="12">
+      <c r="B39" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="12">
         <v>200</v>
       </c>
-      <c r="F39" s="13">
+      <c r="E39" s="13">
         <v>4000000</v>
       </c>
+      <c r="F39" s="1">
+        <v>0.02</v>
+      </c>
       <c r="G39" s="1">
-        <f t="shared" si="2"/>
-        <v>0.02</v>
-      </c>
-      <c r="H39" s="1">
-        <f t="shared" si="1"/>
         <v>80000</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:7">
       <c r="A40" s="12">
         <v>312</v>
       </c>
-      <c r="B40" s="12">
-        <v>16</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" s="12">
+      <c r="B40" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="12">
         <v>100</v>
       </c>
-      <c r="F40" s="13">
+      <c r="E40" s="13">
         <v>8000000</v>
       </c>
+      <c r="F40" s="1">
+        <v>0.01</v>
+      </c>
       <c r="G40" s="1">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="H40" s="1">
-        <f t="shared" si="1"/>
         <v>80000</v>
       </c>
     </row>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="46">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,109 +97,106 @@
     <t>client</t>
   </si>
   <si>
+    <t>1990000_35000</t>
+  </si>
+  <si>
+    <t>gfpj_props_1.png</t>
+  </si>
+  <si>
+    <t>1990000_70000</t>
+  </si>
+  <si>
+    <t>gfpj_props_3.png</t>
+  </si>
+  <si>
+    <t>1990000_245000</t>
+  </si>
+  <si>
+    <t>1990000_140000</t>
+  </si>
+  <si>
+    <t>1990000_350000</t>
+  </si>
+  <si>
+    <t>gfpj_props_5.png</t>
+  </si>
+  <si>
+    <t>1990000_210000</t>
+  </si>
+  <si>
+    <t>gfpj_props_2.png</t>
+  </si>
+  <si>
+    <t>1990000_105000</t>
+  </si>
+  <si>
+    <t>gfpj_props_4.png</t>
+  </si>
+  <si>
+    <t>1990000_280000</t>
+  </si>
+  <si>
+    <t>gfpj_props_6.png</t>
+  </si>
+  <si>
+    <t>1990000_175000</t>
+  </si>
+  <si>
+    <t>1990000_560000</t>
+  </si>
+  <si>
+    <t>gfpj_props_7.png</t>
+  </si>
+  <si>
+    <t>1990000_700000</t>
+  </si>
+  <si>
+    <t>1990000_1225000</t>
+  </si>
+  <si>
+    <t>1990000_1750000</t>
+  </si>
+  <si>
+    <t>1990000_1050000</t>
+  </si>
+  <si>
+    <t>1990000_525000</t>
+  </si>
+  <si>
+    <t>1990000_1400000</t>
+  </si>
+  <si>
+    <t>1990000_875000</t>
+  </si>
+  <si>
+    <t>1990000_2800000</t>
+  </si>
+  <si>
     <t>1990000_3500000</t>
   </si>
   <si>
-    <t>gfpj_props_1.png</t>
+    <t>1990000_6125000</t>
+  </si>
+  <si>
+    <t>1990000_8750000</t>
+  </si>
+  <si>
+    <t>1990000_5250000</t>
+  </si>
+  <si>
+    <t>1990000_2625000</t>
   </si>
   <si>
     <t>1990000_7000000</t>
   </si>
   <si>
-    <t>gfpj_props_3.png</t>
-  </si>
-  <si>
-    <t>1990000_24500000</t>
+    <t>1990000_4375000</t>
   </si>
   <si>
     <t>1990000_14000000</t>
   </si>
   <si>
-    <t>1990000_35000000</t>
-  </si>
-  <si>
-    <t>gfpj_props_5.png</t>
-  </si>
-  <si>
-    <t>1990000_21000000</t>
-  </si>
-  <si>
-    <t>gfpj_props_2.png</t>
-  </si>
-  <si>
-    <t>1990000_10500000</t>
-  </si>
-  <si>
-    <t>gfpj_props_4.png</t>
-  </si>
-  <si>
-    <t>1990000_28000000</t>
-  </si>
-  <si>
-    <t>gfpj_props_6.png</t>
-  </si>
-  <si>
     <t>1990000_17500000</t>
-  </si>
-  <si>
-    <t>1990000_56000000</t>
-  </si>
-  <si>
-    <t>gfpj_props_7.png</t>
-  </si>
-  <si>
-    <t>1990000_70000000</t>
-  </si>
-  <si>
-    <t>1990000_122500000</t>
-  </si>
-  <si>
-    <t>1990000_175000000</t>
-  </si>
-  <si>
-    <t>1990000_105000000</t>
-  </si>
-  <si>
-    <t>1990000_52500000</t>
-  </si>
-  <si>
-    <t>1990000_140000000</t>
-  </si>
-  <si>
-    <t>1990000_87500000</t>
-  </si>
-  <si>
-    <t>1990000_280000000</t>
-  </si>
-  <si>
-    <t>1990000_350000000</t>
-  </si>
-  <si>
-    <t>1990000_1225000000</t>
-  </si>
-  <si>
-    <t>1990000_700000000</t>
-  </si>
-  <si>
-    <t>1990000_1750000000</t>
-  </si>
-  <si>
-    <t>1990000_1050000000</t>
-  </si>
-  <si>
-    <t>1990000_525000000</t>
-  </si>
-  <si>
-    <t>1990000_1400000000</t>
-  </si>
-  <si>
-    <t>1990000_875000000</t>
-  </si>
-  <si>
-    <t>1990000_2800000000</t>
-  </si>
-  <si>
-    <t>1990000_3500000000</t>
   </si>
 </sst>
 </file>
@@ -382,12 +379,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1336,7 +1333,6 @@
       <c r="D8" s="5">
         <v>704</v>
       </c>
-      <c r="E8" s="2"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
@@ -1353,7 +1349,6 @@
       <c r="D9" s="5">
         <v>704</v>
       </c>
-      <c r="E9" s="2"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
@@ -1370,7 +1365,6 @@
       <c r="D10" s="5">
         <v>704</v>
       </c>
-      <c r="E10" s="2"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
@@ -1387,7 +1381,6 @@
       <c r="D11" s="5">
         <v>1480</v>
       </c>
-      <c r="E11" s="2"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
@@ -1404,7 +1397,6 @@
       <c r="D12" s="5">
         <v>704</v>
       </c>
-      <c r="E12" s="2"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
@@ -1421,7 +1413,6 @@
       <c r="D13" s="5">
         <v>704</v>
       </c>
-      <c r="E13" s="2"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
@@ -1438,7 +1429,6 @@
       <c r="D14" s="5">
         <v>704</v>
       </c>
-      <c r="E14" s="2"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
@@ -1455,7 +1445,6 @@
       <c r="D15" s="5">
         <v>704</v>
       </c>
-      <c r="E15" s="2"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
@@ -1472,7 +1461,6 @@
       <c r="D16" s="5">
         <v>704</v>
       </c>
-      <c r="E16" s="2"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
@@ -1531,7 +1519,6 @@
       <c r="D20" s="6">
         <v>704</v>
       </c>
-      <c r="E20" s="2"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
@@ -1548,7 +1535,6 @@
       <c r="D21" s="6">
         <v>704</v>
       </c>
-      <c r="E21" s="2"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
@@ -1565,7 +1551,6 @@
       <c r="D22" s="6">
         <v>704</v>
       </c>
-      <c r="E22" s="2"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
@@ -1582,7 +1567,6 @@
       <c r="D23" s="6">
         <v>1480</v>
       </c>
-      <c r="E23" s="2"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
@@ -1599,7 +1583,6 @@
       <c r="D24" s="6">
         <v>704</v>
       </c>
-      <c r="E24" s="2"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
@@ -1616,7 +1599,6 @@
       <c r="D25" s="6">
         <v>704</v>
       </c>
-      <c r="E25" s="2"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
@@ -1633,7 +1615,6 @@
       <c r="D26" s="6">
         <v>704</v>
       </c>
-      <c r="E26" s="2"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
@@ -1650,7 +1631,6 @@
       <c r="D27" s="6">
         <v>704</v>
       </c>
-      <c r="E27" s="2"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
@@ -1667,7 +1647,6 @@
       <c r="D28" s="6">
         <v>704</v>
       </c>
-      <c r="E28" s="2"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
@@ -1676,7 +1655,7 @@
         <v>301</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
@@ -1684,7 +1663,6 @@
       <c r="D29" s="7">
         <v>1480</v>
       </c>
-      <c r="E29" s="2"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
@@ -1693,7 +1671,7 @@
         <v>302</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>15</v>
@@ -1701,7 +1679,6 @@
       <c r="D30" s="7">
         <v>704</v>
       </c>
-      <c r="E30" s="2"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
@@ -1718,7 +1695,6 @@
       <c r="D31" s="7">
         <v>704</v>
       </c>
-      <c r="E31" s="2"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
@@ -1727,7 +1703,7 @@
         <v>304</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>15</v>
@@ -1735,7 +1711,6 @@
       <c r="D32" s="7">
         <v>704</v>
       </c>
-      <c r="E32" s="2"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
@@ -1744,7 +1719,7 @@
         <v>305</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>19</v>
@@ -1752,7 +1727,6 @@
       <c r="D33" s="7">
         <v>704</v>
       </c>
-      <c r="E33" s="2"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
@@ -1761,7 +1735,7 @@
         <v>306</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>15</v>
@@ -1769,7 +1743,6 @@
       <c r="D34" s="7">
         <v>704</v>
       </c>
-      <c r="E34" s="2"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
@@ -1778,7 +1751,7 @@
         <v>307</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>21</v>
@@ -1786,7 +1759,6 @@
       <c r="D35" s="7">
         <v>1480</v>
       </c>
-      <c r="E35" s="2"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
@@ -1795,7 +1767,7 @@
         <v>308</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>23</v>
@@ -1803,7 +1775,6 @@
       <c r="D36" s="7">
         <v>704</v>
       </c>
-      <c r="E36" s="2"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
@@ -1812,7 +1783,7 @@
         <v>309</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>25</v>
@@ -1820,7 +1791,6 @@
       <c r="D37" s="7">
         <v>704</v>
       </c>
-      <c r="E37" s="2"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
@@ -1829,7 +1799,7 @@
         <v>310</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>19</v>
@@ -1837,7 +1807,6 @@
       <c r="D38" s="7">
         <v>704</v>
       </c>
-      <c r="E38" s="2"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
@@ -1846,7 +1815,7 @@
         <v>311</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>28</v>
@@ -1854,7 +1823,6 @@
       <c r="D39" s="7">
         <v>704</v>
       </c>
-      <c r="E39" s="2"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
@@ -1863,7 +1831,7 @@
         <v>312</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>28</v>
@@ -1871,7 +1839,6 @@
       <c r="D40" s="7">
         <v>704</v>
       </c>
-      <c r="E40" s="2"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="OfficialAwards" sheetId="1" r:id="rId1"/>
@@ -100,13 +100,13 @@
     <t>1990000_35000</t>
   </si>
   <si>
-    <t>gfpj_props_1.png</t>
+    <t>xgfpj_props_1.png</t>
   </si>
   <si>
     <t>1990000_70000</t>
   </si>
   <si>
-    <t>gfpj_props_3.png</t>
+    <t>xgfpj_props_3.png</t>
   </si>
   <si>
     <t>1990000_245000</t>
@@ -118,25 +118,25 @@
     <t>1990000_350000</t>
   </si>
   <si>
-    <t>gfpj_props_5.png</t>
+    <t>xgfpj_props_5.png</t>
   </si>
   <si>
     <t>1990000_210000</t>
   </si>
   <si>
-    <t>gfpj_props_2.png</t>
+    <t>xgfpj_props_2.png</t>
   </si>
   <si>
     <t>1990000_105000</t>
   </si>
   <si>
-    <t>gfpj_props_4.png</t>
+    <t>xgfpj_props_4.png</t>
   </si>
   <si>
     <t>1990000_280000</t>
   </si>
   <si>
-    <t>gfpj_props_6.png</t>
+    <t>xgfpj_props_6.png</t>
   </si>
   <si>
     <t>1990000_175000</t>
@@ -145,7 +145,7 @@
     <t>1990000_560000</t>
   </si>
   <si>
-    <t>gfpj_props_7.png</t>
+    <t>xgfpj_props_7.png</t>
   </si>
   <si>
     <t>1990000_700000</t>
@@ -1221,7 +1221,7 @@
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.2333333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.25" style="2" customWidth="1"/>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="OfficialAwards" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,106 +97,109 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_35000</t>
+    <t>1990000_700000</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
   </si>
   <si>
-    <t>1990000_70000</t>
+    <t>1990000_1400000</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
   </si>
   <si>
-    <t>1990000_245000</t>
-  </si>
-  <si>
-    <t>1990000_140000</t>
-  </si>
-  <si>
-    <t>1990000_350000</t>
+    <t>1990000_28000000</t>
+  </si>
+  <si>
+    <t>1990000_2800000</t>
+  </si>
+  <si>
+    <t>1990000_42000000</t>
   </si>
   <si>
     <t>xgfpj_props_5.png</t>
   </si>
   <si>
-    <t>1990000_210000</t>
+    <t>1990000_4200000</t>
+  </si>
+  <si>
+    <t>1990000_56000000</t>
   </si>
   <si>
     <t>xgfpj_props_2.png</t>
   </si>
   <si>
-    <t>1990000_105000</t>
+    <t>1990000_7000000</t>
   </si>
   <si>
     <t>xgfpj_props_4.png</t>
   </si>
   <si>
-    <t>1990000_280000</t>
+    <t>1990000_70000000</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
   </si>
   <si>
-    <t>1990000_175000</t>
-  </si>
-  <si>
-    <t>1990000_560000</t>
+    <t>1990000_14000000</t>
+  </si>
+  <si>
+    <t>1990000_84000000</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
   </si>
   <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>1990000_1225000</t>
-  </si>
-  <si>
-    <t>1990000_1750000</t>
-  </si>
-  <si>
-    <t>1990000_1050000</t>
-  </si>
-  <si>
-    <t>1990000_525000</t>
-  </si>
-  <si>
-    <t>1990000_1400000</t>
-  </si>
-  <si>
-    <t>1990000_875000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
+    <t>1990000_21000000</t>
   </si>
   <si>
     <t>1990000_3500000</t>
   </si>
   <si>
-    <t>1990000_6125000</t>
-  </si>
-  <si>
-    <t>1990000_8750000</t>
-  </si>
-  <si>
-    <t>1990000_5250000</t>
-  </si>
-  <si>
-    <t>1990000_2625000</t>
-  </si>
-  <si>
-    <t>1990000_7000000</t>
-  </si>
-  <si>
-    <t>1990000_4375000</t>
-  </si>
-  <si>
-    <t>1990000_14000000</t>
+    <t>1990000_140000000</t>
+  </si>
+  <si>
+    <t>1990000_210000000</t>
+  </si>
+  <si>
+    <t>1990000_280000000</t>
+  </si>
+  <si>
+    <t>1990000_35000000</t>
+  </si>
+  <si>
+    <t>1990000_350000000</t>
+  </si>
+  <si>
+    <t>1990000_420000000</t>
+  </si>
+  <si>
+    <t>1990000_105000000</t>
   </si>
   <si>
     <t>1990000_17500000</t>
+  </si>
+  <si>
+    <t>1990000_700000000</t>
+  </si>
+  <si>
+    <t>1990000_1050000000</t>
+  </si>
+  <si>
+    <t>1990000_1400000000</t>
+  </si>
+  <si>
+    <t>1990000_175000000</t>
+  </si>
+  <si>
+    <t>1990000_1750000000</t>
+  </si>
+  <si>
+    <t>1990000_2100000000</t>
+  </si>
+  <si>
+    <t>1990000_525000000</t>
   </si>
 </sst>
 </file>
@@ -379,12 +382,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1303,7 +1306,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="5">
-        <v>704</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
@@ -1317,7 +1320,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5">
-        <v>704</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1331,7 +1334,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="5">
-        <v>704</v>
+        <v>1150</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1347,7 +1350,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="5">
-        <v>704</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1363,7 +1366,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="5">
-        <v>704</v>
+        <v>769</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1373,10 +1376,10 @@
         <v>107</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5">
         <v>1480</v>
@@ -1389,13 +1392,13 @@
         <v>108</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="5">
-        <v>704</v>
+        <v>460</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1405,13 +1408,13 @@
         <v>109</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="5">
-        <v>704</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1421,13 +1424,13 @@
         <v>110</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="5">
-        <v>704</v>
+        <v>230</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1437,13 +1440,13 @@
         <v>111</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="5">
-        <v>704</v>
+        <v>37</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1453,13 +1456,13 @@
         <v>112</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="D16" s="5">
-        <v>704</v>
+        <v>152</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1469,7 +1472,7 @@
         <v>201</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
@@ -1483,13 +1486,13 @@
         <v>202</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="6">
-        <v>704</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:7">
@@ -1497,13 +1500,13 @@
         <v>203</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="6">
-        <v>704</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1511,13 +1514,13 @@
         <v>204</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="6">
-        <v>704</v>
+        <v>1150</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1527,13 +1530,13 @@
         <v>205</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="6">
-        <v>704</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1543,13 +1546,13 @@
         <v>206</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="6">
-        <v>704</v>
+        <v>769</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1559,10 +1562,10 @@
         <v>207</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" s="6">
         <v>1480</v>
@@ -1575,13 +1578,13 @@
         <v>208</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" s="6">
-        <v>704</v>
+        <v>460</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1591,13 +1594,13 @@
         <v>209</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" s="6">
-        <v>704</v>
+        <v>46</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1607,13 +1610,13 @@
         <v>210</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="6">
-        <v>704</v>
+        <v>230</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -1623,13 +1626,13 @@
         <v>211</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="6">
-        <v>704</v>
+        <v>37</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1639,13 +1642,13 @@
         <v>212</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="6">
-        <v>704</v>
+        <v>152</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1655,7 +1658,7 @@
         <v>301</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
@@ -1671,13 +1674,13 @@
         <v>302</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="7">
-        <v>704</v>
+        <v>2301</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1687,13 +1690,13 @@
         <v>303</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="7">
-        <v>704</v>
+        <v>115</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1703,13 +1706,13 @@
         <v>304</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="7">
-        <v>704</v>
+        <v>1150</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1719,13 +1722,13 @@
         <v>305</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="7">
-        <v>704</v>
+        <v>78</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1735,13 +1738,13 @@
         <v>306</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="7">
-        <v>704</v>
+        <v>769</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1751,10 +1754,10 @@
         <v>307</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" s="7">
         <v>1480</v>
@@ -1767,13 +1770,13 @@
         <v>308</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D36" s="7">
-        <v>704</v>
+        <v>460</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1783,13 +1786,13 @@
         <v>309</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37" s="7">
-        <v>704</v>
+        <v>46</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1799,13 +1802,13 @@
         <v>310</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="7">
-        <v>704</v>
+        <v>230</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1815,13 +1818,13 @@
         <v>311</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39" s="7">
-        <v>704</v>
+        <v>37</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1831,13 +1834,13 @@
         <v>312</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" s="7">
-        <v>704</v>
+        <v>152</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="55">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,109 +97,133 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_700000</t>
+    <t>1990000_2520000</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
   </si>
   <si>
-    <t>1990000_1400000</t>
+    <t>1990000_378000</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
   </si>
   <si>
-    <t>1990000_28000000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
-  </si>
-  <si>
-    <t>1990000_42000000</t>
+    <t>1990000_2331000</t>
+  </si>
+  <si>
+    <t>1990000_567000</t>
+  </si>
+  <si>
+    <t>1990000_2142000</t>
   </si>
   <si>
     <t>xgfpj_props_5.png</t>
   </si>
   <si>
-    <t>1990000_4200000</t>
-  </si>
-  <si>
-    <t>1990000_56000000</t>
+    <t>1990000_756000</t>
+  </si>
+  <si>
+    <t>1990000_1953000</t>
   </si>
   <si>
     <t>xgfpj_props_2.png</t>
   </si>
   <si>
-    <t>1990000_7000000</t>
+    <t>1990000_945000</t>
   </si>
   <si>
     <t>xgfpj_props_4.png</t>
   </si>
   <si>
-    <t>1990000_70000000</t>
+    <t>1990000_1764000</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
   </si>
   <si>
-    <t>1990000_14000000</t>
-  </si>
-  <si>
-    <t>1990000_84000000</t>
+    <t>1990000_1134000</t>
+  </si>
+  <si>
+    <t>1990000_1575000</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
   </si>
   <si>
-    <t>1990000_21000000</t>
-  </si>
-  <si>
-    <t>1990000_3500000</t>
-  </si>
-  <si>
-    <t>1990000_140000000</t>
-  </si>
-  <si>
-    <t>1990000_210000000</t>
-  </si>
-  <si>
-    <t>1990000_280000000</t>
-  </si>
-  <si>
-    <t>1990000_35000000</t>
-  </si>
-  <si>
-    <t>1990000_350000000</t>
-  </si>
-  <si>
-    <t>1990000_420000000</t>
-  </si>
-  <si>
-    <t>1990000_105000000</t>
-  </si>
-  <si>
-    <t>1990000_17500000</t>
-  </si>
-  <si>
-    <t>1990000_700000000</t>
-  </si>
-  <si>
-    <t>1990000_1050000000</t>
-  </si>
-  <si>
-    <t>1990000_1400000000</t>
-  </si>
-  <si>
-    <t>1990000_175000000</t>
-  </si>
-  <si>
-    <t>1990000_1750000000</t>
-  </si>
-  <si>
-    <t>1990000_2100000000</t>
-  </si>
-  <si>
-    <t>1990000_525000000</t>
+    <t>1990000_1323000</t>
+  </si>
+  <si>
+    <t>1990000_12600000</t>
+  </si>
+  <si>
+    <t>1990000_1890000</t>
+  </si>
+  <si>
+    <t>1990000_11655000</t>
+  </si>
+  <si>
+    <t>1990000_2835000</t>
+  </si>
+  <si>
+    <t>1990000_10710000</t>
+  </si>
+  <si>
+    <t>1990000_3780000</t>
+  </si>
+  <si>
+    <t>1990000_9765000</t>
+  </si>
+  <si>
+    <t>1990000_4725000</t>
+  </si>
+  <si>
+    <t>1990000_8820000</t>
+  </si>
+  <si>
+    <t>1990000_5670000</t>
+  </si>
+  <si>
+    <t>1990000_7875000</t>
+  </si>
+  <si>
+    <t>1990000_6615000</t>
+  </si>
+  <si>
+    <t>1990000_126000000</t>
+  </si>
+  <si>
+    <t>1990000_18900000</t>
+  </si>
+  <si>
+    <t>1990000_116550000</t>
+  </si>
+  <si>
+    <t>1990000_28350000</t>
+  </si>
+  <si>
+    <t>1990000_107100000</t>
+  </si>
+  <si>
+    <t>1990000_37800000</t>
+  </si>
+  <si>
+    <t>1990000_97650000</t>
+  </si>
+  <si>
+    <t>1990000_47250000</t>
+  </si>
+  <si>
+    <t>1990000_88200000</t>
+  </si>
+  <si>
+    <t>1990000_56700000</t>
+  </si>
+  <si>
+    <t>1990000_78750000</t>
+  </si>
+  <si>
+    <t>1990000_66150000</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1316,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="5">
-        <v>1480</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
@@ -1306,7 +1330,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="5">
-        <v>2301</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
@@ -1320,7 +1344,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5">
-        <v>115</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1334,7 +1358,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="5">
-        <v>1150</v>
+        <v>1540</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1350,7 +1374,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="5">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1366,7 +1390,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="5">
-        <v>769</v>
+        <v>1151</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1382,7 +1406,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="5">
-        <v>1480</v>
+        <v>444</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1398,7 +1422,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="5">
-        <v>460</v>
+        <v>929</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1414,7 +1438,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="5">
-        <v>46</v>
+        <v>499</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1430,7 +1454,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="5">
-        <v>230</v>
+        <v>777</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1446,7 +1470,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="5">
-        <v>37</v>
+        <v>555</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1462,7 +1486,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="5">
-        <v>152</v>
+        <v>666</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1478,7 +1502,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="6">
-        <v>1480</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:7">
@@ -1486,13 +1510,13 @@
         <v>202</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="6">
-        <v>2301</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:7">
@@ -1500,13 +1524,13 @@
         <v>203</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="6">
-        <v>115</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1514,13 +1538,13 @@
         <v>204</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="6">
-        <v>1150</v>
+        <v>1540</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1530,13 +1554,13 @@
         <v>205</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="6">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1546,13 +1570,13 @@
         <v>206</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="6">
-        <v>769</v>
+        <v>1151</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1562,13 +1586,13 @@
         <v>207</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="6">
-        <v>1480</v>
+        <v>444</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1578,13 +1602,13 @@
         <v>208</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="6">
-        <v>460</v>
+        <v>929</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1594,13 +1618,13 @@
         <v>209</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="6">
-        <v>46</v>
+        <v>499</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1610,13 +1634,13 @@
         <v>210</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="6">
-        <v>230</v>
+        <v>777</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -1626,13 +1650,13 @@
         <v>211</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="6">
-        <v>37</v>
+        <v>555</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1642,13 +1666,13 @@
         <v>212</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="6">
-        <v>152</v>
+        <v>666</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1658,13 +1682,13 @@
         <v>301</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="7">
-        <v>1480</v>
+        <v>347</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1674,13 +1698,13 @@
         <v>302</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="7">
-        <v>2301</v>
+        <v>2316</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1690,13 +1714,13 @@
         <v>303</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="7">
-        <v>115</v>
+        <v>374</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1706,13 +1730,13 @@
         <v>304</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="7">
-        <v>1150</v>
+        <v>1540</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1722,13 +1746,13 @@
         <v>305</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="7">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1738,13 +1762,13 @@
         <v>306</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="7">
-        <v>769</v>
+        <v>1151</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1754,13 +1778,13 @@
         <v>307</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D35" s="7">
-        <v>1480</v>
+        <v>444</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1770,13 +1794,13 @@
         <v>308</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D36" s="7">
-        <v>460</v>
+        <v>929</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1786,13 +1810,13 @@
         <v>309</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D37" s="7">
-        <v>46</v>
+        <v>499</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1802,13 +1826,13 @@
         <v>310</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="7">
-        <v>230</v>
+        <v>777</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1818,13 +1842,13 @@
         <v>311</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="7">
-        <v>37</v>
+        <v>555</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1834,13 +1858,13 @@
         <v>312</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="7">
-        <v>152</v>
+        <v>666</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,133 +97,100 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_2520000</t>
+    <t>1990000_43500</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
   </si>
   <si>
-    <t>1990000_378000</t>
+    <t>1990000_170</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
   </si>
   <si>
-    <t>1990000_2331000</t>
-  </si>
-  <si>
-    <t>1990000_567000</t>
-  </si>
-  <si>
-    <t>1990000_2142000</t>
+    <t>1990000_17400</t>
+  </si>
+  <si>
+    <t>1990000_520</t>
+  </si>
+  <si>
+    <t>1990000_8700</t>
   </si>
   <si>
     <t>xgfpj_props_5.png</t>
   </si>
   <si>
-    <t>1990000_756000</t>
-  </si>
-  <si>
-    <t>1990000_1953000</t>
+    <t>1990000_690</t>
+  </si>
+  <si>
+    <t>1990000_4350</t>
   </si>
   <si>
     <t>xgfpj_props_2.png</t>
   </si>
   <si>
-    <t>1990000_945000</t>
+    <t>1990000_870</t>
   </si>
   <si>
     <t>xgfpj_props_4.png</t>
   </si>
   <si>
-    <t>1990000_1764000</t>
+    <t>1990000_3480</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
   </si>
   <si>
-    <t>1990000_1134000</t>
-  </si>
-  <si>
-    <t>1990000_1575000</t>
+    <t>1990000_1300</t>
+  </si>
+  <si>
+    <t>1990000_2610</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
   </si>
   <si>
-    <t>1990000_1323000</t>
-  </si>
-  <si>
-    <t>1990000_12600000</t>
-  </si>
-  <si>
-    <t>1990000_1890000</t>
-  </si>
-  <si>
-    <t>1990000_11655000</t>
-  </si>
-  <si>
-    <t>1990000_2835000</t>
-  </si>
-  <si>
-    <t>1990000_10710000</t>
-  </si>
-  <si>
-    <t>1990000_3780000</t>
-  </si>
-  <si>
-    <t>1990000_9765000</t>
-  </si>
-  <si>
-    <t>1990000_4725000</t>
-  </si>
-  <si>
-    <t>1990000_8820000</t>
-  </si>
-  <si>
-    <t>1990000_5670000</t>
-  </si>
-  <si>
-    <t>1990000_7875000</t>
-  </si>
-  <si>
-    <t>1990000_6615000</t>
-  </si>
-  <si>
-    <t>1990000_126000000</t>
-  </si>
-  <si>
-    <t>1990000_18900000</t>
-  </si>
-  <si>
-    <t>1990000_116550000</t>
-  </si>
-  <si>
-    <t>1990000_28350000</t>
-  </si>
-  <si>
-    <t>1990000_107100000</t>
-  </si>
-  <si>
-    <t>1990000_37800000</t>
-  </si>
-  <si>
-    <t>1990000_97650000</t>
-  </si>
-  <si>
-    <t>1990000_47250000</t>
-  </si>
-  <si>
-    <t>1990000_88200000</t>
-  </si>
-  <si>
-    <t>1990000_56700000</t>
-  </si>
-  <si>
-    <t>1990000_78750000</t>
-  </si>
-  <si>
-    <t>1990000_66150000</t>
+    <t>1990000_1740</t>
+  </si>
+  <si>
+    <t>1990000_261000</t>
+  </si>
+  <si>
+    <t>1990000_87000</t>
+  </si>
+  <si>
+    <t>1990000_26100</t>
+  </si>
+  <si>
+    <t>1990000_13920</t>
+  </si>
+  <si>
+    <t>1990000_6960</t>
+  </si>
+  <si>
+    <t>1990000_6090</t>
+  </si>
+  <si>
+    <t>1990000_5220</t>
+  </si>
+  <si>
+    <t>1990000_174000</t>
+  </si>
+  <si>
+    <t>1990000_430</t>
+  </si>
+  <si>
+    <t>1990000_60900</t>
+  </si>
+  <si>
+    <t>1990000_13050</t>
+  </si>
+  <si>
+    <t>1990000_2170</t>
+  </si>
+  <si>
+    <t>1990000_3040</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1283,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="5">
-        <v>347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
@@ -1330,7 +1297,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="5">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
@@ -1344,7 +1311,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1358,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="5">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1374,7 +1341,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="5">
-        <v>402</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1390,7 +1357,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="5">
-        <v>1151</v>
+        <v>1543</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1406,7 +1373,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="5">
-        <v>444</v>
+        <v>1480</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1422,7 +1389,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="5">
-        <v>929</v>
+        <v>1235</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1438,7 +1405,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="5">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1454,7 +1421,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="5">
-        <v>777</v>
+        <v>926</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1470,7 +1437,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="5">
-        <v>555</v>
+        <v>617</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1486,7 +1453,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="5">
-        <v>666</v>
+        <v>741</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1502,7 +1469,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="6">
-        <v>347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:7">
@@ -1510,13 +1477,13 @@
         <v>202</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="6">
-        <v>2316</v>
+        <v>5357</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:7">
@@ -1524,13 +1491,13 @@
         <v>203</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="6">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1538,13 +1505,13 @@
         <v>204</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="6">
-        <v>1540</v>
+        <v>2143</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1554,13 +1521,13 @@
         <v>205</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="6">
-        <v>402</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1570,13 +1537,13 @@
         <v>206</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="6">
-        <v>1151</v>
+        <v>1071</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1586,13 +1553,13 @@
         <v>207</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="6">
-        <v>444</v>
+        <v>107</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1602,13 +1569,13 @@
         <v>208</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="6">
-        <v>929</v>
+        <v>357</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1618,13 +1585,13 @@
         <v>209</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="6">
-        <v>499</v>
+        <v>179</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1634,13 +1601,13 @@
         <v>210</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="6">
-        <v>777</v>
+        <v>286</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -1650,13 +1617,13 @@
         <v>211</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="6">
-        <v>555</v>
+        <v>214</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1666,13 +1633,13 @@
         <v>212</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="6">
-        <v>666</v>
+        <v>250</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1682,13 +1649,13 @@
         <v>301</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="7">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1698,13 +1665,13 @@
         <v>302</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="7">
-        <v>2316</v>
+        <v>2045</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1714,13 +1681,13 @@
         <v>303</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="7">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1730,13 +1697,13 @@
         <v>304</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="7">
-        <v>1540</v>
+        <v>1705</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1746,13 +1713,13 @@
         <v>305</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="7">
-        <v>402</v>
+        <v>114</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1762,13 +1729,13 @@
         <v>306</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="7">
-        <v>1151</v>
+        <v>1136</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1778,13 +1745,13 @@
         <v>307</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D35" s="7">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1794,13 +1761,13 @@
         <v>308</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D36" s="7">
-        <v>929</v>
+        <v>1136</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1810,13 +1777,13 @@
         <v>309</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D37" s="7">
-        <v>499</v>
+        <v>682</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1826,13 +1793,13 @@
         <v>310</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="7">
-        <v>777</v>
+        <v>1023</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1842,13 +1809,13 @@
         <v>311</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="7">
-        <v>555</v>
+        <v>795</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1858,13 +1825,13 @@
         <v>312</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="7">
-        <v>666</v>
+        <v>909</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
   <si>
     <t>序列ID</t>
   </si>
@@ -100,55 +100,76 @@
     <t>1990000_43500</t>
   </si>
   <si>
+    <t>xgfpj_props_7.png</t>
+  </si>
+  <si>
+    <t>黄金宝箱</t>
+  </si>
+  <si>
+    <t>1990000_170</t>
+  </si>
+  <si>
     <t>xgfpj_props_1.png</t>
   </si>
   <si>
-    <t>1990000_170</t>
+    <t>一个金币</t>
+  </si>
+  <si>
+    <t>1990000_17400</t>
+  </si>
+  <si>
+    <t>xgfpj_props_6.png</t>
+  </si>
+  <si>
+    <t>礼物宝箱</t>
+  </si>
+  <si>
+    <t>1990000_520</t>
+  </si>
+  <si>
+    <t>1990000_8700</t>
+  </si>
+  <si>
+    <t>xgfpj_props_5.png</t>
+  </si>
+  <si>
+    <t>红包</t>
+  </si>
+  <si>
+    <t>1990000_690</t>
+  </si>
+  <si>
+    <t>1990000_4350</t>
+  </si>
+  <si>
+    <t>xgfpj_props_4.png</t>
+  </si>
+  <si>
+    <t>绿色宝箱</t>
+  </si>
+  <si>
+    <t>1990000_870</t>
+  </si>
+  <si>
+    <t>xgfpj_props_2.png</t>
+  </si>
+  <si>
+    <t>两个金币</t>
+  </si>
+  <si>
+    <t>1990000_3480</t>
+  </si>
+  <si>
+    <t>1990000_1300</t>
+  </si>
+  <si>
+    <t>1990000_2610</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
   </si>
   <si>
-    <t>1990000_17400</t>
-  </si>
-  <si>
-    <t>1990000_520</t>
-  </si>
-  <si>
-    <t>1990000_8700</t>
-  </si>
-  <si>
-    <t>xgfpj_props_5.png</t>
-  </si>
-  <si>
-    <t>1990000_690</t>
-  </si>
-  <si>
-    <t>1990000_4350</t>
-  </si>
-  <si>
-    <t>xgfpj_props_2.png</t>
-  </si>
-  <si>
-    <t>1990000_870</t>
-  </si>
-  <si>
-    <t>xgfpj_props_4.png</t>
-  </si>
-  <si>
-    <t>1990000_3480</t>
-  </si>
-  <si>
-    <t>xgfpj_props_6.png</t>
-  </si>
-  <si>
-    <t>1990000_1300</t>
-  </si>
-  <si>
-    <t>1990000_2610</t>
-  </si>
-  <si>
-    <t>xgfpj_props_7.png</t>
+    <t>一堆金币</t>
   </si>
   <si>
     <t>1990000_1740</t>
@@ -384,7 +405,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,6 +421,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.899990844447157"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,7 +761,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -746,16 +785,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -764,79 +803,67 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -845,8 +872,20 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -869,6 +908,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,8 +1258,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.875" style="2" customWidth="1"/>
@@ -1219,10 +1267,11 @@
     <col min="4" max="4" width="16.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.25" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="19.375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1236,7 +1285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1250,7 +1299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -1264,7 +1313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
@@ -1272,11 +1321,11 @@
       </c>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="5">
         <v>101</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1285,553 +1334,660 @@
       <c r="D5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="5">
         <v>102</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>14</v>
+      <c r="B6" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="5">
         <v>2315</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="5">
         <v>103</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
+      <c r="B7" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="5">
         <v>104</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>17</v>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="5">
         <v>1543</v>
       </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7">
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="5">
         <v>105</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5">
         <v>31</v>
       </c>
+      <c r="E9" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7">
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="5">
         <v>106</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>20</v>
+      <c r="B10" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="5">
         <v>1543</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7">
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="5">
         <v>107</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
+      <c r="B11" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D11" s="5">
         <v>1480</v>
       </c>
+      <c r="E11" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7">
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="5">
         <v>108</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
+      <c r="B12" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5">
         <v>1235</v>
       </c>
+      <c r="E12" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7">
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="5">
         <v>109</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
+      <c r="B13" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="5">
         <v>556</v>
       </c>
+      <c r="E13" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7">
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="5">
         <v>110</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>27</v>
+      <c r="B14" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D14" s="5">
         <v>926</v>
       </c>
+      <c r="E14" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7">
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="5">
         <v>111</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>28</v>
+      <c r="B15" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5">
         <v>617</v>
       </c>
+      <c r="E15" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7">
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="5">
         <v>112</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>30</v>
+      <c r="B16" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5">
         <v>741</v>
       </c>
+      <c r="E16" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:7">
-      <c r="A17" s="6">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:8">
+      <c r="A17" s="9">
         <v>201</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>31</v>
+      <c r="B17" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:7">
-      <c r="A18" s="6">
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:8">
+      <c r="A18" s="9">
         <v>202</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>23</v>
+      <c r="B18" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="6">
+        <v>16</v>
+      </c>
+      <c r="D18" s="9">
         <v>5357</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:7">
-      <c r="A19" s="6">
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:8">
+      <c r="A19" s="9">
         <v>203</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>32</v>
+      <c r="B19" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="6">
+        <v>19</v>
+      </c>
+      <c r="D19" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="6">
+      <c r="E19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="9">
         <v>204</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>30</v>
+      <c r="B20" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="6">
+        <v>16</v>
+      </c>
+      <c r="D20" s="9">
         <v>2143</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="6">
+    <row r="21" spans="1:8">
+      <c r="A21" s="9">
         <v>205</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>33</v>
+      <c r="B21" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="6">
+        <v>23</v>
+      </c>
+      <c r="D21" s="9">
         <v>36</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="6">
+    <row r="22" spans="1:8">
+      <c r="A22" s="9">
         <v>206</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>28</v>
+      <c r="B22" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="6">
+        <v>16</v>
+      </c>
+      <c r="D22" s="9">
         <v>1071</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="6">
+    <row r="23" spans="1:8">
+      <c r="A23" s="9">
         <v>207</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>34</v>
+      <c r="B23" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="6">
+        <v>27</v>
+      </c>
+      <c r="D23" s="9">
         <v>107</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="6">
+    <row r="24" spans="1:8">
+      <c r="A24" s="9">
         <v>208</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>25</v>
+      <c r="B24" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="6">
+        <v>30</v>
+      </c>
+      <c r="D24" s="9">
         <v>357</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="6">
+    <row r="25" spans="1:8">
+      <c r="A25" s="9">
         <v>209</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>35</v>
+      <c r="B25" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="6">
+        <v>27</v>
+      </c>
+      <c r="D25" s="9">
         <v>179</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="6">
+    <row r="26" spans="1:8">
+      <c r="A26" s="9">
         <v>210</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>21</v>
+      <c r="B26" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="6">
+        <v>30</v>
+      </c>
+      <c r="D26" s="9">
         <v>286</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="6">
+    <row r="27" spans="1:8">
+      <c r="A27" s="9">
         <v>211</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="9">
+        <v>214</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="6">
-        <v>214</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="6">
+    <row r="28" spans="1:8">
+      <c r="A28" s="9">
         <v>212</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>37</v>
+      <c r="B28" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="6">
+        <v>35</v>
+      </c>
+      <c r="D28" s="9">
         <v>250</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="7">
+    <row r="29" spans="1:8">
+      <c r="A29" s="10">
         <v>301</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>38</v>
+      <c r="B29" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="10">
         <v>0</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="7">
+    <row r="30" spans="1:8">
+      <c r="A30" s="10">
         <v>302</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>39</v>
+      <c r="B30" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="7">
+        <v>16</v>
+      </c>
+      <c r="D30" s="10">
         <v>2045</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="7">
+    <row r="31" spans="1:8">
+      <c r="A31" s="10">
         <v>303</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>40</v>
+      <c r="B31" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="7">
+        <v>19</v>
+      </c>
+      <c r="D31" s="10">
         <v>0</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="7">
+    <row r="32" spans="1:8">
+      <c r="A32" s="10">
         <v>304</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>23</v>
+      <c r="B32" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="7">
+        <v>16</v>
+      </c>
+      <c r="D32" s="10">
         <v>1705</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="7">
+      <c r="A33" s="10">
         <v>305</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>41</v>
+      <c r="B33" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="7">
+        <v>23</v>
+      </c>
+      <c r="D33" s="10">
         <v>114</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="7">
+      <c r="A34" s="10">
         <v>306</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>27</v>
+      <c r="B34" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="7">
+        <v>16</v>
+      </c>
+      <c r="D34" s="10">
         <v>1136</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="7">
+      <c r="A35" s="10">
         <v>307</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>35</v>
+      <c r="B35" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="7">
+        <v>27</v>
+      </c>
+      <c r="D35" s="10">
         <v>455</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="7">
+      <c r="A36" s="10">
         <v>308</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="D36" s="10">
         <v>1136</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="7">
+      <c r="A37" s="10">
         <v>309</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>25</v>
+      <c r="B37" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="7">
+        <v>27</v>
+      </c>
+      <c r="D37" s="10">
         <v>682</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="7">
+      <c r="A38" s="10">
         <v>310</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>42</v>
+      <c r="B38" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="7">
+        <v>30</v>
+      </c>
+      <c r="D38" s="10">
         <v>1023</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="7">
+      <c r="A39" s="10">
         <v>311</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>43</v>
+      <c r="B39" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="7">
+        <v>35</v>
+      </c>
+      <c r="D39" s="10">
         <v>795</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="7">
+      <c r="A40" s="10">
         <v>312</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>28</v>
+      <c r="B40" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="7">
+        <v>35</v>
+      </c>
+      <c r="D40" s="10">
         <v>909</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
   <si>
     <t>序列ID</t>
   </si>
@@ -100,76 +100,55 @@
     <t>1990000_43500</t>
   </si>
   <si>
+    <t>xgfpj_props_1.png</t>
+  </si>
+  <si>
+    <t>1990000_170</t>
+  </si>
+  <si>
+    <t>xgfpj_props_3.png</t>
+  </si>
+  <si>
+    <t>1990000_17400</t>
+  </si>
+  <si>
+    <t>1990000_520</t>
+  </si>
+  <si>
+    <t>1990000_8700</t>
+  </si>
+  <si>
+    <t>xgfpj_props_5.png</t>
+  </si>
+  <si>
+    <t>1990000_690</t>
+  </si>
+  <si>
+    <t>1990000_4350</t>
+  </si>
+  <si>
+    <t>xgfpj_props_2.png</t>
+  </si>
+  <si>
+    <t>1990000_870</t>
+  </si>
+  <si>
+    <t>xgfpj_props_4.png</t>
+  </si>
+  <si>
+    <t>1990000_3480</t>
+  </si>
+  <si>
+    <t>xgfpj_props_6.png</t>
+  </si>
+  <si>
+    <t>1990000_1300</t>
+  </si>
+  <si>
+    <t>1990000_2610</t>
+  </si>
+  <si>
     <t>xgfpj_props_7.png</t>
-  </si>
-  <si>
-    <t>黄金宝箱</t>
-  </si>
-  <si>
-    <t>1990000_170</t>
-  </si>
-  <si>
-    <t>xgfpj_props_1.png</t>
-  </si>
-  <si>
-    <t>一个金币</t>
-  </si>
-  <si>
-    <t>1990000_17400</t>
-  </si>
-  <si>
-    <t>xgfpj_props_6.png</t>
-  </si>
-  <si>
-    <t>礼物宝箱</t>
-  </si>
-  <si>
-    <t>1990000_520</t>
-  </si>
-  <si>
-    <t>1990000_8700</t>
-  </si>
-  <si>
-    <t>xgfpj_props_5.png</t>
-  </si>
-  <si>
-    <t>红包</t>
-  </si>
-  <si>
-    <t>1990000_690</t>
-  </si>
-  <si>
-    <t>1990000_4350</t>
-  </si>
-  <si>
-    <t>xgfpj_props_4.png</t>
-  </si>
-  <si>
-    <t>绿色宝箱</t>
-  </si>
-  <si>
-    <t>1990000_870</t>
-  </si>
-  <si>
-    <t>xgfpj_props_2.png</t>
-  </si>
-  <si>
-    <t>两个金币</t>
-  </si>
-  <si>
-    <t>1990000_3480</t>
-  </si>
-  <si>
-    <t>1990000_1300</t>
-  </si>
-  <si>
-    <t>1990000_2610</t>
-  </si>
-  <si>
-    <t>xgfpj_props_3.png</t>
-  </si>
-  <si>
-    <t>一堆金币</t>
   </si>
   <si>
     <t>1990000_1740</t>
@@ -405,7 +384,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,24 +400,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.899990844447157"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,7 +722,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -785,16 +746,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -803,24 +764,36 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -830,40 +803,40 @@
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -872,20 +845,8 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -908,15 +869,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1258,8 +1210,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.875" style="2" customWidth="1"/>
@@ -1267,11 +1219,10 @@
     <col min="4" max="4" width="16.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.375" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1285,7 +1236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1299,7 +1250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -1313,7 +1264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
@@ -1321,11 +1272,11 @@
       </c>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="5">
         <v>101</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1334,660 +1285,553 @@
       <c r="D5" s="5">
         <v>0</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="5">
         <v>102</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="D6" s="5">
         <v>2315</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:7">
       <c r="A7" s="5">
         <v>103</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>18</v>
+      <c r="B7" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>104</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5">
         <v>1543</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>105</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>22</v>
+      <c r="B9" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D9" s="5">
         <v>31</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>106</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>25</v>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="5">
         <v>1543</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>107</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5">
         <v>1480</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>108</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>29</v>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D12" s="5">
         <v>1235</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>109</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>32</v>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="5">
         <v>556</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>110</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D14" s="5">
         <v>926</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>111</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>34</v>
+      <c r="B15" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D15" s="5">
         <v>617</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>112</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>37</v>
+      <c r="B16" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D16" s="5">
         <v>741</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F16" s="1"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
-      <c r="A17" s="9">
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="A17" s="6">
         <v>201</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>38</v>
+      <c r="B17" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="6">
         <v>0</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
-      <c r="A18" s="9">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:7">
+      <c r="A18" s="6">
         <v>202</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>29</v>
+      <c r="B18" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="9">
+        <v>15</v>
+      </c>
+      <c r="D18" s="6">
         <v>5357</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
-      <c r="A19" s="9">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:7">
+      <c r="A19" s="6">
         <v>203</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>39</v>
+      <c r="B19" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="9">
+        <v>13</v>
+      </c>
+      <c r="D19" s="6">
         <v>0</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="9">
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="6">
         <v>204</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>37</v>
+      <c r="B20" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="9">
+        <v>15</v>
+      </c>
+      <c r="D20" s="6">
         <v>2143</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="9">
+    <row r="21" spans="1:7">
+      <c r="A21" s="6">
         <v>205</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>40</v>
+      <c r="B21" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="9">
+        <v>19</v>
+      </c>
+      <c r="D21" s="6">
         <v>36</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="9">
+    <row r="22" spans="1:7">
+      <c r="A22" s="6">
         <v>206</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>34</v>
+      <c r="B22" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="9">
+        <v>15</v>
+      </c>
+      <c r="D22" s="6">
         <v>1071</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="9">
+    <row r="23" spans="1:7">
+      <c r="A23" s="6">
         <v>207</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>41</v>
+      <c r="B23" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="9">
+        <v>22</v>
+      </c>
+      <c r="D23" s="6">
         <v>107</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="9">
+    <row r="24" spans="1:7">
+      <c r="A24" s="6">
         <v>208</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>32</v>
+      <c r="B24" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="9">
+        <v>24</v>
+      </c>
+      <c r="D24" s="6">
         <v>357</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="9">
+    <row r="25" spans="1:7">
+      <c r="A25" s="6">
         <v>209</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>42</v>
+      <c r="B25" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="9">
+        <v>26</v>
+      </c>
+      <c r="D25" s="6">
         <v>179</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="9">
+    <row r="26" spans="1:7">
+      <c r="A26" s="6">
         <v>210</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>26</v>
+      <c r="B26" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="9">
+        <v>19</v>
+      </c>
+      <c r="D26" s="6">
         <v>286</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="9">
+    <row r="27" spans="1:7">
+      <c r="A27" s="6">
         <v>211</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>43</v>
+      <c r="B27" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="9">
+        <v>29</v>
+      </c>
+      <c r="D27" s="6">
         <v>214</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="9">
+    <row r="28" spans="1:7">
+      <c r="A28" s="6">
         <v>212</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>44</v>
+      <c r="B28" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="9">
+        <v>29</v>
+      </c>
+      <c r="D28" s="6">
         <v>250</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="10">
+    <row r="29" spans="1:7">
+      <c r="A29" s="7">
         <v>301</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>45</v>
+      <c r="B29" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="7">
         <v>0</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="10">
+    <row r="30" spans="1:7">
+      <c r="A30" s="7">
         <v>302</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>46</v>
+      <c r="B30" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="10">
+        <v>15</v>
+      </c>
+      <c r="D30" s="7">
         <v>2045</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="10">
+    <row r="31" spans="1:7">
+      <c r="A31" s="7">
         <v>303</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>47</v>
+      <c r="B31" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="10">
+        <v>13</v>
+      </c>
+      <c r="D31" s="7">
         <v>0</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="10">
+    <row r="32" spans="1:7">
+      <c r="A32" s="7">
         <v>304</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>29</v>
+      <c r="B32" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="10">
+        <v>15</v>
+      </c>
+      <c r="D32" s="7">
         <v>1705</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="10">
+      <c r="A33" s="7">
         <v>305</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>48</v>
+      <c r="B33" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D33" s="10">
+        <v>19</v>
+      </c>
+      <c r="D33" s="7">
         <v>114</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="10">
+      <c r="A34" s="7">
         <v>306</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>33</v>
+      <c r="B34" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="10">
+        <v>15</v>
+      </c>
+      <c r="D34" s="7">
         <v>1136</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="10">
+      <c r="A35" s="7">
         <v>307</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>42</v>
+      <c r="B35" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="10">
+        <v>22</v>
+      </c>
+      <c r="D35" s="7">
         <v>455</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="10">
+      <c r="A36" s="7">
         <v>308</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>37</v>
+      <c r="B36" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="10">
+        <v>24</v>
+      </c>
+      <c r="D36" s="7">
         <v>1136</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="10">
+      <c r="A37" s="7">
         <v>309</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>32</v>
+      <c r="B37" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="10">
+        <v>26</v>
+      </c>
+      <c r="D37" s="7">
         <v>682</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="10">
+      <c r="A38" s="7">
         <v>310</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>49</v>
+      <c r="B38" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="10">
+        <v>19</v>
+      </c>
+      <c r="D38" s="7">
         <v>1023</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="10">
+      <c r="A39" s="7">
         <v>311</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>50</v>
+      <c r="B39" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="10">
+        <v>29</v>
+      </c>
+      <c r="D39" s="7">
         <v>795</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="10">
+      <c r="A40" s="7">
         <v>312</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>34</v>
+      <c r="B40" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="10">
+        <v>29</v>
+      </c>
+      <c r="D40" s="7">
         <v>909</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,7 +97,7 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_43500</t>
+    <t>1990000_279000</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
@@ -106,7 +106,7 @@
     <t>黄金宝箱</t>
   </si>
   <si>
-    <t>1990000_170</t>
+    <t>1990000_1100</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
@@ -115,7 +115,7 @@
     <t>一个金币</t>
   </si>
   <si>
-    <t>1990000_17400</t>
+    <t>1990000_111000</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
@@ -124,10 +124,10 @@
     <t>礼物宝箱</t>
   </si>
   <si>
-    <t>1990000_520</t>
-  </si>
-  <si>
-    <t>1990000_8700</t>
+    <t>1990000_3300</t>
+  </si>
+  <si>
+    <t>1990000_55000</t>
   </si>
   <si>
     <t>xgfpj_props_5.png</t>
@@ -136,10 +136,10 @@
     <t>红包</t>
   </si>
   <si>
-    <t>1990000_690</t>
-  </si>
-  <si>
-    <t>1990000_4350</t>
+    <t>1990000_4400</t>
+  </si>
+  <si>
+    <t>1990000_27000</t>
   </si>
   <si>
     <t>xgfpj_props_4.png</t>
@@ -148,7 +148,7 @@
     <t>绿色宝箱</t>
   </si>
   <si>
-    <t>1990000_870</t>
+    <t>1990000_5500</t>
   </si>
   <si>
     <t>xgfpj_props_2.png</t>
@@ -157,13 +157,13 @@
     <t>两个金币</t>
   </si>
   <si>
-    <t>1990000_3480</t>
-  </si>
-  <si>
-    <t>1990000_1300</t>
-  </si>
-  <si>
-    <t>1990000_2610</t>
+    <t>1990000_22000</t>
+  </si>
+  <si>
+    <t>1990000_8300</t>
+  </si>
+  <si>
+    <t>1990000_16000</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
@@ -172,46 +172,76 @@
     <t>一堆金币</t>
   </si>
   <si>
-    <t>1990000_1740</t>
-  </si>
-  <si>
-    <t>1990000_261000</t>
-  </si>
-  <si>
-    <t>1990000_87000</t>
-  </si>
-  <si>
-    <t>1990000_26100</t>
-  </si>
-  <si>
-    <t>1990000_13920</t>
-  </si>
-  <si>
-    <t>1990000_6960</t>
-  </si>
-  <si>
-    <t>1990000_6090</t>
-  </si>
-  <si>
-    <t>1990000_5220</t>
-  </si>
-  <si>
-    <t>1990000_174000</t>
-  </si>
-  <si>
-    <t>1990000_430</t>
-  </si>
-  <si>
-    <t>1990000_60900</t>
-  </si>
-  <si>
-    <t>1990000_13050</t>
-  </si>
-  <si>
-    <t>1990000_2170</t>
-  </si>
-  <si>
-    <t>1990000_3040</t>
+    <t>1990000_11000</t>
+  </si>
+  <si>
+    <t>1990000_1354000</t>
+  </si>
+  <si>
+    <t>1990000_4500</t>
+  </si>
+  <si>
+    <t>1990000_451000</t>
+  </si>
+  <si>
+    <t>1990000_9000</t>
+  </si>
+  <si>
+    <t>1990000_135000</t>
+  </si>
+  <si>
+    <t>1990000_13500</t>
+  </si>
+  <si>
+    <t>1990000_72000</t>
+  </si>
+  <si>
+    <t>1990000_18000</t>
+  </si>
+  <si>
+    <t>1990000_36000</t>
+  </si>
+  <si>
+    <t>1990000_22500</t>
+  </si>
+  <si>
+    <t>1990000_31000</t>
+  </si>
+  <si>
+    <t>1990000_639000</t>
+  </si>
+  <si>
+    <t>1990000_2100</t>
+  </si>
+  <si>
+    <t>1990000_213000</t>
+  </si>
+  <si>
+    <t>1990000_4200</t>
+  </si>
+  <si>
+    <t>1990000_63000</t>
+  </si>
+  <si>
+    <t>1990000_6300</t>
+  </si>
+  <si>
+    <t>1990000_34000</t>
+  </si>
+  <si>
+    <t>1990000_8500</t>
+  </si>
+  <si>
+    <t>1990000_17000</t>
+  </si>
+  <si>
+    <t>1990000_10600</t>
+  </si>
+  <si>
+    <t>1990000_14000</t>
+  </si>
+  <si>
+    <t>1990000_12700</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1381,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="5">
-        <v>2315</v>
+        <v>2362</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1389,7 +1419,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="5">
-        <v>1543</v>
+        <v>1890</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>17</v>
@@ -1407,7 +1437,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>24</v>
@@ -1425,7 +1455,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="5">
-        <v>1543</v>
+        <v>1575</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>17</v>
@@ -1443,7 +1473,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="5">
-        <v>1480</v>
+        <v>157</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>28</v>
@@ -1461,7 +1491,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="5">
-        <v>1235</v>
+        <v>1260</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>31</v>
@@ -1479,7 +1509,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="5">
-        <v>556</v>
+        <v>472</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>28</v>
@@ -1497,7 +1527,7 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>31</v>
@@ -1515,7 +1545,7 @@
         <v>35</v>
       </c>
       <c r="D15" s="5">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>36</v>
@@ -1533,7 +1563,7 @@
         <v>35</v>
       </c>
       <c r="D16" s="5">
-        <v>741</v>
+        <v>709</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>36</v>
@@ -1564,7 +1594,7 @@
         <v>202</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
@@ -1581,7 +1611,7 @@
         <v>203</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>19</v>
@@ -1598,7 +1628,7 @@
         <v>204</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
@@ -1617,7 +1647,7 @@
         <v>205</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>23</v>
@@ -1636,7 +1666,7 @@
         <v>206</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>16</v>
@@ -1655,7 +1685,7 @@
         <v>207</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>27</v>
@@ -1674,7 +1704,7 @@
         <v>208</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>30</v>
@@ -1693,7 +1723,7 @@
         <v>209</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>27</v>
@@ -1712,7 +1742,7 @@
         <v>210</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>30</v>
@@ -1731,7 +1761,7 @@
         <v>211</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>35</v>
@@ -1750,7 +1780,7 @@
         <v>212</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>35</v>
@@ -1769,7 +1799,7 @@
         <v>301</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
@@ -1788,7 +1818,7 @@
         <v>302</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>16</v>
@@ -1807,7 +1837,7 @@
         <v>303</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>19</v>
@@ -1826,7 +1856,7 @@
         <v>304</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>16</v>
@@ -1845,7 +1875,7 @@
         <v>305</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>23</v>
@@ -1864,7 +1894,7 @@
         <v>306</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>16</v>
@@ -1883,7 +1913,7 @@
         <v>307</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>27</v>
@@ -1902,7 +1932,7 @@
         <v>308</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>30</v>
@@ -1921,7 +1951,7 @@
         <v>309</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>27</v>
@@ -1940,7 +1970,7 @@
         <v>310</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>30</v>
@@ -1959,7 +1989,7 @@
         <v>311</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>35</v>
@@ -1978,7 +2008,7 @@
         <v>312</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>35</v>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,100 +97,151 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_43500</t>
+    <t>1990000_279000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_7.png</t>
+  </si>
+  <si>
+    <t>黄金宝箱</t>
+  </si>
+  <si>
+    <t>1990000_1100</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
   </si>
   <si>
-    <t>1990000_170</t>
+    <t>一个金币</t>
+  </si>
+  <si>
+    <t>1990000_111000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_6.png</t>
+  </si>
+  <si>
+    <t>礼物宝箱</t>
+  </si>
+  <si>
+    <t>1990000_3300</t>
+  </si>
+  <si>
+    <t>1990000_55000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_5.png</t>
+  </si>
+  <si>
+    <t>红包</t>
+  </si>
+  <si>
+    <t>1990000_4400</t>
+  </si>
+  <si>
+    <t>1990000_27000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_4.png</t>
+  </si>
+  <si>
+    <t>绿色宝箱</t>
+  </si>
+  <si>
+    <t>1990000_5500</t>
+  </si>
+  <si>
+    <t>xgfpj_props_2.png</t>
+  </si>
+  <si>
+    <t>两个金币</t>
+  </si>
+  <si>
+    <t>1990000_22000</t>
+  </si>
+  <si>
+    <t>1990000_8300</t>
+  </si>
+  <si>
+    <t>1990000_16000</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
   </si>
   <si>
-    <t>1990000_17400</t>
-  </si>
-  <si>
-    <t>1990000_520</t>
-  </si>
-  <si>
-    <t>1990000_8700</t>
-  </si>
-  <si>
-    <t>xgfpj_props_5.png</t>
-  </si>
-  <si>
-    <t>1990000_690</t>
-  </si>
-  <si>
-    <t>1990000_4350</t>
-  </si>
-  <si>
-    <t>xgfpj_props_2.png</t>
-  </si>
-  <si>
-    <t>1990000_870</t>
-  </si>
-  <si>
-    <t>xgfpj_props_4.png</t>
-  </si>
-  <si>
-    <t>1990000_3480</t>
-  </si>
-  <si>
-    <t>xgfpj_props_6.png</t>
-  </si>
-  <si>
-    <t>1990000_1300</t>
-  </si>
-  <si>
-    <t>1990000_2610</t>
-  </si>
-  <si>
-    <t>xgfpj_props_7.png</t>
-  </si>
-  <si>
-    <t>1990000_1740</t>
-  </si>
-  <si>
-    <t>1990000_261000</t>
-  </si>
-  <si>
-    <t>1990000_87000</t>
-  </si>
-  <si>
-    <t>1990000_26100</t>
-  </si>
-  <si>
-    <t>1990000_13920</t>
-  </si>
-  <si>
-    <t>1990000_6960</t>
-  </si>
-  <si>
-    <t>1990000_6090</t>
-  </si>
-  <si>
-    <t>1990000_5220</t>
-  </si>
-  <si>
-    <t>1990000_174000</t>
-  </si>
-  <si>
-    <t>1990000_430</t>
-  </si>
-  <si>
-    <t>1990000_60900</t>
-  </si>
-  <si>
-    <t>1990000_13050</t>
-  </si>
-  <si>
-    <t>1990000_2170</t>
-  </si>
-  <si>
-    <t>1990000_3040</t>
+    <t>一堆金币</t>
+  </si>
+  <si>
+    <t>1990000_11000</t>
+  </si>
+  <si>
+    <t>1990000_1354000</t>
+  </si>
+  <si>
+    <t>1990000_4500</t>
+  </si>
+  <si>
+    <t>1990000_451000</t>
+  </si>
+  <si>
+    <t>1990000_9000</t>
+  </si>
+  <si>
+    <t>1990000_135000</t>
+  </si>
+  <si>
+    <t>1990000_13500</t>
+  </si>
+  <si>
+    <t>1990000_72000</t>
+  </si>
+  <si>
+    <t>1990000_18000</t>
+  </si>
+  <si>
+    <t>1990000_36000</t>
+  </si>
+  <si>
+    <t>1990000_22500</t>
+  </si>
+  <si>
+    <t>1990000_31000</t>
+  </si>
+  <si>
+    <t>1990000_639000</t>
+  </si>
+  <si>
+    <t>1990000_2100</t>
+  </si>
+  <si>
+    <t>1990000_213000</t>
+  </si>
+  <si>
+    <t>1990000_4200</t>
+  </si>
+  <si>
+    <t>1990000_63000</t>
+  </si>
+  <si>
+    <t>1990000_6300</t>
+  </si>
+  <si>
+    <t>1990000_34000</t>
+  </si>
+  <si>
+    <t>1990000_8500</t>
+  </si>
+  <si>
+    <t>1990000_17000</t>
+  </si>
+  <si>
+    <t>1990000_10600</t>
+  </si>
+  <si>
+    <t>1990000_14000</t>
+  </si>
+  <si>
+    <t>1990000_12700</t>
   </si>
 </sst>
 </file>
@@ -384,7 +435,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,6 +451,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.899990844447157"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,7 +791,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -746,16 +815,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -764,79 +833,67 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -845,8 +902,20 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -869,6 +938,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,8 +1288,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.875" style="2" customWidth="1"/>
@@ -1219,10 +1297,11 @@
     <col min="4" max="4" width="16.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.25" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="19.375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1236,7 +1315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1250,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -1264,7 +1343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
@@ -1272,11 +1351,11 @@
       </c>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="5">
         <v>101</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1285,553 +1364,660 @@
       <c r="D5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="5">
         <v>102</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>14</v>
+      <c r="B6" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="5">
-        <v>2315</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
+        <v>2362</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="5">
         <v>103</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
+      <c r="B7" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="5">
         <v>104</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1890</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1543</v>
-      </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7">
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="5">
         <v>105</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7">
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="5">
         <v>106</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>20</v>
+      <c r="B10" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="5">
-        <v>1543</v>
+        <v>1575</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7">
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="5">
         <v>107</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
+      <c r="B11" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D11" s="5">
-        <v>1480</v>
+        <v>157</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7">
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="5">
         <v>108</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
+      <c r="B12" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5">
-        <v>1235</v>
+        <v>1260</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7">
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="5">
         <v>109</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
+      <c r="B13" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="5">
-        <v>556</v>
+        <v>472</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7">
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="5">
         <v>110</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>27</v>
+      <c r="B14" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>926</v>
+        <v>945</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7">
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="5">
         <v>111</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>28</v>
+      <c r="B15" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5">
-        <v>617</v>
+        <v>630</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7">
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="5">
         <v>112</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>30</v>
+      <c r="B16" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5">
-        <v>741</v>
+        <v>709</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:7">
-      <c r="A17" s="6">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:8">
+      <c r="A17" s="9">
         <v>201</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>31</v>
+      <c r="B17" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:7">
-      <c r="A18" s="6">
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:8">
+      <c r="A18" s="9">
         <v>202</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>23</v>
+      <c r="B18" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="6">
+        <v>16</v>
+      </c>
+      <c r="D18" s="9">
         <v>5357</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:7">
-      <c r="A19" s="6">
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:8">
+      <c r="A19" s="9">
         <v>203</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>32</v>
+      <c r="B19" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="6">
+        <v>19</v>
+      </c>
+      <c r="D19" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="6">
+      <c r="E19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="9">
         <v>204</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>30</v>
+      <c r="B20" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="6">
+        <v>16</v>
+      </c>
+      <c r="D20" s="9">
         <v>2143</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="6">
+    <row r="21" spans="1:8">
+      <c r="A21" s="9">
         <v>205</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>33</v>
+      <c r="B21" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="6">
+        <v>23</v>
+      </c>
+      <c r="D21" s="9">
         <v>36</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="6">
+    <row r="22" spans="1:8">
+      <c r="A22" s="9">
         <v>206</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>28</v>
+      <c r="B22" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="6">
+        <v>16</v>
+      </c>
+      <c r="D22" s="9">
         <v>1071</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="6">
+    <row r="23" spans="1:8">
+      <c r="A23" s="9">
         <v>207</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>34</v>
+      <c r="B23" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="6">
+        <v>27</v>
+      </c>
+      <c r="D23" s="9">
         <v>107</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="6">
+    <row r="24" spans="1:8">
+      <c r="A24" s="9">
         <v>208</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>25</v>
+      <c r="B24" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="6">
+        <v>30</v>
+      </c>
+      <c r="D24" s="9">
         <v>357</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="6">
+    <row r="25" spans="1:8">
+      <c r="A25" s="9">
         <v>209</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>35</v>
+      <c r="B25" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="6">
+        <v>27</v>
+      </c>
+      <c r="D25" s="9">
         <v>179</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="6">
+    <row r="26" spans="1:8">
+      <c r="A26" s="9">
         <v>210</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>21</v>
+      <c r="B26" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="6">
+        <v>30</v>
+      </c>
+      <c r="D26" s="9">
         <v>286</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="6">
+    <row r="27" spans="1:8">
+      <c r="A27" s="9">
         <v>211</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="9">
+        <v>214</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="6">
-        <v>214</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="6">
+    <row r="28" spans="1:8">
+      <c r="A28" s="9">
         <v>212</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>37</v>
+      <c r="B28" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="6">
+        <v>35</v>
+      </c>
+      <c r="D28" s="9">
         <v>250</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="7">
+    <row r="29" spans="1:8">
+      <c r="A29" s="10">
         <v>301</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>38</v>
+      <c r="B29" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="10">
         <v>0</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="7">
+    <row r="30" spans="1:8">
+      <c r="A30" s="10">
         <v>302</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>39</v>
+      <c r="B30" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="7">
+        <v>16</v>
+      </c>
+      <c r="D30" s="10">
         <v>2045</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="7">
+    <row r="31" spans="1:8">
+      <c r="A31" s="10">
         <v>303</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>40</v>
+      <c r="B31" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="7">
+        <v>19</v>
+      </c>
+      <c r="D31" s="10">
         <v>0</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="7">
+    <row r="32" spans="1:8">
+      <c r="A32" s="10">
         <v>304</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>23</v>
+      <c r="B32" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="7">
+        <v>16</v>
+      </c>
+      <c r="D32" s="10">
         <v>1705</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="7">
+      <c r="A33" s="10">
         <v>305</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>41</v>
+      <c r="B33" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="7">
+        <v>23</v>
+      </c>
+      <c r="D33" s="10">
         <v>114</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="7">
+      <c r="A34" s="10">
         <v>306</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>27</v>
+      <c r="B34" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="7">
+        <v>16</v>
+      </c>
+      <c r="D34" s="10">
         <v>1136</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="7">
+      <c r="A35" s="10">
         <v>307</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>35</v>
+      <c r="B35" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="7">
+        <v>27</v>
+      </c>
+      <c r="D35" s="10">
         <v>455</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="7">
+      <c r="A36" s="10">
         <v>308</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="D36" s="10">
         <v>1136</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="7">
+      <c r="A37" s="10">
         <v>309</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>25</v>
+      <c r="B37" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="7">
+        <v>27</v>
+      </c>
+      <c r="D37" s="10">
         <v>682</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="7">
+      <c r="A38" s="10">
         <v>310</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>42</v>
+      <c r="B38" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="7">
+        <v>30</v>
+      </c>
+      <c r="D38" s="10">
         <v>1023</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="7">
+      <c r="A39" s="10">
         <v>311</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>43</v>
+      <c r="B39" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="7">
+        <v>35</v>
+      </c>
+      <c r="D39" s="10">
         <v>795</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="7">
+      <c r="A40" s="10">
         <v>312</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>28</v>
+      <c r="B40" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="7">
+        <v>35</v>
+      </c>
+      <c r="D40" s="10">
         <v>909</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="OfficialAwards" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="59">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,7 +97,7 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_279000</t>
+    <t>1990000_334000</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
@@ -106,7 +106,7 @@
     <t>黄金宝箱</t>
   </si>
   <si>
-    <t>1990000_1100</t>
+    <t>1990000_3000</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
@@ -115,7 +115,7 @@
     <t>一个金币</t>
   </si>
   <si>
-    <t>1990000_111000</t>
+    <t>1990000_204000</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
@@ -124,10 +124,10 @@
     <t>礼物宝箱</t>
   </si>
   <si>
-    <t>1990000_3300</t>
-  </si>
-  <si>
-    <t>1990000_55000</t>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>1990000_152000</t>
   </si>
   <si>
     <t>xgfpj_props_5.png</t>
@@ -136,34 +136,34 @@
     <t>红包</t>
   </si>
   <si>
-    <t>1990000_4400</t>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>1990000_90000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_4.png</t>
+  </si>
+  <si>
+    <t>绿色宝箱</t>
+  </si>
+  <si>
+    <t>1990000_18000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_2.png</t>
+  </si>
+  <si>
+    <t>两个金币</t>
+  </si>
+  <si>
+    <t>1990000_72000</t>
   </si>
   <si>
     <t>1990000_27000</t>
   </si>
   <si>
-    <t>xgfpj_props_4.png</t>
-  </si>
-  <si>
-    <t>绿色宝箱</t>
-  </si>
-  <si>
-    <t>1990000_5500</t>
-  </si>
-  <si>
-    <t>xgfpj_props_2.png</t>
-  </si>
-  <si>
-    <t>两个金币</t>
-  </si>
-  <si>
-    <t>1990000_22000</t>
-  </si>
-  <si>
-    <t>1990000_8300</t>
-  </si>
-  <si>
-    <t>1990000_16000</t>
+    <t>1990000_53000</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
@@ -172,76 +172,70 @@
     <t>一堆金币</t>
   </si>
   <si>
-    <t>1990000_11000</t>
-  </si>
-  <si>
-    <t>1990000_1354000</t>
-  </si>
-  <si>
-    <t>1990000_4500</t>
-  </si>
-  <si>
-    <t>1990000_451000</t>
+    <t>1990000_36000</t>
+  </si>
+  <si>
+    <t>1990000_459000</t>
+  </si>
+  <si>
+    <t>1990000_325000</t>
   </si>
   <si>
     <t>1990000_9000</t>
   </si>
   <si>
-    <t>1990000_135000</t>
-  </si>
-  <si>
-    <t>1990000_13500</t>
-  </si>
-  <si>
-    <t>1990000_72000</t>
-  </si>
-  <si>
-    <t>1990000_18000</t>
-  </si>
-  <si>
-    <t>1990000_36000</t>
-  </si>
-  <si>
-    <t>1990000_22500</t>
-  </si>
-  <si>
-    <t>1990000_31000</t>
-  </si>
-  <si>
-    <t>1990000_639000</t>
-  </si>
-  <si>
-    <t>1990000_2100</t>
-  </si>
-  <si>
-    <t>1990000_213000</t>
-  </si>
-  <si>
-    <t>1990000_4200</t>
-  </si>
-  <si>
-    <t>1990000_63000</t>
-  </si>
-  <si>
-    <t>1990000_6300</t>
-  </si>
-  <si>
-    <t>1990000_34000</t>
-  </si>
-  <si>
-    <t>1990000_8500</t>
-  </si>
-  <si>
-    <t>1990000_17000</t>
-  </si>
-  <si>
-    <t>1990000_10600</t>
-  </si>
-  <si>
-    <t>1990000_14000</t>
-  </si>
-  <si>
-    <t>1990000_12700</t>
+    <t>1990000_242000</t>
+  </si>
+  <si>
+    <t>1990000_15000</t>
+  </si>
+  <si>
+    <t>1990000_144000</t>
+  </si>
+  <si>
+    <t>1990000_28000</t>
+  </si>
+  <si>
+    <t>1990000_115000</t>
+  </si>
+  <si>
+    <t>1990000_43000</t>
+  </si>
+  <si>
+    <t>1990000_85000</t>
+  </si>
+  <si>
+    <t>1990000_57000</t>
+  </si>
+  <si>
+    <t>1990000_356000</t>
+  </si>
+  <si>
+    <t>1990000_4000</t>
+  </si>
+  <si>
+    <t>1990000_277000</t>
+  </si>
+  <si>
+    <t>1990000_7000</t>
+  </si>
+  <si>
+    <t>1990000_206000</t>
+  </si>
+  <si>
+    <t>1990000_13000</t>
+  </si>
+  <si>
+    <t>1990000_123000</t>
+  </si>
+  <si>
+    <t>1990000_24000</t>
+  </si>
+  <si>
+    <t>1990000_98000</t>
+  </si>
+  <si>
+    <t>1990000_49000</t>
   </si>
 </sst>
 </file>
@@ -1594,13 +1588,13 @@
         <v>202</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="9">
-        <v>5357</v>
+        <v>2362</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -1611,7 +1605,7 @@
         <v>203</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>19</v>
@@ -1628,13 +1622,13 @@
         <v>204</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="9">
-        <v>2143</v>
+        <v>1890</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>17</v>
@@ -1647,13 +1641,13 @@
         <v>205</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>24</v>
@@ -1666,13 +1660,13 @@
         <v>206</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="9">
-        <v>1071</v>
+        <v>1575</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>17</v>
@@ -1685,13 +1679,13 @@
         <v>207</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="9">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>28</v>
@@ -1704,13 +1698,13 @@
         <v>208</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="9">
-        <v>357</v>
+        <v>1260</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>31</v>
@@ -1723,13 +1717,13 @@
         <v>209</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="9">
-        <v>179</v>
+        <v>472</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>28</v>
@@ -1742,13 +1736,13 @@
         <v>210</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D26" s="9">
-        <v>286</v>
+        <v>945</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>31</v>
@@ -1761,13 +1755,13 @@
         <v>211</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D27" s="9">
-        <v>214</v>
+        <v>630</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>36</v>
@@ -1780,13 +1774,13 @@
         <v>212</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="9">
-        <v>250</v>
+        <v>709</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
@@ -1824,7 +1818,7 @@
         <v>16</v>
       </c>
       <c r="D30" s="10">
-        <v>2045</v>
+        <v>2362</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>17</v>
@@ -1862,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="D32" s="10">
-        <v>1705</v>
+        <v>1890</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>17</v>
@@ -1881,7 +1875,7 @@
         <v>23</v>
       </c>
       <c r="D33" s="10">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>24</v>
@@ -1900,7 +1894,7 @@
         <v>16</v>
       </c>
       <c r="D34" s="10">
-        <v>1136</v>
+        <v>1575</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>17</v>
@@ -1919,7 +1913,7 @@
         <v>27</v>
       </c>
       <c r="D35" s="10">
-        <v>455</v>
+        <v>157</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>28</v>
@@ -1938,7 +1932,7 @@
         <v>30</v>
       </c>
       <c r="D36" s="10">
-        <v>1136</v>
+        <v>1260</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>31</v>
@@ -1957,7 +1951,7 @@
         <v>27</v>
       </c>
       <c r="D37" s="10">
-        <v>682</v>
+        <v>472</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>28</v>
@@ -1970,13 +1964,13 @@
         <v>310</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="10">
-        <v>1023</v>
+        <v>945</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>31</v>
@@ -1989,13 +1983,13 @@
         <v>311</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D39" s="10">
-        <v>795</v>
+        <v>630</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>36</v>
@@ -2008,13 +2002,13 @@
         <v>312</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="10">
-        <v>909</v>
+        <v>709</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>36</v>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="OfficialAwards" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,7 +97,7 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_334000</t>
+    <t>1990000_279000</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
@@ -106,7 +106,7 @@
     <t>黄金宝箱</t>
   </si>
   <si>
-    <t>1990000_3000</t>
+    <t>1990000_1100</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
@@ -115,7 +115,7 @@
     <t>一个金币</t>
   </si>
   <si>
-    <t>1990000_204000</t>
+    <t>1990000_111000</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
@@ -124,10 +124,10 @@
     <t>礼物宝箱</t>
   </si>
   <si>
-    <t>1990000_5000</t>
-  </si>
-  <si>
-    <t>1990000_152000</t>
+    <t>1990000_3300</t>
+  </si>
+  <si>
+    <t>1990000_55000</t>
   </si>
   <si>
     <t>xgfpj_props_5.png</t>
@@ -136,10 +136,10 @@
     <t>红包</t>
   </si>
   <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1990000_90000</t>
+    <t>1990000_4400</t>
+  </si>
+  <si>
+    <t>1990000_27000</t>
   </si>
   <si>
     <t>xgfpj_props_4.png</t>
@@ -148,94 +148,100 @@
     <t>绿色宝箱</t>
   </si>
   <si>
+    <t>1990000_5500</t>
+  </si>
+  <si>
+    <t>xgfpj_props_2.png</t>
+  </si>
+  <si>
+    <t>两个金币</t>
+  </si>
+  <si>
+    <t>1990000_22000</t>
+  </si>
+  <si>
+    <t>1990000_8300</t>
+  </si>
+  <si>
+    <t>1990000_16000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_3.png</t>
+  </si>
+  <si>
+    <t>一堆金币</t>
+  </si>
+  <si>
+    <t>1990000_11000</t>
+  </si>
+  <si>
+    <t>1990000_1354000</t>
+  </si>
+  <si>
+    <t>1990000_4500</t>
+  </si>
+  <si>
+    <t>1990000_451000</t>
+  </si>
+  <si>
+    <t>1990000_9000</t>
+  </si>
+  <si>
+    <t>1990000_135000</t>
+  </si>
+  <si>
+    <t>1990000_13500</t>
+  </si>
+  <si>
+    <t>1990000_72000</t>
+  </si>
+  <si>
     <t>1990000_18000</t>
   </si>
   <si>
-    <t>xgfpj_props_2.png</t>
-  </si>
-  <si>
-    <t>两个金币</t>
-  </si>
-  <si>
-    <t>1990000_72000</t>
-  </si>
-  <si>
-    <t>1990000_27000</t>
-  </si>
-  <si>
-    <t>1990000_53000</t>
-  </si>
-  <si>
-    <t>xgfpj_props_3.png</t>
-  </si>
-  <si>
-    <t>一堆金币</t>
-  </si>
-  <si>
     <t>1990000_36000</t>
   </si>
   <si>
-    <t>1990000_459000</t>
-  </si>
-  <si>
-    <t>1990000_325000</t>
-  </si>
-  <si>
-    <t>1990000_9000</t>
-  </si>
-  <si>
-    <t>1990000_242000</t>
-  </si>
-  <si>
-    <t>1990000_15000</t>
-  </si>
-  <si>
-    <t>1990000_144000</t>
-  </si>
-  <si>
-    <t>1990000_28000</t>
-  </si>
-  <si>
-    <t>1990000_115000</t>
-  </si>
-  <si>
-    <t>1990000_43000</t>
-  </si>
-  <si>
-    <t>1990000_85000</t>
-  </si>
-  <si>
-    <t>1990000_57000</t>
-  </si>
-  <si>
-    <t>1990000_356000</t>
-  </si>
-  <si>
-    <t>1990000_4000</t>
-  </si>
-  <si>
-    <t>1990000_277000</t>
-  </si>
-  <si>
-    <t>1990000_7000</t>
-  </si>
-  <si>
-    <t>1990000_206000</t>
-  </si>
-  <si>
-    <t>1990000_13000</t>
-  </si>
-  <si>
-    <t>1990000_123000</t>
-  </si>
-  <si>
-    <t>1990000_24000</t>
-  </si>
-  <si>
-    <t>1990000_98000</t>
-  </si>
-  <si>
-    <t>1990000_49000</t>
+    <t>1990000_22500</t>
+  </si>
+  <si>
+    <t>1990000_31000</t>
+  </si>
+  <si>
+    <t>1990000_639000</t>
+  </si>
+  <si>
+    <t>1990000_2100</t>
+  </si>
+  <si>
+    <t>1990000_213000</t>
+  </si>
+  <si>
+    <t>1990000_4200</t>
+  </si>
+  <si>
+    <t>1990000_63000</t>
+  </si>
+  <si>
+    <t>1990000_6300</t>
+  </si>
+  <si>
+    <t>1990000_34000</t>
+  </si>
+  <si>
+    <t>1990000_8500</t>
+  </si>
+  <si>
+    <t>1990000_17000</t>
+  </si>
+  <si>
+    <t>1990000_10600</t>
+  </si>
+  <si>
+    <t>1990000_14000</t>
+  </si>
+  <si>
+    <t>1990000_12700</t>
   </si>
 </sst>
 </file>
@@ -1588,13 +1594,13 @@
         <v>202</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="9">
-        <v>2362</v>
+        <v>5357</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -1605,7 +1611,7 @@
         <v>203</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>19</v>
@@ -1622,13 +1628,13 @@
         <v>204</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="9">
-        <v>1890</v>
+        <v>2143</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>17</v>
@@ -1641,13 +1647,13 @@
         <v>205</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>24</v>
@@ -1660,13 +1666,13 @@
         <v>206</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="9">
-        <v>1575</v>
+        <v>1071</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>17</v>
@@ -1679,13 +1685,13 @@
         <v>207</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="9">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>28</v>
@@ -1698,13 +1704,13 @@
         <v>208</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="9">
-        <v>1260</v>
+        <v>357</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>31</v>
@@ -1717,13 +1723,13 @@
         <v>209</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="9">
-        <v>472</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>28</v>
@@ -1736,13 +1742,13 @@
         <v>210</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D26" s="9">
-        <v>945</v>
+        <v>286</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>31</v>
@@ -1755,13 +1761,13 @@
         <v>211</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D27" s="9">
-        <v>630</v>
+        <v>214</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>36</v>
@@ -1774,13 +1780,13 @@
         <v>212</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="9">
-        <v>709</v>
+        <v>250</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
@@ -1818,7 +1824,7 @@
         <v>16</v>
       </c>
       <c r="D30" s="10">
-        <v>2362</v>
+        <v>2045</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>17</v>
@@ -1856,7 +1862,7 @@
         <v>16</v>
       </c>
       <c r="D32" s="10">
-        <v>1890</v>
+        <v>1705</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>17</v>
@@ -1875,7 +1881,7 @@
         <v>23</v>
       </c>
       <c r="D33" s="10">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>24</v>
@@ -1894,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="D34" s="10">
-        <v>1575</v>
+        <v>1136</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>17</v>
@@ -1913,7 +1919,7 @@
         <v>27</v>
       </c>
       <c r="D35" s="10">
-        <v>157</v>
+        <v>455</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>28</v>
@@ -1932,7 +1938,7 @@
         <v>30</v>
       </c>
       <c r="D36" s="10">
-        <v>1260</v>
+        <v>1136</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>31</v>
@@ -1951,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="D37" s="10">
-        <v>472</v>
+        <v>682</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>28</v>
@@ -1964,13 +1970,13 @@
         <v>310</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="10">
-        <v>945</v>
+        <v>1023</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>31</v>
@@ -1983,13 +1989,13 @@
         <v>311</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D39" s="10">
-        <v>630</v>
+        <v>795</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>36</v>
@@ -2002,13 +2008,13 @@
         <v>312</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="10">
-        <v>709</v>
+        <v>909</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>36</v>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -97,7 +97,7 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_334000</t>
+    <t>1990000_272000</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
@@ -106,7 +106,7 @@
     <t>黄金宝箱</t>
   </si>
   <si>
-    <t>1990000_3000</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
@@ -115,7 +115,7 @@
     <t>一个金币</t>
   </si>
   <si>
-    <t>1990000_204000</t>
+    <t>1990000_166000</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
@@ -124,60 +124,63 @@
     <t>礼物宝箱</t>
   </si>
   <si>
+    <t>1990000_4000</t>
+  </si>
+  <si>
+    <t>1990000_124000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_5.png</t>
+  </si>
+  <si>
+    <t>红包</t>
+  </si>
+  <si>
+    <t>1990000_8000</t>
+  </si>
+  <si>
+    <t>1990000_74000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_4.png</t>
+  </si>
+  <si>
+    <t>绿色宝箱</t>
+  </si>
+  <si>
+    <t>1990000_14000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_2.png</t>
+  </si>
+  <si>
+    <t>两个金币</t>
+  </si>
+  <si>
+    <t>1990000_59000</t>
+  </si>
+  <si>
+    <t>1990000_22000</t>
+  </si>
+  <si>
+    <t>1990000_43000</t>
+  </si>
+  <si>
+    <t>xgfpj_props_3.png</t>
+  </si>
+  <si>
+    <t>一堆金币</t>
+  </si>
+  <si>
+    <t>1990000_29000</t>
+  </si>
+  <si>
+    <t>1990000_458000</t>
+  </si>
+  <si>
     <t>1990000_5000</t>
   </si>
   <si>
-    <t>1990000_152000</t>
-  </si>
-  <si>
-    <t>xgfpj_props_5.png</t>
-  </si>
-  <si>
-    <t>红包</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1990000_90000</t>
-  </si>
-  <si>
-    <t>xgfpj_props_4.png</t>
-  </si>
-  <si>
-    <t>绿色宝箱</t>
-  </si>
-  <si>
-    <t>1990000_18000</t>
-  </si>
-  <si>
-    <t>xgfpj_props_2.png</t>
-  </si>
-  <si>
-    <t>两个金币</t>
-  </si>
-  <si>
-    <t>1990000_72000</t>
-  </si>
-  <si>
-    <t>1990000_27000</t>
-  </si>
-  <si>
-    <t>1990000_53000</t>
-  </si>
-  <si>
-    <t>xgfpj_props_3.png</t>
-  </si>
-  <si>
-    <t>一堆金币</t>
-  </si>
-  <si>
-    <t>1990000_36000</t>
-  </si>
-  <si>
-    <t>1990000_459000</t>
-  </si>
-  <si>
     <t>1990000_325000</t>
   </si>
   <si>
@@ -199,43 +202,40 @@
     <t>1990000_115000</t>
   </si>
   <si>
-    <t>1990000_43000</t>
-  </si>
-  <si>
     <t>1990000_85000</t>
   </si>
   <si>
     <t>1990000_57000</t>
   </si>
   <si>
-    <t>1990000_356000</t>
-  </si>
-  <si>
-    <t>1990000_4000</t>
-  </si>
-  <si>
-    <t>1990000_277000</t>
+    <t>1990000_316000</t>
+  </si>
+  <si>
+    <t>1990000_246000</t>
   </si>
   <si>
     <t>1990000_7000</t>
   </si>
   <si>
-    <t>1990000_206000</t>
-  </si>
-  <si>
-    <t>1990000_13000</t>
-  </si>
-  <si>
-    <t>1990000_123000</t>
-  </si>
-  <si>
-    <t>1990000_24000</t>
-  </si>
-  <si>
-    <t>1990000_98000</t>
-  </si>
-  <si>
-    <t>1990000_49000</t>
+    <t>1990000_183000</t>
+  </si>
+  <si>
+    <t>1990000_12000</t>
+  </si>
+  <si>
+    <t>1990000_109000</t>
+  </si>
+  <si>
+    <t>1990000_21000</t>
+  </si>
+  <si>
+    <t>1990000_87000</t>
+  </si>
+  <si>
+    <t>1990000_32000</t>
+  </si>
+  <si>
+    <t>1990000_64000</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1588,7 @@
         <v>202</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
@@ -1605,7 +1605,7 @@
         <v>203</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>19</v>
@@ -1622,7 +1622,7 @@
         <v>204</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
@@ -1641,7 +1641,7 @@
         <v>205</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>23</v>
@@ -1660,7 +1660,7 @@
         <v>206</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>16</v>
@@ -1679,7 +1679,7 @@
         <v>207</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>27</v>
@@ -1698,7 +1698,7 @@
         <v>208</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>30</v>
@@ -1717,7 +1717,7 @@
         <v>209</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>27</v>
@@ -1736,7 +1736,7 @@
         <v>210</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>30</v>
@@ -1812,7 +1812,7 @@
         <v>302</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>16</v>
@@ -1831,7 +1831,7 @@
         <v>303</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>19</v>
@@ -1850,7 +1850,7 @@
         <v>304</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>16</v>
@@ -1869,7 +1869,7 @@
         <v>305</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>23</v>
@@ -1888,7 +1888,7 @@
         <v>306</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>16</v>
@@ -1907,7 +1907,7 @@
         <v>307</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>27</v>
@@ -1926,7 +1926,7 @@
         <v>308</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>30</v>
@@ -1945,7 +1945,7 @@
         <v>309</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>27</v>
@@ -1964,7 +1964,7 @@
         <v>310</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>30</v>
@@ -1983,7 +1983,7 @@
         <v>311</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>35</v>
@@ -2002,7 +2002,7 @@
         <v>312</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>35</v>

--- a/slots/resources/sample/OfficialAwards.xlsx
+++ b/slots/resources/sample/OfficialAwards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="OfficialAwards" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="59">
   <si>
     <t>序列ID</t>
   </si>
@@ -97,7 +97,7 @@
     <t>client</t>
   </si>
   <si>
-    <t>1990000_279000</t>
+    <t>1990000_272000</t>
   </si>
   <si>
     <t>xgfpj_props_7.png</t>
@@ -106,7 +106,7 @@
     <t>黄金宝箱</t>
   </si>
   <si>
-    <t>1990000_1100</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>xgfpj_props_1.png</t>
@@ -115,7 +115,7 @@
     <t>一个金币</t>
   </si>
   <si>
-    <t>1990000_111000</t>
+    <t>1990000_166000</t>
   </si>
   <si>
     <t>xgfpj_props_6.png</t>
@@ -124,10 +124,10 @@
     <t>礼物宝箱</t>
   </si>
   <si>
-    <t>1990000_3300</t>
-  </si>
-  <si>
-    <t>1990000_55000</t>
+    <t>1990000_4000</t>
+  </si>
+  <si>
+    <t>1990000_124000</t>
   </si>
   <si>
     <t>xgfpj_props_5.png</t>
@@ -136,10 +136,10 @@
     <t>红包</t>
   </si>
   <si>
-    <t>1990000_4400</t>
-  </si>
-  <si>
-    <t>1990000_27000</t>
+    <t>1990000_8000</t>
+  </si>
+  <si>
+    <t>1990000_74000</t>
   </si>
   <si>
     <t>xgfpj_props_4.png</t>
@@ -148,7 +148,7 @@
     <t>绿色宝箱</t>
   </si>
   <si>
-    <t>1990000_5500</t>
+    <t>1990000_14000</t>
   </si>
   <si>
     <t>xgfpj_props_2.png</t>
@@ -157,13 +157,13 @@
     <t>两个金币</t>
   </si>
   <si>
+    <t>1990000_59000</t>
+  </si>
+  <si>
     <t>1990000_22000</t>
   </si>
   <si>
-    <t>1990000_8300</t>
-  </si>
-  <si>
-    <t>1990000_16000</t>
+    <t>1990000_43000</t>
   </si>
   <si>
     <t>xgfpj_props_3.png</t>
@@ -172,76 +172,70 @@
     <t>一堆金币</t>
   </si>
   <si>
-    <t>1990000_11000</t>
-  </si>
-  <si>
-    <t>1990000_1354000</t>
-  </si>
-  <si>
-    <t>1990000_4500</t>
-  </si>
-  <si>
-    <t>1990000_451000</t>
+    <t>1990000_29000</t>
+  </si>
+  <si>
+    <t>1990000_458000</t>
+  </si>
+  <si>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>1990000_325000</t>
   </si>
   <si>
     <t>1990000_9000</t>
   </si>
   <si>
-    <t>1990000_135000</t>
-  </si>
-  <si>
-    <t>1990000_13500</t>
-  </si>
-  <si>
-    <t>1990000_72000</t>
-  </si>
-  <si>
-    <t>1990000_18000</t>
-  </si>
-  <si>
-    <t>1990000_36000</t>
-  </si>
-  <si>
-    <t>1990000_22500</t>
-  </si>
-  <si>
-    <t>1990000_31000</t>
-  </si>
-  <si>
-    <t>1990000_639000</t>
-  </si>
-  <si>
-    <t>1990000_2100</t>
-  </si>
-  <si>
-    <t>1990000_213000</t>
-  </si>
-  <si>
-    <t>1990000_4200</t>
-  </si>
-  <si>
-    <t>1990000_63000</t>
-  </si>
-  <si>
-    <t>1990000_6300</t>
-  </si>
-  <si>
-    <t>1990000_34000</t>
-  </si>
-  <si>
-    <t>1990000_8500</t>
-  </si>
-  <si>
-    <t>1990000_17000</t>
-  </si>
-  <si>
-    <t>1990000_10600</t>
-  </si>
-  <si>
-    <t>1990000_14000</t>
-  </si>
-  <si>
-    <t>1990000_12700</t>
+    <t>1990000_242000</t>
+  </si>
+  <si>
+    <t>1990000_15000</t>
+  </si>
+  <si>
+    <t>1990000_144000</t>
+  </si>
+  <si>
+    <t>1990000_28000</t>
+  </si>
+  <si>
+    <t>1990000_115000</t>
+  </si>
+  <si>
+    <t>1990000_85000</t>
+  </si>
+  <si>
+    <t>1990000_57000</t>
+  </si>
+  <si>
+    <t>1990000_316000</t>
+  </si>
+  <si>
+    <t>1990000_246000</t>
+  </si>
+  <si>
+    <t>1990000_7000</t>
+  </si>
+  <si>
+    <t>1990000_183000</t>
+  </si>
+  <si>
+    <t>1990000_12000</t>
+  </si>
+  <si>
+    <t>1990000_109000</t>
+  </si>
+  <si>
+    <t>1990000_21000</t>
+  </si>
+  <si>
+    <t>1990000_87000</t>
+  </si>
+  <si>
+    <t>1990000_32000</t>
+  </si>
+  <si>
+    <t>1990000_64000</t>
   </si>
 </sst>
 </file>
@@ -1600,7 +1594,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="9">
-        <v>5357</v>
+        <v>2362</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -1634,7 +1628,7 @@
         <v>16</v>
       </c>
       <c r="D20" s="9">
-        <v>2143</v>
+        <v>1890</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>17</v>
@@ -1653,7 +1647,7 @@
         <v>23</v>
       </c>
       <c r="D21" s="9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>24</v>
@@ -1672,7 +1666,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="9">
-        <v>1071</v>
+        <v>1575</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>17</v>
@@ -1691,7 +1685,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="9">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>28</v>
@@ -1710,7 +1704,7 @@
         <v>30</v>
       </c>
       <c r="D24" s="9">
-        <v>357</v>
+        <v>1260</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>31</v>
@@ -1729,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="D25" s="9">
-        <v>179</v>
+        <v>472</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>28</v>
@@ -1742,13 +1736,13 @@
         <v>210</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D26" s="9">
-        <v>286</v>
+        <v>945</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>31</v>
@@ -1761,13 +1755,13 @@
         <v>211</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D27" s="9">
-        <v>214</v>
+        <v>630</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>36</v>
@@ -1780,13 +1774,13 @@
         <v>212</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="9">
-        <v>250</v>
+        <v>709</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
@@ -1818,13 +1812,13 @@
         <v>302</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="10">
-        <v>2045</v>
+        <v>2362</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>17</v>
@@ -1837,7 +1831,7 @@
         <v>303</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>19</v>
@@ -1856,13 +1850,13 @@
         <v>304</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D32" s="10">
-        <v>1705</v>
+        <v>1890</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>17</v>
@@ -1875,13 +1869,13 @@
         <v>305</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D33" s="10">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>24</v>
@@ -1894,13 +1888,13 @@
         <v>306</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D34" s="10">
-        <v>1136</v>
+        <v>1575</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>17</v>
@@ -1913,13 +1907,13 @@
         <v>307</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D35" s="10">
-        <v>455</v>
+        <v>157</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>28</v>
@@ -1932,13 +1926,13 @@
         <v>308</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D36" s="10">
-        <v>1136</v>
+        <v>1260</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>31</v>
@@ -1951,13 +1945,13 @@
         <v>309</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D37" s="10">
-        <v>682</v>
+        <v>472</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>28</v>
@@ -1970,13 +1964,13 @@
         <v>310</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="10">
-        <v>1023</v>
+        <v>945</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>31</v>
@@ -1989,13 +1983,13 @@
         <v>311</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D39" s="10">
-        <v>795</v>
+        <v>630</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>36</v>
@@ -2008,13 +2002,13 @@
         <v>312</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="10">
-        <v>909</v>
+        <v>709</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>36</v>
